--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -183,7 +183,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K30"/>
+  <dimension ref="B2:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>2150</v>
+        <v>2104</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1</v>
+        <v>0.967153</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>2311</v>
+        <v>2196</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024</t>
+          <t>Year built: 2023/2024; Occ: CoStar 97% vs RealPage 100%</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q2 2028</t>
         </is>
       </c>
       <c r="F11" s="10" t="n"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
@@ -813,15 +813,15 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Seasons on the Bench</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>358</v>
+        <v>180</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="F12" s="10" t="n"/>
@@ -838,12 +838,12 @@
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
@@ -853,15 +853,15 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>Seasons on the Bench</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>189</v>
+        <v>358</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="F13" s="10" t="n"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
@@ -893,15 +893,15 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="F14" s="10" t="n"/>
@@ -918,12 +918,12 @@
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F15" s="10" t="n"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q4 2026</t>
         </is>
       </c>
       <c r="F16" s="10" t="n"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q2 2028</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -1104,7 +1104,7 @@
     <row r="21">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Q1 2024</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="C21" s="7" t="n"/>
@@ -1144,7 +1144,7 @@
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Q4 2023</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -1184,7 +1184,7 @@
     <row r="23">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Q3 2023</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -1224,7 +1224,7 @@
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Q2 2023</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -1262,105 +1262,761 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Q1 2027</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7">
+        <f>COUNTIF($E$6:$E$16,B25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="9">
+        <f>SUMIF($E$6:$E$16,B25,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f t="array" ref="F25">IFERROR(SUMPRODUCT(($E$6:$E$16=B25)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B25)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="9">
+        <f>F25*E25</f>
+        <v/>
+      </c>
+      <c r="H25" s="9">
+        <f>E25*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I25" s="9">
+        <f>(E25*0.95)-G25</f>
+        <v/>
+      </c>
+      <c r="J25" s="9">
+        <f>(E25*0.925)-G25</f>
+        <v/>
+      </c>
+      <c r="K25" s="9">
+        <f>(E25*0.90)-G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7">
+        <f>COUNTIF($E$6:$E$16,B26)</f>
+        <v/>
+      </c>
+      <c r="E26" s="9">
+        <f>SUMIF($E$6:$E$16,B26,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F26" s="10">
+        <f t="array" ref="F26">IFERROR(SUMPRODUCT(($E$6:$E$16=B26)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B26)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="9">
+        <f>F26*E26</f>
+        <v/>
+      </c>
+      <c r="H26" s="9">
+        <f>E26*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I26" s="9">
+        <f>(E26*0.95)-G26</f>
+        <v/>
+      </c>
+      <c r="J26" s="9">
+        <f>(E26*0.925)-G26</f>
+        <v/>
+      </c>
+      <c r="K26" s="9">
+        <f>(E26*0.90)-G26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7">
+        <f>COUNTIF($E$6:$E$16,B27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="9">
+        <f>SUMIF($E$6:$E$16,B27,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F27" s="10">
+        <f t="array" ref="F27">IFERROR(SUMPRODUCT(($E$6:$E$16=B27)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B27)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="9">
+        <f>F27*E27</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>E27*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I27" s="9">
+        <f>(E27*0.95)-G27</f>
+        <v/>
+      </c>
+      <c r="J27" s="9">
+        <f>(E27*0.925)-G27</f>
+        <v/>
+      </c>
+      <c r="K27" s="9">
+        <f>(E27*0.90)-G27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7">
+        <f>COUNTIF($E$6:$E$16,B28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="9">
+        <f>SUMIF($E$6:$E$16,B28,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F28" s="10">
+        <f t="array" ref="F28">IFERROR(SUMPRODUCT(($E$6:$E$16=B28)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B28)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="9">
+        <f>F28*E28</f>
+        <v/>
+      </c>
+      <c r="H28" s="9">
+        <f>E28*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I28" s="9">
+        <f>(E28*0.95)-G28</f>
+        <v/>
+      </c>
+      <c r="J28" s="9">
+        <f>(E28*0.925)-G28</f>
+        <v/>
+      </c>
+      <c r="K28" s="9">
+        <f>(E28*0.90)-G28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7">
+        <f>COUNTIF($E$6:$E$16,B29)</f>
+        <v/>
+      </c>
+      <c r="E29" s="9">
+        <f>SUMIF($E$6:$E$16,B29,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F29" s="10">
+        <f t="array" ref="F29">IFERROR(SUMPRODUCT(($E$6:$E$16=B29)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B29)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="9">
+        <f>F29*E29</f>
+        <v/>
+      </c>
+      <c r="H29" s="9">
+        <f>E29*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I29" s="9">
+        <f>(E29*0.95)-G29</f>
+        <v/>
+      </c>
+      <c r="J29" s="9">
+        <f>(E29*0.925)-G29</f>
+        <v/>
+      </c>
+      <c r="K29" s="9">
+        <f>(E29*0.90)-G29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7">
+        <f>COUNTIF($E$6:$E$16,B30)</f>
+        <v/>
+      </c>
+      <c r="E30" s="9">
+        <f>SUMIF($E$6:$E$16,B30,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f t="array" ref="F30">IFERROR(SUMPRODUCT(($E$6:$E$16=B30)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B30)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="9">
+        <f>F30*E30</f>
+        <v/>
+      </c>
+      <c r="H30" s="9">
+        <f>E30*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I30" s="9">
+        <f>(E30*0.95)-G30</f>
+        <v/>
+      </c>
+      <c r="J30" s="9">
+        <f>(E30*0.925)-G30</f>
+        <v/>
+      </c>
+      <c r="K30" s="9">
+        <f>(E30*0.90)-G30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7">
+        <f>COUNTIF($E$6:$E$16,B31)</f>
+        <v/>
+      </c>
+      <c r="E31" s="9">
+        <f>SUMIF($E$6:$E$16,B31,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f t="array" ref="F31">IFERROR(SUMPRODUCT(($E$6:$E$16=B31)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B31)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="9">
+        <f>F31*E31</f>
+        <v/>
+      </c>
+      <c r="H31" s="9">
+        <f>E31*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I31" s="9">
+        <f>(E31*0.95)-G31</f>
+        <v/>
+      </c>
+      <c r="J31" s="9">
+        <f>(E31*0.925)-G31</f>
+        <v/>
+      </c>
+      <c r="K31" s="9">
+        <f>(E31*0.90)-G31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7">
+        <f>COUNTIF($E$6:$E$16,B32)</f>
+        <v/>
+      </c>
+      <c r="E32" s="9">
+        <f>SUMIF($E$6:$E$16,B32,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F32" s="10">
+        <f t="array" ref="F32">IFERROR(SUMPRODUCT(($E$6:$E$16=B32)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B32)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="9">
+        <f>F32*E32</f>
+        <v/>
+      </c>
+      <c r="H32" s="9">
+        <f>E32*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I32" s="9">
+        <f>(E32*0.95)-G32</f>
+        <v/>
+      </c>
+      <c r="J32" s="9">
+        <f>(E32*0.925)-G32</f>
+        <v/>
+      </c>
+      <c r="K32" s="9">
+        <f>(E32*0.90)-G32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7">
+        <f>COUNTIF($E$6:$E$16,B33)</f>
+        <v/>
+      </c>
+      <c r="E33" s="9">
+        <f>SUMIF($E$6:$E$16,B33,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F33" s="10">
+        <f t="array" ref="F33">IFERROR(SUMPRODUCT(($E$6:$E$16=B33)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B33)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="9">
+        <f>F33*E33</f>
+        <v/>
+      </c>
+      <c r="H33" s="9">
+        <f>E33*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I33" s="9">
+        <f>(E33*0.95)-G33</f>
+        <v/>
+      </c>
+      <c r="J33" s="9">
+        <f>(E33*0.925)-G33</f>
+        <v/>
+      </c>
+      <c r="K33" s="9">
+        <f>(E33*0.90)-G33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7">
+        <f>COUNTIF($E$6:$E$16,B34)</f>
+        <v/>
+      </c>
+      <c r="E34" s="9">
+        <f>SUMIF($E$6:$E$16,B34,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f t="array" ref="F34">IFERROR(SUMPRODUCT(($E$6:$E$16=B34)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B34)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="9">
+        <f>F34*E34</f>
+        <v/>
+      </c>
+      <c r="H34" s="9">
+        <f>E34*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I34" s="9">
+        <f>(E34*0.95)-G34</f>
+        <v/>
+      </c>
+      <c r="J34" s="9">
+        <f>(E34*0.925)-G34</f>
+        <v/>
+      </c>
+      <c r="K34" s="9">
+        <f>(E34*0.90)-G34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Q3 2024</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7">
+        <f>COUNTIF($E$6:$E$16,B35)</f>
+        <v/>
+      </c>
+      <c r="E35" s="9">
+        <f>SUMIF($E$6:$E$16,B35,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f t="array" ref="F35">IFERROR(SUMPRODUCT(($E$6:$E$16=B35)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B35)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="9">
+        <f>F35*E35</f>
+        <v/>
+      </c>
+      <c r="H35" s="9">
+        <f>E35*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I35" s="9">
+        <f>(E35*0.95)-G35</f>
+        <v/>
+      </c>
+      <c r="J35" s="9">
+        <f>(E35*0.925)-G35</f>
+        <v/>
+      </c>
+      <c r="K35" s="9">
+        <f>(E35*0.90)-G35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Q2 2024</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7">
+        <f>COUNTIF($E$6:$E$16,B36)</f>
+        <v/>
+      </c>
+      <c r="E36" s="9">
+        <f>SUMIF($E$6:$E$16,B36,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f t="array" ref="F36">IFERROR(SUMPRODUCT(($E$6:$E$16=B36)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B36)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="9">
+        <f>F36*E36</f>
+        <v/>
+      </c>
+      <c r="H36" s="9">
+        <f>E36*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I36" s="9">
+        <f>(E36*0.95)-G36</f>
+        <v/>
+      </c>
+      <c r="J36" s="9">
+        <f>(E36*0.925)-G36</f>
+        <v/>
+      </c>
+      <c r="K36" s="9">
+        <f>(E36*0.90)-G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Q1 2024</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7">
+        <f>COUNTIF($E$6:$E$16,B37)</f>
+        <v/>
+      </c>
+      <c r="E37" s="9">
+        <f>SUMIF($E$6:$E$16,B37,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F37" s="10">
+        <f t="array" ref="F37">IFERROR(SUMPRODUCT(($E$6:$E$16=B37)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B37)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="9">
+        <f>F37*E37</f>
+        <v/>
+      </c>
+      <c r="H37" s="9">
+        <f>E37*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I37" s="9">
+        <f>(E37*0.95)-G37</f>
+        <v/>
+      </c>
+      <c r="J37" s="9">
+        <f>(E37*0.925)-G37</f>
+        <v/>
+      </c>
+      <c r="K37" s="9">
+        <f>(E37*0.90)-G37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Q4 2023</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7">
+        <f>COUNTIF($E$6:$E$16,B38)</f>
+        <v/>
+      </c>
+      <c r="E38" s="9">
+        <f>SUMIF($E$6:$E$16,B38,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F38" s="10">
+        <f t="array" ref="F38">IFERROR(SUMPRODUCT(($E$6:$E$16=B38)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B38)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G38" s="9">
+        <f>F38*E38</f>
+        <v/>
+      </c>
+      <c r="H38" s="9">
+        <f>E38*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I38" s="9">
+        <f>(E38*0.95)-G38</f>
+        <v/>
+      </c>
+      <c r="J38" s="9">
+        <f>(E38*0.925)-G38</f>
+        <v/>
+      </c>
+      <c r="K38" s="9">
+        <f>(E38*0.90)-G38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Q3 2023</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7">
+        <f>COUNTIF($E$6:$E$16,B39)</f>
+        <v/>
+      </c>
+      <c r="E39" s="9">
+        <f>SUMIF($E$6:$E$16,B39,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f t="array" ref="F39">IFERROR(SUMPRODUCT(($E$6:$E$16=B39)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B39)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G39" s="9">
+        <f>F39*E39</f>
+        <v/>
+      </c>
+      <c r="H39" s="9">
+        <f>E39*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I39" s="9">
+        <f>(E39*0.95)-G39</f>
+        <v/>
+      </c>
+      <c r="J39" s="9">
+        <f>(E39*0.925)-G39</f>
+        <v/>
+      </c>
+      <c r="K39" s="9">
+        <f>(E39*0.90)-G39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Q2 2023</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7">
+        <f>COUNTIF($E$6:$E$16,B40)</f>
+        <v/>
+      </c>
+      <c r="E40" s="9">
+        <f>SUMIF($E$6:$E$16,B40,$D$6:$D$16)</f>
+        <v/>
+      </c>
+      <c r="F40" s="10">
+        <f t="array" ref="F40">IFERROR(SUMPRODUCT(($E$6:$E$16=B40)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B40)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
+        <v/>
+      </c>
+      <c r="G40" s="9">
+        <f>F40*E40</f>
+        <v/>
+      </c>
+      <c r="H40" s="9">
+        <f>E40*Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="I40" s="9">
+        <f>(E40*0.95)-G40</f>
+        <v/>
+      </c>
+      <c r="J40" s="9">
+        <f>(E40*0.925)-G40</f>
+        <v/>
+      </c>
+      <c r="K40" s="9">
+        <f>(E40*0.90)-G40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4">
-        <f>SUM(D20:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="14">
-        <f>SUM(E20:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="15">
-        <f>IFERROR(SUMPRODUCT($E$20:$E$24,F20:F24)/$E$25,0)</f>
-        <v/>
-      </c>
-      <c r="G25" s="14">
-        <f>SUM(G20:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="14">
-        <f>SUM(H20:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="14">
-        <f>SUM(I20:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="14">
-        <f>SUM(J20:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="14">
-        <f>SUM(K20:K24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="G27" s="16" t="inlineStr">
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4">
+        <f>SUM(D20:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="14">
+        <f>SUM(E20:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="15">
+        <f>IFERROR(SUMPRODUCT($E$20:$E$40,F20:F40)/$E$41,0)</f>
+        <v/>
+      </c>
+      <c r="G41" s="14">
+        <f>SUM(G20:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="14">
+        <f>SUM(H20:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="14">
+        <f>SUM(I20:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="14">
+        <f>SUM(J20:J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="14">
+        <f>SUM(K20:K40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>Total Current Inventory</t>
         </is>
       </c>
-      <c r="I27" s="17" t="n">
+      <c r="I43" s="17" t="n">
         <v>5925</v>
       </c>
-      <c r="J27" s="18">
-        <f>I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="18">
-        <f>I27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="G28" s="16" t="inlineStr">
+      <c r="J43" s="18">
+        <f>I43</f>
+        <v/>
+      </c>
+      <c r="K43" s="18">
+        <f>I43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="G44" s="16" t="inlineStr">
         <is>
           <t>% to be Absorbed</t>
         </is>
       </c>
-      <c r="I28" s="19">
-        <f>IFERROR(I25/I27,0)</f>
-        <v/>
-      </c>
-      <c r="J28" s="19">
-        <f>IFERROR(J25/J27,0)</f>
-        <v/>
-      </c>
-      <c r="K28" s="19">
-        <f>IFERROR(K25/K27,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="20" t="inlineStr">
+      <c r="I44" s="19">
+        <f>IFERROR(I41/I43,0)</f>
+        <v/>
+      </c>
+      <c r="J44" s="19">
+        <f>IFERROR(J41/J43,0)</f>
+        <v/>
+      </c>
+      <c r="K44" s="19">
+        <f>IFERROR(K41/K43,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>* 5-Mile radius. Total inventory from CoStar Data Analytics. Proximity (mi) to be filled manually. Lease-up rent/occupancy should be verified with a HelloData pull.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="30">
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B46:K46"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="C2:G2"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="C5:K5"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B30:K30"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1412,68 +2068,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="H1" s="23" t="inlineStr">
-        <is>
-          <t>Eff Rent</t>
-        </is>
-      </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
+        <is>
+          <t>CoStar Occ</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
+        <is>
+          <t>RealPage Occ</t>
+        </is>
+      </c>
+      <c r="I1" s="16" t="inlineStr">
+        <is>
+          <t>CoStar Ask Rent</t>
+        </is>
+      </c>
+      <c r="J1" s="16" t="inlineStr">
+        <is>
+          <t>RealPage Eff Rent</t>
+        </is>
+      </c>
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="J1" s="23" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1506,18 +2174,24 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="23" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H2" s="23" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" s="18" t="n">
+        <v>2104</v>
+      </c>
+      <c r="J2" s="18" t="n">
         <v>2150</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1546,18 +2220,20 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="23" t="n"/>
+      <c r="H3" s="23" t="n">
         <v>0.961</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="18" t="n">
         <v>1273</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>RealPage</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>RealPage only (sub-50 unit)</t>
         </is>
@@ -1590,200 +2266,260 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="23" t="n">
+        <v>0.967153</v>
+      </c>
+      <c r="H4" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" s="18" t="n">
+        <v>2196</v>
+      </c>
+      <c r="J4" s="18" t="n">
         <v>2311</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Year built: 2023/2024</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Year built: 2023/2024; Occ: CoStar 97% vs RealPage 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Station Village</t>
+          <t>Vista Point</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2350 W Kootenai St</t>
+          <t>2017 W Victory Rd</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>84</v>
+        <v>893</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="G5" s="23" t="n"/>
+      <c r="H5" s="23" t="n"/>
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="n"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>RealPage</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Seasons on the Bench</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2521 W Victory Rd</t>
+          <t>3300 S Vista Ave</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>358</v>
+        <v>180</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>RealPage</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vista Point</t>
+          <t>Seasons on the Bench</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2017 W Victory Rd</t>
+          <t>2521 W Victory Rd</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>893</v>
+        <v>358</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Q4 2027</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>RealPage</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3300 S Vista Ave</t>
+          <t>1519 S Londoner Ave</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>180</v>
+        <v>189</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>RealPage</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Harris Ranch East</t>
+          <t>Station Village</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3201 S Council Spring Rd</t>
+          <t>2350 W Kootenai St</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>59</v>
+        <v>84</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>RealPage</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>Harris Ranch East</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1519 S Londoner Ave</t>
+          <t>3201 S Council Spring Rd</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>59</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>RealPage</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>

--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -76,7 +76,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +91,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -158,7 +173,35 @@
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -760,301 +803,301 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>PROPOSED (6 properties, 1,763 units)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Vista Point</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="16" t="n">
         <v>893</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>3300 South Vista Avenue</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="16" t="n">
         <v>180</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Q1 2028</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Seasons on the Bench</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="16" t="n">
         <v>358</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>1519 South Londoner Avenue</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="16" t="n">
         <v>189</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Station Village</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="16" t="n">
         <v>84</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>Privately Owned</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="I15" s="14" t="n"/>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Harris Ranch East</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="16" t="n">
         <v>59</v>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>Single Family</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K16" s="15" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t># Props</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>Total Units</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>Wtd Avg
 Occupancy</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>Currently
 Occupied</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="H19" s="19" t="inlineStr">
         <is>
           <t>Target
 @ Goal</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
+      <c r="I19" s="19" t="inlineStr">
         <is>
           <t>Units to
 95%</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J19" s="19" t="inlineStr">
         <is>
           <t>Units to
 92.5%</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr">
+      <c r="K19" s="19" t="inlineStr">
         <is>
           <t>Units to
 90%</t>
@@ -1062,847 +1105,847 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7">
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20">
         <f>COUNTIF($E$6:$E$16,B20)</f>
         <v/>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="21">
         <f>SUMIF($E$6:$E$16,B20,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="22">
         <f t="array" ref="F20">IFERROR(SUMPRODUCT(($E$6:$E$16=B20)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B20)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="21">
         <f>F20*E20</f>
         <v/>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="21">
         <f>E20*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="21">
         <f>(E20*0.95)-G20</f>
         <v/>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="21">
         <f>(E20*0.925)-G20</f>
         <v/>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="21">
         <f>(E20*0.90)-G20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Q1 2028</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7">
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20">
         <f>COUNTIF($E$6:$E$16,B21)</f>
         <v/>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="21">
         <f>SUMIF($E$6:$E$16,B21,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="22">
         <f t="array" ref="F21">IFERROR(SUMPRODUCT(($E$6:$E$16=B21)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B21)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="21">
         <f>F21*E21</f>
         <v/>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="21">
         <f>E21*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="21">
         <f>(E21*0.95)-G21</f>
         <v/>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="21">
         <f>(E21*0.925)-G21</f>
         <v/>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="21">
         <f>(E21*0.90)-G21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7">
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20">
         <f>COUNTIF($E$6:$E$16,B22)</f>
         <v/>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="21">
         <f>SUMIF($E$6:$E$16,B22,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="22">
         <f t="array" ref="F22">IFERROR(SUMPRODUCT(($E$6:$E$16=B22)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B22)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="21">
         <f>F22*E22</f>
         <v/>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="21">
         <f>E22*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="21">
         <f>(E22*0.95)-G22</f>
         <v/>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="21">
         <f>(E22*0.925)-G22</f>
         <v/>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="21">
         <f>(E22*0.90)-G22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7">
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20">
         <f>COUNTIF($E$6:$E$16,B23)</f>
         <v/>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="21">
         <f>SUMIF($E$6:$E$16,B23,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="22">
         <f t="array" ref="F23">IFERROR(SUMPRODUCT(($E$6:$E$16=B23)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B23)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="21">
         <f>F23*E23</f>
         <v/>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="21">
         <f>E23*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="21">
         <f>(E23*0.95)-G23</f>
         <v/>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="21">
         <f>(E23*0.925)-G23</f>
         <v/>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="21">
         <f>(E23*0.90)-G23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7">
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20">
         <f>COUNTIF($E$6:$E$16,B24)</f>
         <v/>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="21">
         <f>SUMIF($E$6:$E$16,B24,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="22">
         <f t="array" ref="F24">IFERROR(SUMPRODUCT(($E$6:$E$16=B24)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B24)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="21">
         <f>F24*E24</f>
         <v/>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="21">
         <f>E24*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="21">
         <f>(E24*0.95)-G24</f>
         <v/>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="21">
         <f>(E24*0.925)-G24</f>
         <v/>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="21">
         <f>(E24*0.90)-G24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Q1 2027</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7">
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20">
         <f>COUNTIF($E$6:$E$16,B25)</f>
         <v/>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="21">
         <f>SUMIF($E$6:$E$16,B25,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="22">
         <f t="array" ref="F25">IFERROR(SUMPRODUCT(($E$6:$E$16=B25)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B25)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="21">
         <f>F25*E25</f>
         <v/>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="21">
         <f>E25*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="21">
         <f>(E25*0.95)-G25</f>
         <v/>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="21">
         <f>(E25*0.925)-G25</f>
         <v/>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="21">
         <f>(E25*0.90)-G25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7">
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20">
         <f>COUNTIF($E$6:$E$16,B26)</f>
         <v/>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="21">
         <f>SUMIF($E$6:$E$16,B26,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="22">
         <f t="array" ref="F26">IFERROR(SUMPRODUCT(($E$6:$E$16=B26)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B26)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="21">
         <f>F26*E26</f>
         <v/>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="21">
         <f>E26*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="21">
         <f>(E26*0.95)-G26</f>
         <v/>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="21">
         <f>(E26*0.925)-G26</f>
         <v/>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="21">
         <f>(E26*0.90)-G26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>Q3 2026</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7">
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20">
         <f>COUNTIF($E$6:$E$16,B27)</f>
         <v/>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="21">
         <f>SUMIF($E$6:$E$16,B27,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="22">
         <f t="array" ref="F27">IFERROR(SUMPRODUCT(($E$6:$E$16=B27)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B27)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="21">
         <f>F27*E27</f>
         <v/>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="21">
         <f>E27*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="21">
         <f>(E27*0.95)-G27</f>
         <v/>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="21">
         <f>(E27*0.925)-G27</f>
         <v/>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="21">
         <f>(E27*0.90)-G27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7">
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20">
         <f>COUNTIF($E$6:$E$16,B28)</f>
         <v/>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="21">
         <f>SUMIF($E$6:$E$16,B28,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="22">
         <f t="array" ref="F28">IFERROR(SUMPRODUCT(($E$6:$E$16=B28)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B28)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="21">
         <f>F28*E28</f>
         <v/>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="21">
         <f>E28*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="21">
         <f>(E28*0.95)-G28</f>
         <v/>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="21">
         <f>(E28*0.925)-G28</f>
         <v/>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="21">
         <f>(E28*0.90)-G28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>Q1 2026</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7">
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20">
         <f>COUNTIF($E$6:$E$16,B29)</f>
         <v/>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="21">
         <f>SUMIF($E$6:$E$16,B29,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="22">
         <f t="array" ref="F29">IFERROR(SUMPRODUCT(($E$6:$E$16=B29)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B29)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="21">
         <f>F29*E29</f>
         <v/>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="21">
         <f>E29*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="21">
         <f>(E29*0.95)-G29</f>
         <v/>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="21">
         <f>(E29*0.925)-G29</f>
         <v/>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="21">
         <f>(E29*0.90)-G29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7">
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20">
         <f>COUNTIF($E$6:$E$16,B30)</f>
         <v/>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="21">
         <f>SUMIF($E$6:$E$16,B30,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="22">
         <f t="array" ref="F30">IFERROR(SUMPRODUCT(($E$6:$E$16=B30)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B30)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="21">
         <f>F30*E30</f>
         <v/>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="21">
         <f>E30*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="21">
         <f>(E30*0.95)-G30</f>
         <v/>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="21">
         <f>(E30*0.925)-G30</f>
         <v/>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="21">
         <f>(E30*0.90)-G30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7">
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20">
         <f>COUNTIF($E$6:$E$16,B31)</f>
         <v/>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="21">
         <f>SUMIF($E$6:$E$16,B31,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="22">
         <f t="array" ref="F31">IFERROR(SUMPRODUCT(($E$6:$E$16=B31)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B31)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="21">
         <f>F31*E31</f>
         <v/>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="21">
         <f>E31*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="21">
         <f>(E31*0.95)-G31</f>
         <v/>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="21">
         <f>(E31*0.925)-G31</f>
         <v/>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="21">
         <f>(E31*0.90)-G31</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7">
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20">
         <f>COUNTIF($E$6:$E$16,B32)</f>
         <v/>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="21">
         <f>SUMIF($E$6:$E$16,B32,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="22">
         <f t="array" ref="F32">IFERROR(SUMPRODUCT(($E$6:$E$16=B32)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B32)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="21">
         <f>F32*E32</f>
         <v/>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="21">
         <f>E32*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="21">
         <f>(E32*0.95)-G32</f>
         <v/>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="21">
         <f>(E32*0.925)-G32</f>
         <v/>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="21">
         <f>(E32*0.90)-G32</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>Q1 2025</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7">
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20">
         <f>COUNTIF($E$6:$E$16,B33)</f>
         <v/>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="21">
         <f>SUMIF($E$6:$E$16,B33,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="22">
         <f t="array" ref="F33">IFERROR(SUMPRODUCT(($E$6:$E$16=B33)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B33)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="21">
         <f>F33*E33</f>
         <v/>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="21">
         <f>E33*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="21">
         <f>(E33*0.95)-G33</f>
         <v/>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="21">
         <f>(E33*0.925)-G33</f>
         <v/>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="21">
         <f>(E33*0.90)-G33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>Q4 2024</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7">
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20">
         <f>COUNTIF($E$6:$E$16,B34)</f>
         <v/>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="21">
         <f>SUMIF($E$6:$E$16,B34,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="22">
         <f t="array" ref="F34">IFERROR(SUMPRODUCT(($E$6:$E$16=B34)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B34)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="21">
         <f>F34*E34</f>
         <v/>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="21">
         <f>E34*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="21">
         <f>(E34*0.95)-G34</f>
         <v/>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="21">
         <f>(E34*0.925)-G34</f>
         <v/>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="21">
         <f>(E34*0.90)-G34</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Q3 2024</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7">
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20">
         <f>COUNTIF($E$6:$E$16,B35)</f>
         <v/>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="21">
         <f>SUMIF($E$6:$E$16,B35,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="22">
         <f t="array" ref="F35">IFERROR(SUMPRODUCT(($E$6:$E$16=B35)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B35)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="21">
         <f>F35*E35</f>
         <v/>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="21">
         <f>E35*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="21">
         <f>(E35*0.95)-G35</f>
         <v/>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="21">
         <f>(E35*0.925)-G35</f>
         <v/>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="21">
         <f>(E35*0.90)-G35</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>Q2 2024</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7">
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20">
         <f>COUNTIF($E$6:$E$16,B36)</f>
         <v/>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="21">
         <f>SUMIF($E$6:$E$16,B36,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="22">
         <f t="array" ref="F36">IFERROR(SUMPRODUCT(($E$6:$E$16=B36)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B36)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="21">
         <f>F36*E36</f>
         <v/>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="21">
         <f>E36*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="21">
         <f>(E36*0.95)-G36</f>
         <v/>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="21">
         <f>(E36*0.925)-G36</f>
         <v/>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="21">
         <f>(E36*0.90)-G36</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>Q1 2024</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7">
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20">
         <f>COUNTIF($E$6:$E$16,B37)</f>
         <v/>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="21">
         <f>SUMIF($E$6:$E$16,B37,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="22">
         <f t="array" ref="F37">IFERROR(SUMPRODUCT(($E$6:$E$16=B37)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B37)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="21">
         <f>F37*E37</f>
         <v/>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="21">
         <f>E37*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="21">
         <f>(E37*0.95)-G37</f>
         <v/>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="21">
         <f>(E37*0.925)-G37</f>
         <v/>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="21">
         <f>(E37*0.90)-G37</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Q4 2023</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7">
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20">
         <f>COUNTIF($E$6:$E$16,B38)</f>
         <v/>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="21">
         <f>SUMIF($E$6:$E$16,B38,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="22">
         <f t="array" ref="F38">IFERROR(SUMPRODUCT(($E$6:$E$16=B38)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B38)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="21">
         <f>F38*E38</f>
         <v/>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="21">
         <f>E38*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="21">
         <f>(E38*0.95)-G38</f>
         <v/>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="21">
         <f>(E38*0.925)-G38</f>
         <v/>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="21">
         <f>(E38*0.90)-G38</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>Q3 2023</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7">
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20">
         <f>COUNTIF($E$6:$E$16,B39)</f>
         <v/>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="21">
         <f>SUMIF($E$6:$E$16,B39,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="22">
         <f t="array" ref="F39">IFERROR(SUMPRODUCT(($E$6:$E$16=B39)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B39)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="21">
         <f>F39*E39</f>
         <v/>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="21">
         <f>E39*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="21">
         <f>(E39*0.95)-G39</f>
         <v/>
       </c>
-      <c r="J39" s="9">
+      <c r="J39" s="21">
         <f>(E39*0.925)-G39</f>
         <v/>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="21">
         <f>(E39*0.90)-G39</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>Q2 2023</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7">
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20">
         <f>COUNTIF($E$6:$E$16,B40)</f>
         <v/>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="21">
         <f>SUMIF($E$6:$E$16,B40,$D$6:$D$16)</f>
         <v/>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="22">
         <f t="array" ref="F40">IFERROR(SUMPRODUCT(($E$6:$E$16=B40)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B40)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
         <v/>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="21">
         <f>F40*E40</f>
         <v/>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="21">
         <f>E40*Settings!$B$2</f>
         <v/>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="21">
         <f>(E40*0.95)-G40</f>
         <v/>
       </c>
-      <c r="J40" s="9">
+      <c r="J40" s="21">
         <f>(E40*0.925)-G40</f>
         <v/>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="21">
         <f>(E40*0.90)-G40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -1912,74 +1955,74 @@
         <f>SUM(D20:D40)</f>
         <v/>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="24">
         <f>SUM(E20:E40)</f>
         <v/>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="25">
         <f>IFERROR(SUMPRODUCT($E$20:$E$40,F20:F40)/$E$41,0)</f>
         <v/>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="24">
         <f>SUM(G20:G40)</f>
         <v/>
       </c>
-      <c r="H41" s="14">
+      <c r="H41" s="24">
         <f>SUM(H20:H40)</f>
         <v/>
       </c>
-      <c r="I41" s="14">
+      <c r="I41" s="24">
         <f>SUM(I20:I40)</f>
         <v/>
       </c>
-      <c r="J41" s="14">
+      <c r="J41" s="24">
         <f>SUM(J20:J40)</f>
         <v/>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="24">
         <f>SUM(K20:K40)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="G43" s="16" t="inlineStr">
+      <c r="G43" s="26" t="inlineStr">
         <is>
           <t>Total Current Inventory</t>
         </is>
       </c>
-      <c r="I43" s="17" t="n">
+      <c r="I43" s="27" t="n">
         <v>5925</v>
       </c>
-      <c r="J43" s="18">
+      <c r="J43" s="28">
         <f>I43</f>
         <v/>
       </c>
-      <c r="K43" s="18">
+      <c r="K43" s="28">
         <f>I43</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="G44" s="16" t="inlineStr">
+      <c r="G44" s="26" t="inlineStr">
         <is>
           <t>% to be Absorbed</t>
         </is>
       </c>
-      <c r="I44" s="19">
+      <c r="I44" s="29">
         <f>IFERROR(I41/I43,0)</f>
         <v/>
       </c>
-      <c r="J44" s="19">
+      <c r="J44" s="29">
         <f>IFERROR(J41/J43,0)</f>
         <v/>
       </c>
-      <c r="K44" s="19">
+      <c r="K44" s="29">
         <f>IFERROR(K41/K43,0)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>* 5-Mile radius. Total inventory from CoStar Data Analytics. Proximity (mi) to be filled manually. Lease-up rent/occupancy should be verified with a HelloData pull.</t>
         </is>
@@ -2036,7 +2079,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>ANALYSIS SETTINGS</t>
         </is>
@@ -2048,7 +2091,7 @@
           <t>Stabilized Occupancy Target</t>
         </is>
       </c>
-      <c r="B2" s="22" t="n">
+      <c r="B2" s="32" t="n">
         <v>0.95</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -2086,62 +2129,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="G1" s="16" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>CoStar Occ</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>RealPage Occ</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>CoStar Ask Rent</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>RealPage Eff Rent</t>
         </is>
       </c>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="K1" s="26" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="L1" s="16" t="inlineStr">
+      <c r="L1" s="26" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2174,16 +2217,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G2" s="23" t="n">
+      <c r="G2" s="33" t="n">
         <v>0.92</v>
       </c>
-      <c r="H2" s="23" t="n">
+      <c r="H2" s="33" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="I2" s="18" t="n">
+      <c r="I2" s="28" t="n">
         <v>2104</v>
       </c>
-      <c r="J2" s="18" t="n">
+      <c r="J2" s="28" t="n">
         <v>2150</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -2220,12 +2263,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G3" s="23" t="n"/>
-      <c r="H3" s="23" t="n">
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n">
         <v>0.961</v>
       </c>
-      <c r="I3" s="18" t="n"/>
-      <c r="J3" s="18" t="n">
+      <c r="I3" s="28" t="n"/>
+      <c r="J3" s="28" t="n">
         <v>1273</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -2266,16 +2309,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G4" s="23" t="n">
+      <c r="G4" s="33" t="n">
         <v>0.967153</v>
       </c>
-      <c r="H4" s="23" t="n">
+      <c r="H4" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="28" t="n">
         <v>2196</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="28" t="n">
         <v>2311</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -2313,10 +2356,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G5" s="23" t="n"/>
-      <c r="H5" s="23" t="n"/>
-      <c r="I5" s="18" t="n"/>
-      <c r="J5" s="18" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="28" t="n"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2352,10 +2395,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G6" s="23" t="n"/>
-      <c r="H6" s="23" t="n"/>
-      <c r="I6" s="18" t="n"/>
-      <c r="J6" s="18" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="28" t="n"/>
+      <c r="J6" s="28" t="n"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2391,10 +2434,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G7" s="23" t="n"/>
-      <c r="H7" s="23" t="n"/>
-      <c r="I7" s="18" t="n"/>
-      <c r="J7" s="18" t="n"/>
+      <c r="G7" s="33" t="n"/>
+      <c r="H7" s="33" t="n"/>
+      <c r="I7" s="28" t="n"/>
+      <c r="J7" s="28" t="n"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2430,10 +2473,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G8" s="23" t="n"/>
-      <c r="H8" s="23" t="n"/>
-      <c r="I8" s="18" t="n"/>
-      <c r="J8" s="18" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="33" t="n"/>
+      <c r="I8" s="28" t="n"/>
+      <c r="J8" s="28" t="n"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2469,10 +2512,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G9" s="23" t="n"/>
-      <c r="H9" s="23" t="n"/>
-      <c r="I9" s="18" t="n"/>
-      <c r="J9" s="18" t="n"/>
+      <c r="G9" s="33" t="n"/>
+      <c r="H9" s="33" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="28" t="n"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2508,10 +2551,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G10" s="23" t="n"/>
-      <c r="H10" s="23" t="n"/>
-      <c r="I10" s="18" t="n"/>
-      <c r="J10" s="18" t="n"/>
+      <c r="G10" s="33" t="n"/>
+      <c r="H10" s="33" t="n"/>
+      <c r="I10" s="28" t="n"/>
+      <c r="J10" s="28" t="n"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>RealPage</t>

--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Competitive Analysis" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Reconciliation Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Supply &amp; Absorption" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,9 +21,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0;;&quot;—&quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,12 +61,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <color rgb="FF808080"/>
       <sz val="8"/>
     </font>
@@ -75,8 +70,20 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -110,7 +117,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -140,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -192,41 +209,55 @@
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -592,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K46"/>
+  <dimension ref="B2:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1050,1016 +1081,20 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
+    <row r="19">
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t># Props</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>Total Units</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>Wtd Avg
-Occupancy</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>Currently
-Occupied</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>Target
-@ Goal</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>Units to
-95%</t>
-        </is>
-      </c>
-      <c r="J19" s="19" t="inlineStr">
-        <is>
-          <t>Units to
-92.5%</t>
-        </is>
-      </c>
-      <c r="K19" s="19" t="inlineStr">
-        <is>
-          <t>Units to
-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20">
-        <f>COUNTIF($E$6:$E$16,B20)</f>
-        <v/>
-      </c>
-      <c r="E20" s="21">
-        <f>SUMIF($E$6:$E$16,B20,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F20" s="22">
-        <f t="array" ref="F20">IFERROR(SUMPRODUCT(($E$6:$E$16=B20)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B20)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G20" s="21">
-        <f>F20*E20</f>
-        <v/>
-      </c>
-      <c r="H20" s="21">
-        <f>E20*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I20" s="21">
-        <f>(E20*0.95)-G20</f>
-        <v/>
-      </c>
-      <c r="J20" s="21">
-        <f>(E20*0.925)-G20</f>
-        <v/>
-      </c>
-      <c r="K20" s="21">
-        <f>(E20*0.90)-G20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Q1 2028</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20">
-        <f>COUNTIF($E$6:$E$16,B21)</f>
-        <v/>
-      </c>
-      <c r="E21" s="21">
-        <f>SUMIF($E$6:$E$16,B21,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F21" s="22">
-        <f t="array" ref="F21">IFERROR(SUMPRODUCT(($E$6:$E$16=B21)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B21)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="21">
-        <f>F21*E21</f>
-        <v/>
-      </c>
-      <c r="H21" s="21">
-        <f>E21*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I21" s="21">
-        <f>(E21*0.95)-G21</f>
-        <v/>
-      </c>
-      <c r="J21" s="21">
-        <f>(E21*0.925)-G21</f>
-        <v/>
-      </c>
-      <c r="K21" s="21">
-        <f>(E21*0.90)-G21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>Q4 2027</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20">
-        <f>COUNTIF($E$6:$E$16,B22)</f>
-        <v/>
-      </c>
-      <c r="E22" s="21">
-        <f>SUMIF($E$6:$E$16,B22,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F22" s="22">
-        <f t="array" ref="F22">IFERROR(SUMPRODUCT(($E$6:$E$16=B22)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B22)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G22" s="21">
-        <f>F22*E22</f>
-        <v/>
-      </c>
-      <c r="H22" s="21">
-        <f>E22*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I22" s="21">
-        <f>(E22*0.95)-G22</f>
-        <v/>
-      </c>
-      <c r="J22" s="21">
-        <f>(E22*0.925)-G22</f>
-        <v/>
-      </c>
-      <c r="K22" s="21">
-        <f>(E22*0.90)-G22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>Q3 2027</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20">
-        <f>COUNTIF($E$6:$E$16,B23)</f>
-        <v/>
-      </c>
-      <c r="E23" s="21">
-        <f>SUMIF($E$6:$E$16,B23,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F23" s="22">
-        <f t="array" ref="F23">IFERROR(SUMPRODUCT(($E$6:$E$16=B23)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B23)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G23" s="21">
-        <f>F23*E23</f>
-        <v/>
-      </c>
-      <c r="H23" s="21">
-        <f>E23*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I23" s="21">
-        <f>(E23*0.95)-G23</f>
-        <v/>
-      </c>
-      <c r="J23" s="21">
-        <f>(E23*0.925)-G23</f>
-        <v/>
-      </c>
-      <c r="K23" s="21">
-        <f>(E23*0.90)-G23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20">
-        <f>COUNTIF($E$6:$E$16,B24)</f>
-        <v/>
-      </c>
-      <c r="E24" s="21">
-        <f>SUMIF($E$6:$E$16,B24,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F24" s="22">
-        <f t="array" ref="F24">IFERROR(SUMPRODUCT(($E$6:$E$16=B24)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B24)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="21">
-        <f>F24*E24</f>
-        <v/>
-      </c>
-      <c r="H24" s="21">
-        <f>E24*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I24" s="21">
-        <f>(E24*0.95)-G24</f>
-        <v/>
-      </c>
-      <c r="J24" s="21">
-        <f>(E24*0.925)-G24</f>
-        <v/>
-      </c>
-      <c r="K24" s="21">
-        <f>(E24*0.90)-G24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>Q1 2027</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20">
-        <f>COUNTIF($E$6:$E$16,B25)</f>
-        <v/>
-      </c>
-      <c r="E25" s="21">
-        <f>SUMIF($E$6:$E$16,B25,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F25" s="22">
-        <f t="array" ref="F25">IFERROR(SUMPRODUCT(($E$6:$E$16=B25)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B25)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G25" s="21">
-        <f>F25*E25</f>
-        <v/>
-      </c>
-      <c r="H25" s="21">
-        <f>E25*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I25" s="21">
-        <f>(E25*0.95)-G25</f>
-        <v/>
-      </c>
-      <c r="J25" s="21">
-        <f>(E25*0.925)-G25</f>
-        <v/>
-      </c>
-      <c r="K25" s="21">
-        <f>(E25*0.90)-G25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20">
-        <f>COUNTIF($E$6:$E$16,B26)</f>
-        <v/>
-      </c>
-      <c r="E26" s="21">
-        <f>SUMIF($E$6:$E$16,B26,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F26" s="22">
-        <f t="array" ref="F26">IFERROR(SUMPRODUCT(($E$6:$E$16=B26)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B26)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G26" s="21">
-        <f>F26*E26</f>
-        <v/>
-      </c>
-      <c r="H26" s="21">
-        <f>E26*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I26" s="21">
-        <f>(E26*0.95)-G26</f>
-        <v/>
-      </c>
-      <c r="J26" s="21">
-        <f>(E26*0.925)-G26</f>
-        <v/>
-      </c>
-      <c r="K26" s="21">
-        <f>(E26*0.90)-G26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>Q3 2026</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20">
-        <f>COUNTIF($E$6:$E$16,B27)</f>
-        <v/>
-      </c>
-      <c r="E27" s="21">
-        <f>SUMIF($E$6:$E$16,B27,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F27" s="22">
-        <f t="array" ref="F27">IFERROR(SUMPRODUCT(($E$6:$E$16=B27)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B27)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G27" s="21">
-        <f>F27*E27</f>
-        <v/>
-      </c>
-      <c r="H27" s="21">
-        <f>E27*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I27" s="21">
-        <f>(E27*0.95)-G27</f>
-        <v/>
-      </c>
-      <c r="J27" s="21">
-        <f>(E27*0.925)-G27</f>
-        <v/>
-      </c>
-      <c r="K27" s="21">
-        <f>(E27*0.90)-G27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20">
-        <f>COUNTIF($E$6:$E$16,B28)</f>
-        <v/>
-      </c>
-      <c r="E28" s="21">
-        <f>SUMIF($E$6:$E$16,B28,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F28" s="22">
-        <f t="array" ref="F28">IFERROR(SUMPRODUCT(($E$6:$E$16=B28)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B28)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G28" s="21">
-        <f>F28*E28</f>
-        <v/>
-      </c>
-      <c r="H28" s="21">
-        <f>E28*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I28" s="21">
-        <f>(E28*0.95)-G28</f>
-        <v/>
-      </c>
-      <c r="J28" s="21">
-        <f>(E28*0.925)-G28</f>
-        <v/>
-      </c>
-      <c r="K28" s="21">
-        <f>(E28*0.90)-G28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>Q1 2026</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20">
-        <f>COUNTIF($E$6:$E$16,B29)</f>
-        <v/>
-      </c>
-      <c r="E29" s="21">
-        <f>SUMIF($E$6:$E$16,B29,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F29" s="22">
-        <f t="array" ref="F29">IFERROR(SUMPRODUCT(($E$6:$E$16=B29)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B29)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G29" s="21">
-        <f>F29*E29</f>
-        <v/>
-      </c>
-      <c r="H29" s="21">
-        <f>E29*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I29" s="21">
-        <f>(E29*0.95)-G29</f>
-        <v/>
-      </c>
-      <c r="J29" s="21">
-        <f>(E29*0.925)-G29</f>
-        <v/>
-      </c>
-      <c r="K29" s="21">
-        <f>(E29*0.90)-G29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>Q4 2025</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20">
-        <f>COUNTIF($E$6:$E$16,B30)</f>
-        <v/>
-      </c>
-      <c r="E30" s="21">
-        <f>SUMIF($E$6:$E$16,B30,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F30" s="22">
-        <f t="array" ref="F30">IFERROR(SUMPRODUCT(($E$6:$E$16=B30)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B30)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G30" s="21">
-        <f>F30*E30</f>
-        <v/>
-      </c>
-      <c r="H30" s="21">
-        <f>E30*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I30" s="21">
-        <f>(E30*0.95)-G30</f>
-        <v/>
-      </c>
-      <c r="J30" s="21">
-        <f>(E30*0.925)-G30</f>
-        <v/>
-      </c>
-      <c r="K30" s="21">
-        <f>(E30*0.90)-G30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>Q3 2025</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20">
-        <f>COUNTIF($E$6:$E$16,B31)</f>
-        <v/>
-      </c>
-      <c r="E31" s="21">
-        <f>SUMIF($E$6:$E$16,B31,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F31" s="22">
-        <f t="array" ref="F31">IFERROR(SUMPRODUCT(($E$6:$E$16=B31)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B31)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G31" s="21">
-        <f>F31*E31</f>
-        <v/>
-      </c>
-      <c r="H31" s="21">
-        <f>E31*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I31" s="21">
-        <f>(E31*0.95)-G31</f>
-        <v/>
-      </c>
-      <c r="J31" s="21">
-        <f>(E31*0.925)-G31</f>
-        <v/>
-      </c>
-      <c r="K31" s="21">
-        <f>(E31*0.90)-G31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>Q2 2025</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="n"/>
-      <c r="D32" s="20">
-        <f>COUNTIF($E$6:$E$16,B32)</f>
-        <v/>
-      </c>
-      <c r="E32" s="21">
-        <f>SUMIF($E$6:$E$16,B32,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F32" s="22">
-        <f t="array" ref="F32">IFERROR(SUMPRODUCT(($E$6:$E$16=B32)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B32)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G32" s="21">
-        <f>F32*E32</f>
-        <v/>
-      </c>
-      <c r="H32" s="21">
-        <f>E32*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I32" s="21">
-        <f>(E32*0.95)-G32</f>
-        <v/>
-      </c>
-      <c r="J32" s="21">
-        <f>(E32*0.925)-G32</f>
-        <v/>
-      </c>
-      <c r="K32" s="21">
-        <f>(E32*0.90)-G32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>Q1 2025</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="n"/>
-      <c r="D33" s="20">
-        <f>COUNTIF($E$6:$E$16,B33)</f>
-        <v/>
-      </c>
-      <c r="E33" s="21">
-        <f>SUMIF($E$6:$E$16,B33,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F33" s="22">
-        <f t="array" ref="F33">IFERROR(SUMPRODUCT(($E$6:$E$16=B33)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B33)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G33" s="21">
-        <f>F33*E33</f>
-        <v/>
-      </c>
-      <c r="H33" s="21">
-        <f>E33*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I33" s="21">
-        <f>(E33*0.95)-G33</f>
-        <v/>
-      </c>
-      <c r="J33" s="21">
-        <f>(E33*0.925)-G33</f>
-        <v/>
-      </c>
-      <c r="K33" s="21">
-        <f>(E33*0.90)-G33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>Q4 2024</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="n"/>
-      <c r="D34" s="20">
-        <f>COUNTIF($E$6:$E$16,B34)</f>
-        <v/>
-      </c>
-      <c r="E34" s="21">
-        <f>SUMIF($E$6:$E$16,B34,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F34" s="22">
-        <f t="array" ref="F34">IFERROR(SUMPRODUCT(($E$6:$E$16=B34)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B34)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G34" s="21">
-        <f>F34*E34</f>
-        <v/>
-      </c>
-      <c r="H34" s="21">
-        <f>E34*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I34" s="21">
-        <f>(E34*0.95)-G34</f>
-        <v/>
-      </c>
-      <c r="J34" s="21">
-        <f>(E34*0.925)-G34</f>
-        <v/>
-      </c>
-      <c r="K34" s="21">
-        <f>(E34*0.90)-G34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>Q3 2024</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="n"/>
-      <c r="D35" s="20">
-        <f>COUNTIF($E$6:$E$16,B35)</f>
-        <v/>
-      </c>
-      <c r="E35" s="21">
-        <f>SUMIF($E$6:$E$16,B35,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F35" s="22">
-        <f t="array" ref="F35">IFERROR(SUMPRODUCT(($E$6:$E$16=B35)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B35)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G35" s="21">
-        <f>F35*E35</f>
-        <v/>
-      </c>
-      <c r="H35" s="21">
-        <f>E35*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I35" s="21">
-        <f>(E35*0.95)-G35</f>
-        <v/>
-      </c>
-      <c r="J35" s="21">
-        <f>(E35*0.925)-G35</f>
-        <v/>
-      </c>
-      <c r="K35" s="21">
-        <f>(E35*0.90)-G35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>Q2 2024</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="n"/>
-      <c r="D36" s="20">
-        <f>COUNTIF($E$6:$E$16,B36)</f>
-        <v/>
-      </c>
-      <c r="E36" s="21">
-        <f>SUMIF($E$6:$E$16,B36,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F36" s="22">
-        <f t="array" ref="F36">IFERROR(SUMPRODUCT(($E$6:$E$16=B36)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B36)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G36" s="21">
-        <f>F36*E36</f>
-        <v/>
-      </c>
-      <c r="H36" s="21">
-        <f>E36*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I36" s="21">
-        <f>(E36*0.95)-G36</f>
-        <v/>
-      </c>
-      <c r="J36" s="21">
-        <f>(E36*0.925)-G36</f>
-        <v/>
-      </c>
-      <c r="K36" s="21">
-        <f>(E36*0.90)-G36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>Q1 2024</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="n"/>
-      <c r="D37" s="20">
-        <f>COUNTIF($E$6:$E$16,B37)</f>
-        <v/>
-      </c>
-      <c r="E37" s="21">
-        <f>SUMIF($E$6:$E$16,B37,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F37" s="22">
-        <f t="array" ref="F37">IFERROR(SUMPRODUCT(($E$6:$E$16=B37)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B37)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G37" s="21">
-        <f>F37*E37</f>
-        <v/>
-      </c>
-      <c r="H37" s="21">
-        <f>E37*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I37" s="21">
-        <f>(E37*0.95)-G37</f>
-        <v/>
-      </c>
-      <c r="J37" s="21">
-        <f>(E37*0.925)-G37</f>
-        <v/>
-      </c>
-      <c r="K37" s="21">
-        <f>(E37*0.90)-G37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>Q4 2023</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="n"/>
-      <c r="D38" s="20">
-        <f>COUNTIF($E$6:$E$16,B38)</f>
-        <v/>
-      </c>
-      <c r="E38" s="21">
-        <f>SUMIF($E$6:$E$16,B38,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F38" s="22">
-        <f t="array" ref="F38">IFERROR(SUMPRODUCT(($E$6:$E$16=B38)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B38)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G38" s="21">
-        <f>F38*E38</f>
-        <v/>
-      </c>
-      <c r="H38" s="21">
-        <f>E38*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I38" s="21">
-        <f>(E38*0.95)-G38</f>
-        <v/>
-      </c>
-      <c r="J38" s="21">
-        <f>(E38*0.925)-G38</f>
-        <v/>
-      </c>
-      <c r="K38" s="21">
-        <f>(E38*0.90)-G38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>Q3 2023</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20">
-        <f>COUNTIF($E$6:$E$16,B39)</f>
-        <v/>
-      </c>
-      <c r="E39" s="21">
-        <f>SUMIF($E$6:$E$16,B39,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F39" s="22">
-        <f t="array" ref="F39">IFERROR(SUMPRODUCT(($E$6:$E$16=B39)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B39)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G39" s="21">
-        <f>F39*E39</f>
-        <v/>
-      </c>
-      <c r="H39" s="21">
-        <f>E39*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I39" s="21">
-        <f>(E39*0.95)-G39</f>
-        <v/>
-      </c>
-      <c r="J39" s="21">
-        <f>(E39*0.925)-G39</f>
-        <v/>
-      </c>
-      <c r="K39" s="21">
-        <f>(E39*0.90)-G39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>Q2 2023</t>
-        </is>
-      </c>
-      <c r="C40" s="20" t="n"/>
-      <c r="D40" s="20">
-        <f>COUNTIF($E$6:$E$16,B40)</f>
-        <v/>
-      </c>
-      <c r="E40" s="21">
-        <f>SUMIF($E$6:$E$16,B40,$D$6:$D$16)</f>
-        <v/>
-      </c>
-      <c r="F40" s="22">
-        <f t="array" ref="F40">IFERROR(SUMPRODUCT(($E$6:$E$16=B40)*IFERROR($D$6:$D$16*$F$6:$F$16,0))/SUMPRODUCT(($E$6:$E$16=B40)*ISNUMBER($F$6:$F$16)*$D$6:$D$16),0)</f>
-        <v/>
-      </c>
-      <c r="G40" s="21">
-        <f>F40*E40</f>
-        <v/>
-      </c>
-      <c r="H40" s="21">
-        <f>E40*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I40" s="21">
-        <f>(E40*0.95)-G40</f>
-        <v/>
-      </c>
-      <c r="J40" s="21">
-        <f>(E40*0.925)-G40</f>
-        <v/>
-      </c>
-      <c r="K40" s="21">
-        <f>(E40*0.90)-G40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4">
-        <f>SUM(D20:D40)</f>
-        <v/>
-      </c>
-      <c r="E41" s="24">
-        <f>SUM(E20:E40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="25">
-        <f>IFERROR(SUMPRODUCT($E$20:$E$40,F20:F40)/$E$41,0)</f>
-        <v/>
-      </c>
-      <c r="G41" s="24">
-        <f>SUM(G20:G40)</f>
-        <v/>
-      </c>
-      <c r="H41" s="24">
-        <f>SUM(H20:H40)</f>
-        <v/>
-      </c>
-      <c r="I41" s="24">
-        <f>SUM(I20:I40)</f>
-        <v/>
-      </c>
-      <c r="J41" s="24">
-        <f>SUM(J20:J40)</f>
-        <v/>
-      </c>
-      <c r="K41" s="24">
-        <f>SUM(K20:K40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="G43" s="26" t="inlineStr">
-        <is>
-          <t>Total Current Inventory</t>
-        </is>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>5925</v>
-      </c>
-      <c r="J43" s="28">
-        <f>I43</f>
-        <v/>
-      </c>
-      <c r="K43" s="28">
-        <f>I43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="G44" s="26" t="inlineStr">
-        <is>
-          <t>% to be Absorbed</t>
-        </is>
-      </c>
-      <c r="I44" s="29">
-        <f>IFERROR(I41/I43,0)</f>
-        <v/>
-      </c>
-      <c r="J44" s="29">
-        <f>IFERROR(J41/J43,0)</f>
-        <v/>
-      </c>
-      <c r="K44" s="29">
-        <f>IFERROR(K41/K43,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="30" t="inlineStr">
-        <is>
-          <t>* 5-Mile radius. Total inventory from CoStar Data Analytics. Proximity (mi) to be filled manually. Lease-up rent/occupancy should be verified with a HelloData pull.</t>
+          <t>* 5-Mile radius. Rent ($) = market asking. Proximity (mi) to be filled manually; lease-up rent/occupancy to be verified w/ HelloData. See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="G43:H43"/>
+  <mergeCells count="5">
     <mergeCell ref="C10:K10"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C2:G2"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B46:K46"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B19:K19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2079,7 +1114,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>ANALYSIS SETTINGS</t>
         </is>
@@ -2091,7 +1126,7 @@
           <t>Stabilized Occupancy Target</t>
         </is>
       </c>
-      <c r="B2" s="32" t="n">
+      <c r="B2" s="21" t="n">
         <v>0.95</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -2129,62 +1164,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="E1" s="26" t="inlineStr">
+      <c r="E1" s="22" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="F1" s="26" t="inlineStr">
+      <c r="F1" s="22" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="G1" s="26" t="inlineStr">
+      <c r="G1" s="22" t="inlineStr">
         <is>
           <t>CoStar Occ</t>
         </is>
       </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="H1" s="22" t="inlineStr">
         <is>
           <t>RealPage Occ</t>
         </is>
       </c>
-      <c r="I1" s="26" t="inlineStr">
+      <c r="I1" s="22" t="inlineStr">
         <is>
           <t>CoStar Ask Rent</t>
         </is>
       </c>
-      <c r="J1" s="26" t="inlineStr">
+      <c r="J1" s="22" t="inlineStr">
         <is>
           <t>RealPage Eff Rent</t>
         </is>
       </c>
-      <c r="K1" s="26" t="inlineStr">
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="L1" s="26" t="inlineStr">
+      <c r="L1" s="22" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2217,16 +1252,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G2" s="33" t="n">
+      <c r="G2" s="23" t="n">
         <v>0.92</v>
       </c>
-      <c r="H2" s="33" t="n">
+      <c r="H2" s="23" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="I2" s="28" t="n">
+      <c r="I2" s="24" t="n">
         <v>2104</v>
       </c>
-      <c r="J2" s="28" t="n">
+      <c r="J2" s="24" t="n">
         <v>2150</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -2263,12 +1298,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G3" s="33" t="n"/>
-      <c r="H3" s="33" t="n">
+      <c r="G3" s="23" t="n"/>
+      <c r="H3" s="23" t="n">
         <v>0.961</v>
       </c>
-      <c r="I3" s="28" t="n"/>
-      <c r="J3" s="28" t="n">
+      <c r="I3" s="24" t="n"/>
+      <c r="J3" s="24" t="n">
         <v>1273</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -2309,16 +1344,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G4" s="33" t="n">
+      <c r="G4" s="23" t="n">
         <v>0.967153</v>
       </c>
-      <c r="H4" s="33" t="n">
+      <c r="H4" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="28" t="n">
+      <c r="I4" s="24" t="n">
         <v>2196</v>
       </c>
-      <c r="J4" s="28" t="n">
+      <c r="J4" s="24" t="n">
         <v>2311</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -2356,10 +1391,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G5" s="33" t="n"/>
-      <c r="H5" s="33" t="n"/>
-      <c r="I5" s="28" t="n"/>
-      <c r="J5" s="28" t="n"/>
+      <c r="G5" s="23" t="n"/>
+      <c r="H5" s="23" t="n"/>
+      <c r="I5" s="24" t="n"/>
+      <c r="J5" s="24" t="n"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2395,10 +1430,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G6" s="33" t="n"/>
-      <c r="H6" s="33" t="n"/>
-      <c r="I6" s="28" t="n"/>
-      <c r="J6" s="28" t="n"/>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="24" t="n"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2434,10 +1469,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G7" s="33" t="n"/>
-      <c r="H7" s="33" t="n"/>
-      <c r="I7" s="28" t="n"/>
-      <c r="J7" s="28" t="n"/>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="24" t="n"/>
+      <c r="J7" s="24" t="n"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2473,10 +1508,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G8" s="33" t="n"/>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="28" t="n"/>
-      <c r="J8" s="28" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="24" t="n"/>
+      <c r="J8" s="24" t="n"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2512,10 +1547,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G9" s="33" t="n"/>
-      <c r="H9" s="33" t="n"/>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="28" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="24" t="n"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2551,10 +1586,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G10" s="33" t="n"/>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="28" t="n"/>
-      <c r="J10" s="28" t="n"/>
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="24" t="n"/>
+      <c r="J10" s="24" t="n"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2569,4 +1604,1418 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:M51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="22" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY &amp; ABSORPTION FORECAST — 5-MILE MARKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>Stabilization Target</t>
+        </is>
+      </c>
+      <c r="C3" s="26">
+        <f>Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="J3" s="22" t="inlineStr">
+        <is>
+          <t>PIPELINE INPUTS  (forward new supply — edit date / include)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Demand Scenario (Bear/Base/Bull)</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J4" s="29" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="L4" s="29" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="M4" s="29" t="inlineStr">
+        <is>
+          <t>Include?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Hist. Avg Annual Absorption (CoStar)</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>Vista Point</t>
+        </is>
+      </c>
+      <c r="K5" s="32" t="n">
+        <v>893</v>
+      </c>
+      <c r="L5" s="33" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
+      </c>
+      <c r="M5" s="33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Bear — Annual Absorption (units)</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>150</v>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>Seasons on the Bench</t>
+        </is>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>358</v>
+      </c>
+      <c r="L6" s="33" t="inlineStr">
+        <is>
+          <t>Q4 2027</t>
+        </is>
+      </c>
+      <c r="M6" s="33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Base — Annual Absorption (units)</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>1519 South Londoner Avenue</t>
+        </is>
+      </c>
+      <c r="K7" s="32" t="n">
+        <v>189</v>
+      </c>
+      <c r="L7" s="33" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="M7" s="33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Bull — Annual Absorption (units)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>450</v>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>3300 South Vista Avenue</t>
+        </is>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>180</v>
+      </c>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="M8" s="33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Selected Annual Demand</t>
+        </is>
+      </c>
+      <c r="C9" s="30">
+        <f>IF($C$4="Bear",$C$6,IF($C$4="Bull",$C$8,$C$7))</f>
+        <v/>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>Station Village</t>
+        </is>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>84</v>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="M9" s="33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Selected Quarterly Demand</t>
+        </is>
+      </c>
+      <c r="C10" s="30">
+        <f>$C$9/4</f>
+        <v/>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>Harris Ranch East</t>
+        </is>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="M10" s="33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>New Supply</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Absorption</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Overall Occ</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Q3 2023</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="35" t="n">
+        <v>-43</v>
+      </c>
+      <c r="E14" s="35" t="n">
+        <v>4793</v>
+      </c>
+      <c r="F14" s="35" t="n">
+        <v>5411</v>
+      </c>
+      <c r="G14" s="36">
+        <f>IFERROR(E14/F14,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Q4 2023</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="n">
+        <v>46</v>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>51</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>4844</v>
+      </c>
+      <c r="F15" s="35" t="n">
+        <v>5457</v>
+      </c>
+      <c r="G15" s="36">
+        <f>IFERROR(E15/F15,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>Q1 2024</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="35" t="n">
+        <v>96</v>
+      </c>
+      <c r="E16" s="35" t="n">
+        <v>4940</v>
+      </c>
+      <c r="F16" s="35" t="n">
+        <v>5457</v>
+      </c>
+      <c r="G16" s="36">
+        <f>IFERROR(E16/F16,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>Q2 2024</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="n">
+        <v>125</v>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>173</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>5113</v>
+      </c>
+      <c r="F17" s="35" t="n">
+        <v>5582</v>
+      </c>
+      <c r="G17" s="36">
+        <f>IFERROR(E17/F17,0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>Q3 2024</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="n">
+        <v>299</v>
+      </c>
+      <c r="D18" s="35" t="n">
+        <v>140</v>
+      </c>
+      <c r="E18" s="35" t="n">
+        <v>5253</v>
+      </c>
+      <c r="F18" s="35" t="n">
+        <v>5881</v>
+      </c>
+      <c r="G18" s="36">
+        <f>IFERROR(E18/F18,0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="D19" s="35" t="n">
+        <v>56</v>
+      </c>
+      <c r="E19" s="35" t="n">
+        <v>5309</v>
+      </c>
+      <c r="F19" s="35" t="n">
+        <v>5916</v>
+      </c>
+      <c r="G19" s="36">
+        <f>IFERROR(E19/F19,0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="35" t="n">
+        <v>87</v>
+      </c>
+      <c r="E20" s="35" t="n">
+        <v>5396</v>
+      </c>
+      <c r="F20" s="35" t="n">
+        <v>5916</v>
+      </c>
+      <c r="G20" s="36">
+        <f>IFERROR(E20/F20,0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>116</v>
+      </c>
+      <c r="E21" s="35" t="n">
+        <v>5512</v>
+      </c>
+      <c r="F21" s="35" t="n">
+        <v>5916</v>
+      </c>
+      <c r="G21" s="36">
+        <f>IFERROR(E21/F21,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="E22" s="35" t="n">
+        <v>5542</v>
+      </c>
+      <c r="F22" s="35" t="n">
+        <v>5916</v>
+      </c>
+      <c r="G22" s="36">
+        <f>IFERROR(E22/F22,0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="35" t="n">
+        <v>45</v>
+      </c>
+      <c r="E23" s="35" t="n">
+        <v>5587</v>
+      </c>
+      <c r="F23" s="35" t="n">
+        <v>5916</v>
+      </c>
+      <c r="G23" s="36">
+        <f>IFERROR(E23/F23,0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="35" t="n">
+        <v>109</v>
+      </c>
+      <c r="E24" s="35" t="n">
+        <v>5695</v>
+      </c>
+      <c r="F24" s="35" t="n">
+        <v>5916</v>
+      </c>
+      <c r="G24" s="36">
+        <f>IFERROR(E24/F24,0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="E25" s="35" t="n">
+        <v>5727</v>
+      </c>
+      <c r="F25" s="35" t="n">
+        <v>5925</v>
+      </c>
+      <c r="G25" s="36">
+        <f>IFERROR(E25/F25,0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="34" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="C26" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B26,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D26" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F26-E25))</f>
+        <v/>
+      </c>
+      <c r="E26" s="38">
+        <f>E25+D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="38">
+        <f>F25+C26</f>
+        <v/>
+      </c>
+      <c r="G26" s="39">
+        <f>IFERROR(E26/F26,0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="37" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="C27" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B27,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D27" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F27-E26))</f>
+        <v/>
+      </c>
+      <c r="E27" s="38">
+        <f>E26+D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="38">
+        <f>F26+C27</f>
+        <v/>
+      </c>
+      <c r="G27" s="39">
+        <f>IFERROR(E27/F27,0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>Q1 2027</t>
+        </is>
+      </c>
+      <c r="C28" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B28,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D28" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F28-E27))</f>
+        <v/>
+      </c>
+      <c r="E28" s="38">
+        <f>E27+D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="38">
+        <f>F27+C28</f>
+        <v/>
+      </c>
+      <c r="G28" s="39">
+        <f>IFERROR(E28/F28,0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="37" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="C29" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B29,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D29" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F29-E28))</f>
+        <v/>
+      </c>
+      <c r="E29" s="38">
+        <f>E28+D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="38">
+        <f>F28+C29</f>
+        <v/>
+      </c>
+      <c r="G29" s="39">
+        <f>IFERROR(E29/F29,0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="C30" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B30,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D30" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F30-E29))</f>
+        <v/>
+      </c>
+      <c r="E30" s="38">
+        <f>E29+D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="38">
+        <f>F29+C30</f>
+        <v/>
+      </c>
+      <c r="G30" s="39">
+        <f>IFERROR(E30/F30,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="37" t="inlineStr">
+        <is>
+          <t>Q4 2027</t>
+        </is>
+      </c>
+      <c r="C31" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B31,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D31" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F31-E30))</f>
+        <v/>
+      </c>
+      <c r="E31" s="38">
+        <f>E30+D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="38">
+        <f>F30+C31</f>
+        <v/>
+      </c>
+      <c r="G31" s="39">
+        <f>IFERROR(E31/F31,0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="37" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="C32" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B32,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D32" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F32-E31))</f>
+        <v/>
+      </c>
+      <c r="E32" s="38">
+        <f>E31+D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="38">
+        <f>F31+C32</f>
+        <v/>
+      </c>
+      <c r="G32" s="39">
+        <f>IFERROR(E32/F32,0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="37" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
+      </c>
+      <c r="C33" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B33,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D33" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F33-E32))</f>
+        <v/>
+      </c>
+      <c r="E33" s="38">
+        <f>E32+D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="38">
+        <f>F32+C33</f>
+        <v/>
+      </c>
+      <c r="G33" s="39">
+        <f>IFERROR(E33/F33,0)</f>
+        <v/>
+      </c>
+      <c r="H33" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="37" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="C34" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B34,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D34" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F34-E33))</f>
+        <v/>
+      </c>
+      <c r="E34" s="38">
+        <f>E33+D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="38">
+        <f>F33+C34</f>
+        <v/>
+      </c>
+      <c r="G34" s="39">
+        <f>IFERROR(E34/F34,0)</f>
+        <v/>
+      </c>
+      <c r="H34" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Q4 2028</t>
+        </is>
+      </c>
+      <c r="C35" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B35,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D35" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F35-E34))</f>
+        <v/>
+      </c>
+      <c r="E35" s="38">
+        <f>E34+D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="38">
+        <f>F34+C35</f>
+        <v/>
+      </c>
+      <c r="G35" s="39">
+        <f>IFERROR(E35/F35,0)</f>
+        <v/>
+      </c>
+      <c r="H35" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
+      <c r="C36" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B36,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D36" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F36-E35))</f>
+        <v/>
+      </c>
+      <c r="E36" s="38">
+        <f>E35+D36</f>
+        <v/>
+      </c>
+      <c r="F36" s="38">
+        <f>F35+C36</f>
+        <v/>
+      </c>
+      <c r="G36" s="39">
+        <f>IFERROR(E36/F36,0)</f>
+        <v/>
+      </c>
+      <c r="H36" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="37" t="inlineStr">
+        <is>
+          <t>Q2 2029</t>
+        </is>
+      </c>
+      <c r="C37" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B37,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D37" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F37-E36))</f>
+        <v/>
+      </c>
+      <c r="E37" s="38">
+        <f>E36+D37</f>
+        <v/>
+      </c>
+      <c r="F37" s="38">
+        <f>F36+C37</f>
+        <v/>
+      </c>
+      <c r="G37" s="39">
+        <f>IFERROR(E37/F37,0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>Q3 2029</t>
+        </is>
+      </c>
+      <c r="C38" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B38,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D38" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F38-E37))</f>
+        <v/>
+      </c>
+      <c r="E38" s="38">
+        <f>E37+D38</f>
+        <v/>
+      </c>
+      <c r="F38" s="38">
+        <f>F37+C38</f>
+        <v/>
+      </c>
+      <c r="G38" s="39">
+        <f>IFERROR(E38/F38,0)</f>
+        <v/>
+      </c>
+      <c r="H38" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>Q4 2029</t>
+        </is>
+      </c>
+      <c r="C39" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B39,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D39" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F39-E38))</f>
+        <v/>
+      </c>
+      <c r="E39" s="38">
+        <f>E38+D39</f>
+        <v/>
+      </c>
+      <c r="F39" s="38">
+        <f>F38+C39</f>
+        <v/>
+      </c>
+      <c r="G39" s="39">
+        <f>IFERROR(E39/F39,0)</f>
+        <v/>
+      </c>
+      <c r="H39" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>Q1 2030</t>
+        </is>
+      </c>
+      <c r="C40" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B40,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D40" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F40-E39))</f>
+        <v/>
+      </c>
+      <c r="E40" s="38">
+        <f>E39+D40</f>
+        <v/>
+      </c>
+      <c r="F40" s="38">
+        <f>F39+C40</f>
+        <v/>
+      </c>
+      <c r="G40" s="39">
+        <f>IFERROR(E40/F40,0)</f>
+        <v/>
+      </c>
+      <c r="H40" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>Q2 2030</t>
+        </is>
+      </c>
+      <c r="C41" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B41,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D41" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F41-E40))</f>
+        <v/>
+      </c>
+      <c r="E41" s="38">
+        <f>E40+D41</f>
+        <v/>
+      </c>
+      <c r="F41" s="38">
+        <f>F40+C41</f>
+        <v/>
+      </c>
+      <c r="G41" s="39">
+        <f>IFERROR(E41/F41,0)</f>
+        <v/>
+      </c>
+      <c r="H41" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>Q3 2030</t>
+        </is>
+      </c>
+      <c r="C42" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B42,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D42" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F42-E41))</f>
+        <v/>
+      </c>
+      <c r="E42" s="38">
+        <f>E41+D42</f>
+        <v/>
+      </c>
+      <c r="F42" s="38">
+        <f>F41+C42</f>
+        <v/>
+      </c>
+      <c r="G42" s="39">
+        <f>IFERROR(E42/F42,0)</f>
+        <v/>
+      </c>
+      <c r="H42" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>Q4 2030</t>
+        </is>
+      </c>
+      <c r="C43" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B43,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D43" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F43-E42))</f>
+        <v/>
+      </c>
+      <c r="E43" s="38">
+        <f>E42+D43</f>
+        <v/>
+      </c>
+      <c r="F43" s="38">
+        <f>F42+C43</f>
+        <v/>
+      </c>
+      <c r="G43" s="39">
+        <f>IFERROR(E43/F43,0)</f>
+        <v/>
+      </c>
+      <c r="H43" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>Q1 2031</t>
+        </is>
+      </c>
+      <c r="C44" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B44,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D44" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F44-E43))</f>
+        <v/>
+      </c>
+      <c r="E44" s="38">
+        <f>E43+D44</f>
+        <v/>
+      </c>
+      <c r="F44" s="38">
+        <f>F43+C44</f>
+        <v/>
+      </c>
+      <c r="G44" s="39">
+        <f>IFERROR(E44/F44,0)</f>
+        <v/>
+      </c>
+      <c r="H44" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>Q2 2031</t>
+        </is>
+      </c>
+      <c r="C45" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B45,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D45" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F45-E44))</f>
+        <v/>
+      </c>
+      <c r="E45" s="38">
+        <f>E44+D45</f>
+        <v/>
+      </c>
+      <c r="F45" s="38">
+        <f>F44+C45</f>
+        <v/>
+      </c>
+      <c r="G45" s="39">
+        <f>IFERROR(E45/F45,0)</f>
+        <v/>
+      </c>
+      <c r="H45" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>Q3 2031</t>
+        </is>
+      </c>
+      <c r="C46" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B46,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D46" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F46-E45))</f>
+        <v/>
+      </c>
+      <c r="E46" s="38">
+        <f>E45+D46</f>
+        <v/>
+      </c>
+      <c r="F46" s="38">
+        <f>F45+C46</f>
+        <v/>
+      </c>
+      <c r="G46" s="39">
+        <f>IFERROR(E46/F46,0)</f>
+        <v/>
+      </c>
+      <c r="H46" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>Q4 2031</t>
+        </is>
+      </c>
+      <c r="C47" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B47,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D47" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F47-E46))</f>
+        <v/>
+      </c>
+      <c r="E47" s="38">
+        <f>E46+D47</f>
+        <v/>
+      </c>
+      <c r="F47" s="38">
+        <f>F46+C47</f>
+        <v/>
+      </c>
+      <c r="G47" s="39">
+        <f>IFERROR(E47/F47,0)</f>
+        <v/>
+      </c>
+      <c r="H47" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>Q1 2032</t>
+        </is>
+      </c>
+      <c r="C48" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B48,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D48" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F48-E47))</f>
+        <v/>
+      </c>
+      <c r="E48" s="38">
+        <f>E47+D48</f>
+        <v/>
+      </c>
+      <c r="F48" s="38">
+        <f>F47+C48</f>
+        <v/>
+      </c>
+      <c r="G48" s="39">
+        <f>IFERROR(E48/F48,0)</f>
+        <v/>
+      </c>
+      <c r="H48" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>Q2 2032</t>
+        </is>
+      </c>
+      <c r="C49" s="38">
+        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B49,$M$5:$M$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="D49" s="38">
+        <f>MIN($C$10,MAX(0,$C$3*F49-E48))</f>
+        <v/>
+      </c>
+      <c r="E49" s="38">
+        <f>E48+D49</f>
+        <v/>
+      </c>
+      <c r="F49" s="38">
+        <f>F48+C49</f>
+        <v/>
+      </c>
+      <c r="G49" s="39">
+        <f>IFERROR(E49/F49,0)</f>
+        <v/>
+      </c>
+      <c r="H49" s="37" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>Historical = CoStar 5-mi actuals. Forecast: inventory grows by scheduled pipeline deliveries (edit dates/include at right); absorption = min(quarterly demand, units to reach target); overall occ = occupied / inventory. Yellow cells are editable.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="J3:M3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Bear,Base,Bull"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M5 M6 M7 M8 M9 M10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +80,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -157,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,45 +223,67 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1612,1407 +1640,1243 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M51"/>
+  <dimension ref="B2:W45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="9.5" customWidth="1" min="7" max="7"/>
+    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9.5" customWidth="1" min="11" max="11"/>
+    <col width="9.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="9.5" customWidth="1" min="14" max="14"/>
+    <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>SUPPLY &amp; ABSORPTION FORECAST — 5-MILE MARKET</t>
+          <t>SUPPLY &amp; ABSORPTION  —  5-MILE MARKET (relative-year / TTM)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="25" t="inlineStr">
+      <c r="R3" s="25" t="inlineStr">
+        <is>
+          <t>PIPELINE INPUTS (forward new supply)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>As-of Quarter</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>8105</v>
+      </c>
+      <c r="R4" s="28" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="S4" s="28" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="T4" s="28" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="U4" s="28" t="inlineStr">
+        <is>
+          <t>Incl?</t>
+        </is>
+      </c>
+      <c r="V4" s="28" t="inlineStr">
+        <is>
+          <t>DelivIdx</t>
+        </is>
+      </c>
+      <c r="W4" s="28" t="inlineStr">
+        <is>
+          <t>HoldYr</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Close Quarter (Y1 start)</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="E5">
+        <f>IFERROR(VALUE(RIGHT($C$5,4))*4+MATCH(LEFT($C$5,2),{"Q1","Q2","Q3","Q4"},0)-1,0)</f>
+        <v/>
+      </c>
+      <c r="R5" s="30" t="inlineStr">
+        <is>
+          <t>Vista Point</t>
+        </is>
+      </c>
+      <c r="S5" s="31" t="n">
+        <v>893</v>
+      </c>
+      <c r="T5" s="32" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
+      </c>
+      <c r="U5" s="32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V5" s="33">
+        <f>IFERROR(VALUE(RIGHT(T5,4))*4+MATCH(LEFT(T5,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W5" s="33">
+        <f>IF(V5="","",IF(V5&lt;=$E$4,0,MAX(1,INT((V5-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Stabilization Target</t>
         </is>
       </c>
-      <c r="C3" s="26">
+      <c r="C6" s="34">
         <f>Settings!$B$2</f>
         <v/>
       </c>
-      <c r="J3" s="22" t="inlineStr">
-        <is>
-          <t>PIPELINE INPUTS  (forward new supply — edit date / include)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>Demand Scenario (Bear/Base/Bull)</t>
-        </is>
-      </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="R6" s="30" t="inlineStr">
+        <is>
+          <t>Seasons on the Bench</t>
+        </is>
+      </c>
+      <c r="S6" s="31" t="n">
+        <v>358</v>
+      </c>
+      <c r="T6" s="32" t="inlineStr">
+        <is>
+          <t>Q4 2027</t>
+        </is>
+      </c>
+      <c r="U6" s="32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V6" s="33">
+        <f>IFERROR(VALUE(RIGHT(T6,4))*4+MATCH(LEFT(T6,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W6" s="33">
+        <f>IF(V6="","",IF(V6&lt;=$E$4,0,MAX(1,INT((V6-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Demand Scenario</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J4" s="29" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="K4" s="29" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="L4" s="29" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="M4" s="29" t="inlineStr">
-        <is>
-          <t>Include?</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="25" t="inlineStr">
-        <is>
-          <t>Hist. Avg Annual Absorption (CoStar)</t>
-        </is>
-      </c>
-      <c r="C5" s="30" t="n">
+      <c r="R7" s="30" t="inlineStr">
+        <is>
+          <t>1519 South Londoner Avenue</t>
+        </is>
+      </c>
+      <c r="S7" s="31" t="n">
+        <v>189</v>
+      </c>
+      <c r="T7" s="32" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="U7" s="32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V7" s="33">
+        <f>IFERROR(VALUE(RIGHT(T7,4))*4+MATCH(LEFT(T7,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W7" s="33">
+        <f>IF(V7="","",IF(V7&lt;=$E$4,0,MAX(1,INT((V7-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Bear Annual Absorption</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>150</v>
+      </c>
+      <c r="R8" s="30" t="inlineStr">
+        <is>
+          <t>3300 South Vista Avenue</t>
+        </is>
+      </c>
+      <c r="S8" s="31" t="n">
+        <v>180</v>
+      </c>
+      <c r="T8" s="32" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="U8" s="32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V8" s="33">
+        <f>IFERROR(VALUE(RIGHT(T8,4))*4+MATCH(LEFT(T8,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W8" s="33">
+        <f>IF(V8="","",IF(V8&lt;=$E$4,0,MAX(1,INT((V8-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Base Annual Absorption</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="n">
         <v>300</v>
       </c>
-      <c r="J5" s="31" t="inlineStr">
-        <is>
-          <t>Vista Point</t>
-        </is>
-      </c>
-      <c r="K5" s="32" t="n">
-        <v>893</v>
-      </c>
-      <c r="L5" s="33" t="inlineStr">
-        <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="M5" s="33" t="inlineStr">
+      <c r="R9" s="30" t="inlineStr">
+        <is>
+          <t>Station Village</t>
+        </is>
+      </c>
+      <c r="S9" s="31" t="n">
+        <v>84</v>
+      </c>
+      <c r="T9" s="32" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="U9" s="32" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t>Bear — Annual Absorption (units)</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="n">
+      <c r="V9" s="33">
+        <f>IFERROR(VALUE(RIGHT(T9,4))*4+MATCH(LEFT(T9,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W9" s="33">
+        <f>IF(V9="","",IF(V9&lt;=$E$4,0,MAX(1,INT((V9-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Bull Annual Absorption</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="n">
+        <v>450</v>
+      </c>
+      <c r="R10" s="30" t="inlineStr">
+        <is>
+          <t>Harris Ranch East</t>
+        </is>
+      </c>
+      <c r="S10" s="31" t="n">
+        <v>59</v>
+      </c>
+      <c r="T10" s="32" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="U10" s="32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V10" s="33">
+        <f>IFERROR(VALUE(RIGHT(T10,4))*4+MATCH(LEFT(T10,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W10" s="33">
+        <f>IF(V10="","",IF(V10&lt;=$E$4,0,MAX(1,INT((V10-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Selected Annual Demand</t>
+        </is>
+      </c>
+      <c r="C11" s="36">
+        <f>IF($C$7="Bear",$C$8,IF($C$7="Bull",$C$10,$C$9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Occupied (as-of)</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>5727</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Inventory (as-of)</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>5925</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>5-MILE MARKET</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>-Y6</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>-Y5</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-Y4</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>-Y3</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>-Y2</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>-Y1</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Y0</t>
+        </is>
+      </c>
+      <c r="J17" s="37" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K17" s="37" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L17" s="37" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M17" s="37" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N17" s="37" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O17" s="37" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>Q3 2019–Q2 2020</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="inlineStr">
+        <is>
+          <t>Q3 2020–Q2 2021</t>
+        </is>
+      </c>
+      <c r="E18" s="38" t="inlineStr">
+        <is>
+          <t>Q3 2021–Q2 2022</t>
+        </is>
+      </c>
+      <c r="F18" s="38" t="inlineStr">
+        <is>
+          <t>Q3 2022–Q2 2023</t>
+        </is>
+      </c>
+      <c r="G18" s="38" t="inlineStr">
+        <is>
+          <t>Q3 2023–Q2 2024</t>
+        </is>
+      </c>
+      <c r="H18" s="38" t="inlineStr">
+        <is>
+          <t>Q3 2024–Q2 2025</t>
+        </is>
+      </c>
+      <c r="I18" s="38" t="inlineStr">
+        <is>
+          <t>Q3 2025–Q2 2026</t>
+        </is>
+      </c>
+      <c r="J18" s="38" t="inlineStr">
+        <is>
+          <t>Hold Yr 1</t>
+        </is>
+      </c>
+      <c r="K18" s="38" t="inlineStr">
+        <is>
+          <t>Hold Yr 2</t>
+        </is>
+      </c>
+      <c r="L18" s="38" t="inlineStr">
+        <is>
+          <t>Hold Yr 3</t>
+        </is>
+      </c>
+      <c r="M18" s="38" t="inlineStr">
+        <is>
+          <t>Hold Yr 4</t>
+        </is>
+      </c>
+      <c r="N18" s="38" t="inlineStr">
+        <is>
+          <t>Hold Yr 5</t>
+        </is>
+      </c>
+      <c r="O18" s="38" t="inlineStr">
+        <is>
+          <t>Hold Yr 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>NEW SUPPLY (5-mi)</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="n">
+        <v>213</v>
+      </c>
+      <c r="D19" s="39" t="n">
+        <v>237</v>
+      </c>
+      <c r="E19" s="39" t="n">
+        <v>33</v>
+      </c>
+      <c r="F19" s="39" t="n">
+        <v>289</v>
+      </c>
+      <c r="G19" s="39" t="n">
+        <v>178</v>
+      </c>
+      <c r="H19" s="39" t="n">
+        <v>334</v>
+      </c>
+      <c r="I19" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" s="40">
+        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,1,$U$5:$U$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="K19" s="40">
+        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,2,$U$5:$U$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="L19" s="40">
+        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,3,$U$5:$U$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="M19" s="40">
+        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,4,$U$5:$U$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="N19" s="40">
+        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,5,$U$5:$U$10,"Y")</f>
+        <v/>
+      </c>
+      <c r="O19" s="40">
+        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,6,$U$5:$U$10,"Y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>ABSORPTION (5-mi)</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="n">
+        <v>213</v>
+      </c>
+      <c r="D20" s="39" t="n">
         <v>150</v>
       </c>
-      <c r="J6" s="31" t="inlineStr">
-        <is>
-          <t>Seasons on the Bench</t>
-        </is>
-      </c>
-      <c r="K6" s="32" t="n">
-        <v>358</v>
-      </c>
-      <c r="L6" s="33" t="inlineStr">
-        <is>
-          <t>Q4 2027</t>
-        </is>
-      </c>
-      <c r="M6" s="33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>Base — Annual Absorption (units)</t>
-        </is>
-      </c>
-      <c r="C7" s="30" t="n">
-        <v>300</v>
-      </c>
-      <c r="J7" s="31" t="inlineStr">
-        <is>
-          <t>1519 South Londoner Avenue</t>
-        </is>
-      </c>
-      <c r="K7" s="32" t="n">
-        <v>189</v>
-      </c>
-      <c r="L7" s="33" t="inlineStr">
-        <is>
-          <t>Q3 2027</t>
-        </is>
-      </c>
-      <c r="M7" s="33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>Bull — Annual Absorption (units)</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="n">
-        <v>450</v>
-      </c>
-      <c r="J8" s="31" t="inlineStr">
-        <is>
-          <t>3300 South Vista Avenue</t>
-        </is>
-      </c>
-      <c r="K8" s="32" t="n">
-        <v>180</v>
-      </c>
-      <c r="L8" s="33" t="inlineStr">
-        <is>
-          <t>Q1 2028</t>
-        </is>
-      </c>
-      <c r="M8" s="33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>Selected Annual Demand</t>
-        </is>
-      </c>
-      <c r="C9" s="30">
-        <f>IF($C$4="Bear",$C$6,IF($C$4="Bull",$C$8,$C$7))</f>
-        <v/>
-      </c>
-      <c r="J9" s="31" t="inlineStr">
-        <is>
-          <t>Station Village</t>
-        </is>
-      </c>
-      <c r="K9" s="32" t="n">
-        <v>84</v>
-      </c>
-      <c r="L9" s="33" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="M9" s="33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>Selected Quarterly Demand</t>
-        </is>
-      </c>
-      <c r="C10" s="30">
-        <f>$C$9/4</f>
-        <v/>
-      </c>
-      <c r="J10" s="31" t="inlineStr">
-        <is>
-          <t>Harris Ranch East</t>
-        </is>
-      </c>
-      <c r="K10" s="32" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" s="33" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="M10" s="33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>New Supply</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Absorption</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Occupied</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Overall Occ</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>Q3 2023</t>
-        </is>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" s="35" t="n">
-        <v>-43</v>
-      </c>
-      <c r="E14" s="35" t="n">
-        <v>4793</v>
-      </c>
-      <c r="F14" s="35" t="n">
-        <v>5411</v>
-      </c>
-      <c r="G14" s="36">
-        <f>IFERROR(E14/F14,0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>Q4 2023</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>46</v>
-      </c>
-      <c r="D15" s="35" t="n">
-        <v>51</v>
-      </c>
-      <c r="E15" s="35" t="n">
-        <v>4844</v>
-      </c>
-      <c r="F15" s="35" t="n">
-        <v>5457</v>
-      </c>
-      <c r="G15" s="36">
-        <f>IFERROR(E15/F15,0)</f>
-        <v/>
-      </c>
-      <c r="H15" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>Q1 2024</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="n">
+      <c r="E20" s="39" t="n">
+        <v>86</v>
+      </c>
+      <c r="F20" s="39" t="n">
+        <v>-91</v>
+      </c>
+      <c r="G20" s="39" t="n">
+        <v>277</v>
+      </c>
+      <c r="H20" s="39" t="n">
+        <v>399</v>
+      </c>
+      <c r="I20" s="39" t="n">
+        <v>216</v>
+      </c>
+      <c r="J20" s="40">
+        <f>J25-I25</f>
+        <v/>
+      </c>
+      <c r="K20" s="40">
+        <f>K25-J25</f>
+        <v/>
+      </c>
+      <c r="L20" s="40">
+        <f>L25-K25</f>
+        <v/>
+      </c>
+      <c r="M20" s="40">
+        <f>M25-L25</f>
+        <v/>
+      </c>
+      <c r="N20" s="40">
+        <f>N25-M25</f>
+        <v/>
+      </c>
+      <c r="O20" s="40">
+        <f>O25-N25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>OCCUPANCY (5-mi)</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="D21" s="41" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="E21" s="41" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="F21" s="41" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="G21" s="41" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="H21" s="41" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="I21" s="41" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="J21" s="42">
+        <f>IFERROR(J25/J24,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="42">
+        <f>IFERROR(K25/K24,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="42">
+        <f>IFERROR(L25/L24,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="42">
+        <f>IFERROR(M25/M24,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="42">
+        <f>IFERROR(N25/N24,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="42">
+        <f>IFERROR(O25/O24,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>CUM. UNABSORBED (since -Y3)</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="n"/>
+      <c r="D22" s="43" t="n"/>
+      <c r="E22" s="43" t="n"/>
+      <c r="F22" s="43">
+        <f>F19-F20</f>
+        <v/>
+      </c>
+      <c r="G22" s="43">
+        <f>F22+G19-G20</f>
+        <v/>
+      </c>
+      <c r="H22" s="43">
+        <f>G22+H19-H20</f>
+        <v/>
+      </c>
+      <c r="I22" s="43">
+        <f>H22+I19-I20</f>
+        <v/>
+      </c>
+      <c r="J22" s="43">
+        <f>I22+J19-J20</f>
+        <v/>
+      </c>
+      <c r="K22" s="43">
+        <f>J22+K19-K20</f>
+        <v/>
+      </c>
+      <c r="L22" s="43">
+        <f>K22+L19-L20</f>
+        <v/>
+      </c>
+      <c r="M22" s="43">
+        <f>L22+M19-M20</f>
+        <v/>
+      </c>
+      <c r="N22" s="43">
+        <f>M22+N19-N20</f>
+        <v/>
+      </c>
+      <c r="O22" s="43">
+        <f>N22+O19-O20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" hidden="1">
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  inventory</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="n">
+        <v>4845</v>
+      </c>
+      <c r="D24" s="43" t="n">
+        <v>5082</v>
+      </c>
+      <c r="E24" s="43" t="n">
+        <v>5115</v>
+      </c>
+      <c r="F24" s="43" t="n">
+        <v>5404</v>
+      </c>
+      <c r="G24" s="43" t="n">
+        <v>5582</v>
+      </c>
+      <c r="H24" s="43" t="n">
+        <v>5916</v>
+      </c>
+      <c r="I24" s="43" t="n">
+        <v>5925</v>
+      </c>
+      <c r="J24" s="43">
+        <f>I24+J19</f>
+        <v/>
+      </c>
+      <c r="K24" s="43">
+        <f>J24+K19</f>
+        <v/>
+      </c>
+      <c r="L24" s="43">
+        <f>K24+L19</f>
+        <v/>
+      </c>
+      <c r="M24" s="43">
+        <f>L24+M19</f>
+        <v/>
+      </c>
+      <c r="N24" s="43">
+        <f>M24+N19</f>
+        <v/>
+      </c>
+      <c r="O24" s="43">
+        <f>N24+O19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" hidden="1">
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  occupied</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="n">
+        <v>4691</v>
+      </c>
+      <c r="D25" s="43" t="n">
+        <v>4841</v>
+      </c>
+      <c r="E25" s="43" t="n">
+        <v>4927</v>
+      </c>
+      <c r="F25" s="43" t="n">
+        <v>4836</v>
+      </c>
+      <c r="G25" s="43" t="n">
+        <v>5113</v>
+      </c>
+      <c r="H25" s="43" t="n">
+        <v>5512</v>
+      </c>
+      <c r="I25" s="43" t="n">
+        <v>5727</v>
+      </c>
+      <c r="J25" s="43">
+        <f>MIN($C$6*J24,I25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="K25" s="43">
+        <f>MIN($C$6*K24,J25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="L25" s="43">
+        <f>MIN($C$6*L24,K25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="M25" s="43">
+        <f>MIN($C$6*M24,L25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="N25" s="43">
+        <f>MIN($C$6*N24,M25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="O25" s="43">
+        <f>MIN($C$6*O24,N25+$C$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
+        </is>
+      </c>
+      <c r="J27" s="44" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K27" s="44" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L27" s="44" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M27" s="44" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N27" s="44" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O27" s="44" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J28" s="45">
+        <f>MIN($C$6,($C$12+$C$8*1)/J24)</f>
+        <v/>
+      </c>
+      <c r="K28" s="45">
+        <f>MIN($C$6,($C$12+$C$8*2)/K24)</f>
+        <v/>
+      </c>
+      <c r="L28" s="45">
+        <f>MIN($C$6,($C$12+$C$8*3)/L24)</f>
+        <v/>
+      </c>
+      <c r="M28" s="45">
+        <f>MIN($C$6,($C$12+$C$8*4)/M24)</f>
+        <v/>
+      </c>
+      <c r="N28" s="45">
+        <f>MIN($C$6,($C$12+$C$8*5)/N24)</f>
+        <v/>
+      </c>
+      <c r="O28" s="45">
+        <f>MIN($C$6,($C$12+$C$8*6)/O24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J29" s="45">
+        <f>MIN($C$6,($C$12+$C$9*1)/J24)</f>
+        <v/>
+      </c>
+      <c r="K29" s="45">
+        <f>MIN($C$6,($C$12+$C$9*2)/K24)</f>
+        <v/>
+      </c>
+      <c r="L29" s="45">
+        <f>MIN($C$6,($C$12+$C$9*3)/L24)</f>
+        <v/>
+      </c>
+      <c r="M29" s="45">
+        <f>MIN($C$6,($C$12+$C$9*4)/M24)</f>
+        <v/>
+      </c>
+      <c r="N29" s="45">
+        <f>MIN($C$6,($C$12+$C$9*5)/N24)</f>
+        <v/>
+      </c>
+      <c r="O29" s="45">
+        <f>MIN($C$6,($C$12+$C$9*6)/O24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J30" s="45">
+        <f>MIN($C$6,($C$12+$C$10*1)/J24)</f>
+        <v/>
+      </c>
+      <c r="K30" s="45">
+        <f>MIN($C$6,($C$12+$C$10*2)/K24)</f>
+        <v/>
+      </c>
+      <c r="L30" s="45">
+        <f>MIN($C$6,($C$12+$C$10*3)/L24)</f>
+        <v/>
+      </c>
+      <c r="M30" s="45">
+        <f>MIN($C$6,($C$12+$C$10*4)/M24)</f>
+        <v/>
+      </c>
+      <c r="N30" s="45">
+        <f>MIN($C$6,($C$12+$C$10*5)/N24)</f>
+        <v/>
+      </c>
+      <c r="O30" s="45">
+        <f>MIN($C$6,($C$12+$C$10*6)/O24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>MARKET RENT GROWTH (editable assumptions)</t>
+        </is>
+      </c>
+      <c r="J32" s="46" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K32" s="46" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L32" s="46" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M32" s="46" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N32" s="46" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O32" s="46" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J33" s="47" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="K33" s="47" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="L33" s="47" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M33" s="47" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="N33" s="47" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O33" s="47" t="n">
+        <v>0.0175</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="26" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J34" s="47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K34" s="47" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L34" s="47" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M34" s="47" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N34" s="47" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O34" s="47" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J35" s="47" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K35" s="47" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L35" s="47" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M35" s="47" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N35" s="47" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O35" s="47" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>CONCESSIONS (months, editable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J37" s="47" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K37" s="47" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L37" s="47" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M37" s="47" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N37" s="47" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O37" s="47" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J38" s="47" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K38" s="47" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L38" s="47" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M38" s="47" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N38" s="47" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O38" s="47" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J39" s="47" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K39" s="47" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L39" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="35" t="n">
-        <v>96</v>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>4940</v>
-      </c>
-      <c r="F16" s="35" t="n">
-        <v>5457</v>
-      </c>
-      <c r="G16" s="36">
-        <f>IFERROR(E16/F16,0)</f>
-        <v/>
-      </c>
-      <c r="H16" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>Q2 2024</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>125</v>
-      </c>
-      <c r="D17" s="35" t="n">
-        <v>173</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>5113</v>
-      </c>
-      <c r="F17" s="35" t="n">
-        <v>5582</v>
-      </c>
-      <c r="G17" s="36">
-        <f>IFERROR(E17/F17,0)</f>
-        <v/>
-      </c>
-      <c r="H17" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>Q3 2024</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>299</v>
-      </c>
-      <c r="D18" s="35" t="n">
-        <v>140</v>
-      </c>
-      <c r="E18" s="35" t="n">
-        <v>5253</v>
-      </c>
-      <c r="F18" s="35" t="n">
-        <v>5881</v>
-      </c>
-      <c r="G18" s="36">
-        <f>IFERROR(E18/F18,0)</f>
-        <v/>
-      </c>
-      <c r="H18" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>Q4 2024</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="D19" s="35" t="n">
-        <v>56</v>
-      </c>
-      <c r="E19" s="35" t="n">
-        <v>5309</v>
-      </c>
-      <c r="F19" s="35" t="n">
-        <v>5916</v>
-      </c>
-      <c r="G19" s="36">
-        <f>IFERROR(E19/F19,0)</f>
-        <v/>
-      </c>
-      <c r="H19" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="34" t="inlineStr">
-        <is>
-          <t>Q1 2025</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="n">
+      <c r="M39" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="35" t="n">
-        <v>87</v>
-      </c>
-      <c r="E20" s="35" t="n">
-        <v>5396</v>
-      </c>
-      <c r="F20" s="35" t="n">
-        <v>5916</v>
-      </c>
-      <c r="G20" s="36">
-        <f>IFERROR(E20/F20,0)</f>
-        <v/>
-      </c>
-      <c r="H20" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>Q2 2025</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="n">
+      <c r="N39" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="35" t="n">
-        <v>116</v>
-      </c>
-      <c r="E21" s="35" t="n">
-        <v>5512</v>
-      </c>
-      <c r="F21" s="35" t="n">
-        <v>5916</v>
-      </c>
-      <c r="G21" s="36">
-        <f>IFERROR(E21/F21,0)</f>
-        <v/>
-      </c>
-      <c r="H21" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="34" t="inlineStr">
-        <is>
-          <t>Q3 2025</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="n">
+      <c r="O39" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="E22" s="35" t="n">
-        <v>5542</v>
-      </c>
-      <c r="F22" s="35" t="n">
-        <v>5916</v>
-      </c>
-      <c r="G22" s="36">
-        <f>IFERROR(E22/F22,0)</f>
-        <v/>
-      </c>
-      <c r="H22" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>Q4 2025</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>45</v>
-      </c>
-      <c r="E23" s="35" t="n">
-        <v>5587</v>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>5916</v>
-      </c>
-      <c r="G23" s="36">
-        <f>IFERROR(E23/F23,0)</f>
-        <v/>
-      </c>
-      <c r="H23" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="34" t="inlineStr">
-        <is>
-          <t>Q1 2026</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="35" t="n">
-        <v>109</v>
-      </c>
-      <c r="E24" s="35" t="n">
-        <v>5695</v>
-      </c>
-      <c r="F24" s="35" t="n">
-        <v>5916</v>
-      </c>
-      <c r="G24" s="36">
-        <f>IFERROR(E24/F24,0)</f>
-        <v/>
-      </c>
-      <c r="H24" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="D25" s="35" t="n">
-        <v>32</v>
-      </c>
-      <c r="E25" s="35" t="n">
-        <v>5727</v>
-      </c>
-      <c r="F25" s="35" t="n">
-        <v>5925</v>
-      </c>
-      <c r="G25" s="36">
-        <f>IFERROR(E25/F25,0)</f>
-        <v/>
-      </c>
-      <c r="H25" s="34" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="37" t="inlineStr">
-        <is>
-          <t>Q3 2026</t>
-        </is>
-      </c>
-      <c r="C26" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B26,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D26" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F26-E25))</f>
-        <v/>
-      </c>
-      <c r="E26" s="38">
-        <f>E25+D26</f>
-        <v/>
-      </c>
-      <c r="F26" s="38">
-        <f>F25+C26</f>
-        <v/>
-      </c>
-      <c r="G26" s="39">
-        <f>IFERROR(E26/F26,0)</f>
-        <v/>
-      </c>
-      <c r="H26" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="37" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="C27" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B27,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D27" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F27-E26))</f>
-        <v/>
-      </c>
-      <c r="E27" s="38">
-        <f>E26+D27</f>
-        <v/>
-      </c>
-      <c r="F27" s="38">
-        <f>F26+C27</f>
-        <v/>
-      </c>
-      <c r="G27" s="39">
-        <f>IFERROR(E27/F27,0)</f>
-        <v/>
-      </c>
-      <c r="H27" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="37" t="inlineStr">
-        <is>
-          <t>Q1 2027</t>
-        </is>
-      </c>
-      <c r="C28" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B28,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D28" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F28-E27))</f>
-        <v/>
-      </c>
-      <c r="E28" s="38">
-        <f>E27+D28</f>
-        <v/>
-      </c>
-      <c r="F28" s="38">
-        <f>F27+C28</f>
-        <v/>
-      </c>
-      <c r="G28" s="39">
-        <f>IFERROR(E28/F28,0)</f>
-        <v/>
-      </c>
-      <c r="H28" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="37" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="C29" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B29,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D29" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F29-E28))</f>
-        <v/>
-      </c>
-      <c r="E29" s="38">
-        <f>E28+D29</f>
-        <v/>
-      </c>
-      <c r="F29" s="38">
-        <f>F28+C29</f>
-        <v/>
-      </c>
-      <c r="G29" s="39">
-        <f>IFERROR(E29/F29,0)</f>
-        <v/>
-      </c>
-      <c r="H29" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="37" t="inlineStr">
-        <is>
-          <t>Q3 2027</t>
-        </is>
-      </c>
-      <c r="C30" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B30,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D30" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F30-E29))</f>
-        <v/>
-      </c>
-      <c r="E30" s="38">
-        <f>E29+D30</f>
-        <v/>
-      </c>
-      <c r="F30" s="38">
-        <f>F29+C30</f>
-        <v/>
-      </c>
-      <c r="G30" s="39">
-        <f>IFERROR(E30/F30,0)</f>
-        <v/>
-      </c>
-      <c r="H30" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="37" t="inlineStr">
-        <is>
-          <t>Q4 2027</t>
-        </is>
-      </c>
-      <c r="C31" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B31,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D31" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F31-E30))</f>
-        <v/>
-      </c>
-      <c r="E31" s="38">
-        <f>E30+D31</f>
-        <v/>
-      </c>
-      <c r="F31" s="38">
-        <f>F30+C31</f>
-        <v/>
-      </c>
-      <c r="G31" s="39">
-        <f>IFERROR(E31/F31,0)</f>
-        <v/>
-      </c>
-      <c r="H31" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="37" t="inlineStr">
-        <is>
-          <t>Q1 2028</t>
-        </is>
-      </c>
-      <c r="C32" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B32,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D32" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F32-E31))</f>
-        <v/>
-      </c>
-      <c r="E32" s="38">
-        <f>E31+D32</f>
-        <v/>
-      </c>
-      <c r="F32" s="38">
-        <f>F31+C32</f>
-        <v/>
-      </c>
-      <c r="G32" s="39">
-        <f>IFERROR(E32/F32,0)</f>
-        <v/>
-      </c>
-      <c r="H32" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="37" t="inlineStr">
-        <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="C33" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B33,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D33" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F33-E32))</f>
-        <v/>
-      </c>
-      <c r="E33" s="38">
-        <f>E32+D33</f>
-        <v/>
-      </c>
-      <c r="F33" s="38">
-        <f>F32+C33</f>
-        <v/>
-      </c>
-      <c r="G33" s="39">
-        <f>IFERROR(E33/F33,0)</f>
-        <v/>
-      </c>
-      <c r="H33" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="37" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="C34" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B34,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D34" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F34-E33))</f>
-        <v/>
-      </c>
-      <c r="E34" s="38">
-        <f>E33+D34</f>
-        <v/>
-      </c>
-      <c r="F34" s="38">
-        <f>F33+C34</f>
-        <v/>
-      </c>
-      <c r="G34" s="39">
-        <f>IFERROR(E34/F34,0)</f>
-        <v/>
-      </c>
-      <c r="H34" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="37" t="inlineStr">
-        <is>
-          <t>Q4 2028</t>
-        </is>
-      </c>
-      <c r="C35" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B35,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D35" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F35-E34))</f>
-        <v/>
-      </c>
-      <c r="E35" s="38">
-        <f>E34+D35</f>
-        <v/>
-      </c>
-      <c r="F35" s="38">
-        <f>F34+C35</f>
-        <v/>
-      </c>
-      <c r="G35" s="39">
-        <f>IFERROR(E35/F35,0)</f>
-        <v/>
-      </c>
-      <c r="H35" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="37" t="inlineStr">
-        <is>
-          <t>Q1 2029</t>
-        </is>
-      </c>
-      <c r="C36" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B36,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D36" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F36-E35))</f>
-        <v/>
-      </c>
-      <c r="E36" s="38">
-        <f>E35+D36</f>
-        <v/>
-      </c>
-      <c r="F36" s="38">
-        <f>F35+C36</f>
-        <v/>
-      </c>
-      <c r="G36" s="39">
-        <f>IFERROR(E36/F36,0)</f>
-        <v/>
-      </c>
-      <c r="H36" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="37" t="inlineStr">
-        <is>
-          <t>Q2 2029</t>
-        </is>
-      </c>
-      <c r="C37" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B37,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D37" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F37-E36))</f>
-        <v/>
-      </c>
-      <c r="E37" s="38">
-        <f>E36+D37</f>
-        <v/>
-      </c>
-      <c r="F37" s="38">
-        <f>F36+C37</f>
-        <v/>
-      </c>
-      <c r="G37" s="39">
-        <f>IFERROR(E37/F37,0)</f>
-        <v/>
-      </c>
-      <c r="H37" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="37" t="inlineStr">
-        <is>
-          <t>Q3 2029</t>
-        </is>
-      </c>
-      <c r="C38" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B38,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D38" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F38-E37))</f>
-        <v/>
-      </c>
-      <c r="E38" s="38">
-        <f>E37+D38</f>
-        <v/>
-      </c>
-      <c r="F38" s="38">
-        <f>F37+C38</f>
-        <v/>
-      </c>
-      <c r="G38" s="39">
-        <f>IFERROR(E38/F38,0)</f>
-        <v/>
-      </c>
-      <c r="H38" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="37" t="inlineStr">
-        <is>
-          <t>Q4 2029</t>
-        </is>
-      </c>
-      <c r="C39" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B39,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D39" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F39-E38))</f>
-        <v/>
-      </c>
-      <c r="E39" s="38">
-        <f>E38+D39</f>
-        <v/>
-      </c>
-      <c r="F39" s="38">
-        <f>F38+C39</f>
-        <v/>
-      </c>
-      <c r="G39" s="39">
-        <f>IFERROR(E39/F39,0)</f>
-        <v/>
-      </c>
-      <c r="H39" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
     </row>
     <row r="40">
-      <c r="B40" s="37" t="inlineStr">
-        <is>
-          <t>Q1 2030</t>
-        </is>
-      </c>
-      <c r="C40" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B40,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D40" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F40-E39))</f>
-        <v/>
-      </c>
-      <c r="E40" s="38">
-        <f>E39+D40</f>
-        <v/>
-      </c>
-      <c r="F40" s="38">
-        <f>F39+C40</f>
-        <v/>
-      </c>
-      <c r="G40" s="39">
-        <f>IFERROR(E40/F40,0)</f>
-        <v/>
-      </c>
-      <c r="H40" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>EFFECTIVE RENT GROWTH (derived)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="37" t="inlineStr">
-        <is>
-          <t>Q2 2030</t>
-        </is>
-      </c>
-      <c r="C41" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B41,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D41" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F41-E40))</f>
-        <v/>
-      </c>
-      <c r="E41" s="38">
-        <f>E40+D41</f>
-        <v/>
-      </c>
-      <c r="F41" s="38">
-        <f>F40+C41</f>
-        <v/>
-      </c>
-      <c r="G41" s="39">
-        <f>IFERROR(E41/F41,0)</f>
-        <v/>
-      </c>
-      <c r="H41" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
+      <c r="B41" s="26" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J41" s="45">
+        <f>(1+J33)*(1-J37)-1</f>
+        <v/>
+      </c>
+      <c r="K41" s="45">
+        <f>(1+K33)*(1-K37)/(1-J37)-1</f>
+        <v/>
+      </c>
+      <c r="L41" s="45">
+        <f>(1+L33)*(1-L37)/(1-K37)-1</f>
+        <v/>
+      </c>
+      <c r="M41" s="45">
+        <f>(1+M33)*(1-M37)/(1-L37)-1</f>
+        <v/>
+      </c>
+      <c r="N41" s="45">
+        <f>(1+N33)*(1-N37)/(1-M37)-1</f>
+        <v/>
+      </c>
+      <c r="O41" s="45">
+        <f>(1+O33)*(1-O37)/(1-N37)-1</f>
+        <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="37" t="inlineStr">
-        <is>
-          <t>Q3 2030</t>
-        </is>
-      </c>
-      <c r="C42" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B42,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D42" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F42-E41))</f>
-        <v/>
-      </c>
-      <c r="E42" s="38">
-        <f>E41+D42</f>
-        <v/>
-      </c>
-      <c r="F42" s="38">
-        <f>F41+C42</f>
-        <v/>
-      </c>
-      <c r="G42" s="39">
-        <f>IFERROR(E42/F42,0)</f>
-        <v/>
-      </c>
-      <c r="H42" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J42" s="45">
+        <f>(1+J34)*(1-J38)-1</f>
+        <v/>
+      </c>
+      <c r="K42" s="45">
+        <f>(1+K34)*(1-K38)/(1-J38)-1</f>
+        <v/>
+      </c>
+      <c r="L42" s="45">
+        <f>(1+L34)*(1-L38)/(1-K38)-1</f>
+        <v/>
+      </c>
+      <c r="M42" s="45">
+        <f>(1+M34)*(1-M38)/(1-L38)-1</f>
+        <v/>
+      </c>
+      <c r="N42" s="45">
+        <f>(1+N34)*(1-N38)/(1-M38)-1</f>
+        <v/>
+      </c>
+      <c r="O42" s="45">
+        <f>(1+O34)*(1-O38)/(1-N38)-1</f>
+        <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="37" t="inlineStr">
-        <is>
-          <t>Q4 2030</t>
-        </is>
-      </c>
-      <c r="C43" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B43,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D43" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F43-E42))</f>
-        <v/>
-      </c>
-      <c r="E43" s="38">
-        <f>E42+D43</f>
-        <v/>
-      </c>
-      <c r="F43" s="38">
-        <f>F42+C43</f>
-        <v/>
-      </c>
-      <c r="G43" s="39">
-        <f>IFERROR(E43/F43,0)</f>
-        <v/>
-      </c>
-      <c r="H43" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J43" s="45">
+        <f>(1+J35)*(1-J39)-1</f>
+        <v/>
+      </c>
+      <c r="K43" s="45">
+        <f>(1+K35)*(1-K39)/(1-J39)-1</f>
+        <v/>
+      </c>
+      <c r="L43" s="45">
+        <f>(1+L35)*(1-L39)/(1-K39)-1</f>
+        <v/>
+      </c>
+      <c r="M43" s="45">
+        <f>(1+M35)*(1-M39)/(1-L39)-1</f>
+        <v/>
+      </c>
+      <c r="N43" s="45">
+        <f>(1+N35)*(1-N39)/(1-M39)-1</f>
+        <v/>
+      </c>
+      <c r="O43" s="45">
+        <f>(1+O35)*(1-O39)/(1-N39)-1</f>
+        <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="37" t="inlineStr">
-        <is>
-          <t>Q1 2031</t>
-        </is>
-      </c>
-      <c r="C44" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B44,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D44" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F44-E43))</f>
-        <v/>
-      </c>
-      <c r="E44" s="38">
-        <f>E43+D44</f>
-        <v/>
-      </c>
-      <c r="F44" s="38">
-        <f>F43+C44</f>
-        <v/>
-      </c>
-      <c r="G44" s="39">
-        <f>IFERROR(E44/F44,0)</f>
-        <v/>
-      </c>
-      <c r="H44" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>Reconciliation: scheduled pipeline (Incl=Y) vs CoStar Under Construction = 27 units.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="37" t="inlineStr">
-        <is>
-          <t>Q2 2031</t>
-        </is>
-      </c>
-      <c r="C45" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B45,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D45" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F45-E44))</f>
-        <v/>
-      </c>
-      <c r="E45" s="38">
-        <f>E44+D45</f>
-        <v/>
-      </c>
-      <c r="F45" s="38">
-        <f>F44+C45</f>
-        <v/>
-      </c>
-      <c r="G45" s="39">
-        <f>IFERROR(E45/F45,0)</f>
-        <v/>
-      </c>
-      <c r="H45" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="37" t="inlineStr">
-        <is>
-          <t>Q3 2031</t>
-        </is>
-      </c>
-      <c r="C46" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B46,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D46" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F46-E45))</f>
-        <v/>
-      </c>
-      <c r="E46" s="38">
-        <f>E45+D46</f>
-        <v/>
-      </c>
-      <c r="F46" s="38">
-        <f>F45+C46</f>
-        <v/>
-      </c>
-      <c r="G46" s="39">
-        <f>IFERROR(E46/F46,0)</f>
-        <v/>
-      </c>
-      <c r="H46" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="37" t="inlineStr">
-        <is>
-          <t>Q4 2031</t>
-        </is>
-      </c>
-      <c r="C47" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B47,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D47" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F47-E46))</f>
-        <v/>
-      </c>
-      <c r="E47" s="38">
-        <f>E46+D47</f>
-        <v/>
-      </c>
-      <c r="F47" s="38">
-        <f>F46+C47</f>
-        <v/>
-      </c>
-      <c r="G47" s="39">
-        <f>IFERROR(E47/F47,0)</f>
-        <v/>
-      </c>
-      <c r="H47" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="37" t="inlineStr">
-        <is>
-          <t>Q1 2032</t>
-        </is>
-      </c>
-      <c r="C48" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B48,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D48" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F48-E47))</f>
-        <v/>
-      </c>
-      <c r="E48" s="38">
-        <f>E47+D48</f>
-        <v/>
-      </c>
-      <c r="F48" s="38">
-        <f>F47+C48</f>
-        <v/>
-      </c>
-      <c r="G48" s="39">
-        <f>IFERROR(E48/F48,0)</f>
-        <v/>
-      </c>
-      <c r="H48" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="37" t="inlineStr">
-        <is>
-          <t>Q2 2032</t>
-        </is>
-      </c>
-      <c r="C49" s="38">
-        <f>SUMIFS($K$5:$K$10,$L$5:$L$10,B49,$M$5:$M$10,"Y")</f>
-        <v/>
-      </c>
-      <c r="D49" s="38">
-        <f>MIN($C$10,MAX(0,$C$3*F49-E48))</f>
-        <v/>
-      </c>
-      <c r="E49" s="38">
-        <f>E48+D49</f>
-        <v/>
-      </c>
-      <c r="F49" s="38">
-        <f>F48+C49</f>
-        <v/>
-      </c>
-      <c r="G49" s="39">
-        <f>IFERROR(E49/F49,0)</f>
-        <v/>
-      </c>
-      <c r="H49" s="37" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t>Historical = CoStar 5-mi actuals. Forecast: inventory grows by scheduled pipeline deliveries (edit dates/include at right); absorption = min(quarterly demand, units to reach target); overall occ = occupied / inventory. Yellow cells are editable.</t>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += scheduled pipeline; occupied += selected demand (capped at target). Edit yellow cells (close quarter, demand scenario/levels, pipeline dates &amp; include, rent-growth &amp; concessions).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B51:H51"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="J3:M3"/>
+  <mergeCells count="1">
+    <mergeCell ref="B2:O2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5 M6 M7 M8 M9 M10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U5 U6 U7 U8 U9 U10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -234,6 +234,12 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -244,12 +250,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1640,7 +1640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:W45"/>
+  <dimension ref="B2:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1661,9 +1661,10 @@
     <col width="28" customWidth="1" min="18" max="18"/>
     <col width="7" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
     <col width="8" customWidth="1" min="22" max="22"/>
     <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="2" ht="22" customHeight="1">
@@ -1676,7 +1677,7 @@
     <row r="3">
       <c r="R3" s="25" t="inlineStr">
         <is>
-          <t>PIPELINE INPUTS (forward new supply)</t>
+          <t>UNDER CONSTRUCTION (linked from Competitive Analysis)</t>
         </is>
       </c>
     </row>
@@ -1711,15 +1712,10 @@
       </c>
       <c r="U4" s="28" t="inlineStr">
         <is>
-          <t>Incl?</t>
+          <t>DelivIdx</t>
         </is>
       </c>
       <c r="V4" s="28" t="inlineStr">
-        <is>
-          <t>DelivIdx</t>
-        </is>
-      </c>
-      <c r="W4" s="28" t="inlineStr">
         <is>
           <t>HoldYr</t>
         </is>
@@ -1740,32 +1736,6 @@
         <f>IFERROR(VALUE(RIGHT($C$5,4))*4+MATCH(LEFT($C$5,2),{"Q1","Q2","Q3","Q4"},0)-1,0)</f>
         <v/>
       </c>
-      <c r="R5" s="30" t="inlineStr">
-        <is>
-          <t>Vista Point</t>
-        </is>
-      </c>
-      <c r="S5" s="31" t="n">
-        <v>893</v>
-      </c>
-      <c r="T5" s="32" t="inlineStr">
-        <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="U5" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V5" s="33">
-        <f>IFERROR(VALUE(RIGHT(T5,4))*4+MATCH(LEFT(T5,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W5" s="33">
-        <f>IF(V5="","",IF(V5&lt;=$E$4,0,MAX(1,INT((V5-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="B6" s="26" t="inlineStr">
@@ -1773,34 +1743,12 @@
           <t>Stabilization Target</t>
         </is>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="30">
         <f>Settings!$B$2</f>
         <v/>
       </c>
-      <c r="R6" s="30" t="inlineStr">
-        <is>
-          <t>Seasons on the Bench</t>
-        </is>
-      </c>
-      <c r="S6" s="31" t="n">
-        <v>358</v>
-      </c>
-      <c r="T6" s="32" t="inlineStr">
-        <is>
-          <t>Q4 2027</t>
-        </is>
-      </c>
-      <c r="U6" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V6" s="33">
-        <f>IFERROR(VALUE(RIGHT(T6,4))*4+MATCH(LEFT(T6,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W6" s="33">
-        <f>IF(V6="","",IF(V6&lt;=$E$4,0,MAX(1,INT((V6-$E$5)/4)+1)))</f>
+      <c r="E6">
+        <f>IF($C$7="Bear",3,IF($C$7="Base",2,1))</f>
         <v/>
       </c>
     </row>
@@ -1815,31 +1763,10 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="R7" s="30" t="inlineStr">
-        <is>
-          <t>1519 South Londoner Avenue</t>
-        </is>
-      </c>
-      <c r="S7" s="31" t="n">
-        <v>189</v>
-      </c>
-      <c r="T7" s="32" t="inlineStr">
-        <is>
-          <t>Q3 2027</t>
-        </is>
-      </c>
-      <c r="U7" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V7" s="33">
-        <f>IFERROR(VALUE(RIGHT(T7,4))*4+MATCH(LEFT(T7,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W7" s="33">
-        <f>IF(V7="","",IF(V7&lt;=$E$4,0,MAX(1,INT((V7-$E$5)/4)+1)))</f>
-        <v/>
+      <c r="R7" s="25" t="inlineStr">
+        <is>
+          <t>PROPOSED PIPELINE (scenario toggle)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1848,34 +1775,43 @@
           <t>Bear Annual Absorption</t>
         </is>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="31" t="n">
         <v>150</v>
       </c>
-      <c r="R8" s="30" t="inlineStr">
-        <is>
-          <t>3300 South Vista Avenue</t>
-        </is>
-      </c>
-      <c r="S8" s="31" t="n">
-        <v>180</v>
-      </c>
-      <c r="T8" s="32" t="inlineStr">
-        <is>
-          <t>Q1 2028</t>
-        </is>
-      </c>
-      <c r="U8" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V8" s="33">
-        <f>IFERROR(VALUE(RIGHT(T8,4))*4+MATCH(LEFT(T8,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W8" s="33">
-        <f>IF(V8="","",IF(V8&lt;=$E$4,0,MAX(1,INT((V8-$E$5)/4)+1)))</f>
-        <v/>
+      <c r="R8" s="28" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="S8" s="28" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="T8" s="28" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="U8" s="28" t="inlineStr">
+        <is>
+          <t>Built In</t>
+        </is>
+      </c>
+      <c r="V8" s="28" t="inlineStr">
+        <is>
+          <t>DelivIdx</t>
+        </is>
+      </c>
+      <c r="W8" s="28" t="inlineStr">
+        <is>
+          <t>HoldYr</t>
+        </is>
+      </c>
+      <c r="X8" s="28" t="inlineStr">
+        <is>
+          <t>Built?</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1884,33 +1820,37 @@
           <t>Base Annual Absorption</t>
         </is>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="31" t="n">
         <v>300</v>
       </c>
-      <c r="R9" s="30" t="inlineStr">
-        <is>
-          <t>Station Village</t>
-        </is>
-      </c>
-      <c r="S9" s="31" t="n">
-        <v>84</v>
-      </c>
-      <c r="T9" s="32" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="U9" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V9" s="33">
+      <c r="R9" s="32" t="inlineStr">
+        <is>
+          <t>Vista Point</t>
+        </is>
+      </c>
+      <c r="S9" s="33" t="n">
+        <v>893</v>
+      </c>
+      <c r="T9" s="34" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
+      </c>
+      <c r="U9" s="34" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V9" s="35">
         <f>IFERROR(VALUE(RIGHT(T9,4))*4+MATCH(LEFT(T9,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W9" s="33">
+      <c r="W9" s="35">
         <f>IF(V9="","",IF(V9&lt;=$E$4,0,MAX(1,INT((V9-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X9" s="35">
+        <f>IF(U9="None",0,IF($E$6&gt;=IF(U9="Bear",3,IF(U9="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -1920,33 +1860,37 @@
           <t>Bull Annual Absorption</t>
         </is>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="31" t="n">
         <v>450</v>
       </c>
-      <c r="R10" s="30" t="inlineStr">
-        <is>
-          <t>Harris Ranch East</t>
-        </is>
-      </c>
-      <c r="S10" s="31" t="n">
-        <v>59</v>
-      </c>
-      <c r="T10" s="32" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="U10" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V10" s="33">
+      <c r="R10" s="32" t="inlineStr">
+        <is>
+          <t>Seasons on the Bench</t>
+        </is>
+      </c>
+      <c r="S10" s="33" t="n">
+        <v>358</v>
+      </c>
+      <c r="T10" s="34" t="inlineStr">
+        <is>
+          <t>Q4 2027</t>
+        </is>
+      </c>
+      <c r="U10" s="34" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V10" s="35">
         <f>IFERROR(VALUE(RIGHT(T10,4))*4+MATCH(LEFT(T10,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W10" s="33">
+      <c r="W10" s="35">
         <f>IF(V10="","",IF(V10&lt;=$E$4,0,MAX(1,INT((V10-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X10" s="35">
+        <f>IF(U10="None",0,IF($E$6&gt;=IF(U10="Bear",3,IF(U10="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -1960,6 +1904,36 @@
         <f>IF($C$7="Bear",$C$8,IF($C$7="Bull",$C$10,$C$9))</f>
         <v/>
       </c>
+      <c r="R11" s="32" t="inlineStr">
+        <is>
+          <t>1519 South Londoner Avenue</t>
+        </is>
+      </c>
+      <c r="S11" s="33" t="n">
+        <v>189</v>
+      </c>
+      <c r="T11" s="34" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="U11" s="34" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V11" s="35">
+        <f>IFERROR(VALUE(RIGHT(T11,4))*4+MATCH(LEFT(T11,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W11" s="35">
+        <f>IF(V11="","",IF(V11&lt;=$E$4,0,MAX(1,INT((V11-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X11" s="35">
+        <f>IF(U11="None",0,IF($E$6&gt;=IF(U11="Bear",3,IF(U11="Base",2,1)),1,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="26" t="inlineStr">
@@ -1970,6 +1944,36 @@
       <c r="C12" s="36" t="n">
         <v>5727</v>
       </c>
+      <c r="R12" s="32" t="inlineStr">
+        <is>
+          <t>3300 South Vista Avenue</t>
+        </is>
+      </c>
+      <c r="S12" s="33" t="n">
+        <v>180</v>
+      </c>
+      <c r="T12" s="34" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="U12" s="34" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V12" s="35">
+        <f>IFERROR(VALUE(RIGHT(T12,4))*4+MATCH(LEFT(T12,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W12" s="35">
+        <f>IF(V12="","",IF(V12&lt;=$E$4,0,MAX(1,INT((V12-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X12" s="35">
+        <f>IF(U12="None",0,IF($E$6&gt;=IF(U12="Bear",3,IF(U12="Base",2,1)),1,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="26" t="inlineStr">
@@ -1980,6 +1984,68 @@
       <c r="C13" s="36" t="n">
         <v>5925</v>
       </c>
+      <c r="R13" s="32" t="inlineStr">
+        <is>
+          <t>Station Village</t>
+        </is>
+      </c>
+      <c r="S13" s="33" t="n">
+        <v>84</v>
+      </c>
+      <c r="T13" s="34" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="U13" s="34" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V13" s="35">
+        <f>IFERROR(VALUE(RIGHT(T13,4))*4+MATCH(LEFT(T13,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W13" s="35">
+        <f>IF(V13="","",IF(V13&lt;=$E$4,0,MAX(1,INT((V13-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X13" s="35">
+        <f>IF(U13="None",0,IF($E$6&gt;=IF(U13="Bear",3,IF(U13="Base",2,1)),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="R14" s="32" t="inlineStr">
+        <is>
+          <t>Harris Ranch East</t>
+        </is>
+      </c>
+      <c r="S14" s="33" t="n">
+        <v>59</v>
+      </c>
+      <c r="T14" s="34" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="U14" s="34" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V14" s="35">
+        <f>IFERROR(VALUE(RIGHT(T14,4))*4+MATCH(LEFT(T14,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W14" s="35">
+        <f>IF(V14="","",IF(V14&lt;=$E$4,0,MAX(1,INT((V14-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X14" s="35">
+        <f>IF(U14="None",0,IF($E$6&gt;=IF(U14="Bear",3,IF(U14="Base",2,1)),1,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="26" t="inlineStr">
@@ -2148,27 +2214,27 @@
         <v>9</v>
       </c>
       <c r="J19" s="40">
-        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,1,$U$5:$U$10,"Y")</f>
+        <f>SUMIFS($S$5:$S$5,$V$5:$V$5,1)+SUMIFS($S$9:$S$14,$W$9:$W$14,1,$X$9:$X$14,1)</f>
         <v/>
       </c>
       <c r="K19" s="40">
-        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,2,$U$5:$U$10,"Y")</f>
+        <f>SUMIFS($S$5:$S$5,$V$5:$V$5,2)+SUMIFS($S$9:$S$14,$W$9:$W$14,2,$X$9:$X$14,1)</f>
         <v/>
       </c>
       <c r="L19" s="40">
-        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,3,$U$5:$U$10,"Y")</f>
+        <f>SUMIFS($S$5:$S$5,$V$5:$V$5,3)+SUMIFS($S$9:$S$14,$W$9:$W$14,3,$X$9:$X$14,1)</f>
         <v/>
       </c>
       <c r="M19" s="40">
-        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,4,$U$5:$U$10,"Y")</f>
+        <f>SUMIFS($S$5:$S$5,$V$5:$V$5,4)+SUMIFS($S$9:$S$14,$W$9:$W$14,4,$X$9:$X$14,1)</f>
         <v/>
       </c>
       <c r="N19" s="40">
-        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,5,$U$5:$U$10,"Y")</f>
+        <f>SUMIFS($S$5:$S$5,$V$5:$V$5,5)+SUMIFS($S$9:$S$14,$W$9:$W$14,5,$X$9:$X$14,1)</f>
         <v/>
       </c>
       <c r="O19" s="40">
-        <f>SUMIFS($S$5:$S$10,$W$5:$W$10,6,$U$5:$U$10,"Y")</f>
+        <f>SUMIFS($S$5:$S$5,$V$5:$V$5,6)+SUMIFS($S$9:$S$14,$W$9:$W$14,6,$X$9:$X$14,1)</f>
         <v/>
       </c>
     </row>
@@ -2857,14 +2923,21 @@
     <row r="44">
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>Reconciliation: scheduled pipeline (Incl=Y) vs CoStar Under Construction = 27 units.</t>
+          <t>Reconciliation: UC pipeline scheduled = 0 units vs CoStar current Under Construction = 27 units.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += scheduled pipeline; occupied += selected demand (capped at target). Edit yellow cells (close quarter, demand scenario/levels, pipeline dates &amp; include, rent-growth &amp; concessions).</t>
+          <t>Note: as-of quarter (2026 Q2 QTD) is partial (quarter-to-date). Occupancy is point-in-time (valid); Y0 supply/absorption sums for that quarter are partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += UC (linked from Competitive Analysis) + proposed built this scenario; occupied += selected demand (capped at target). Yellow cells are editable.</t>
         </is>
       </c>
     </row>
@@ -2876,8 +2949,8 @@
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="U5 U6 U7 U8 U9 U10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Y,N"</formula1>
+    <dataValidation sqref="U9 U10 U11 U12 U13 U14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Bear,Base,Bull,None"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -163,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -274,6 +275,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1640,7 +1653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:X46"/>
+  <dimension ref="B2:X50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2266,27 +2279,27 @@
         <v>216</v>
       </c>
       <c r="J20" s="40">
-        <f>J25-I25</f>
+        <f>J29-I29</f>
         <v/>
       </c>
       <c r="K20" s="40">
-        <f>K25-J25</f>
+        <f>K29-J29</f>
         <v/>
       </c>
       <c r="L20" s="40">
-        <f>L25-K25</f>
+        <f>L29-K29</f>
         <v/>
       </c>
       <c r="M20" s="40">
-        <f>M25-L25</f>
+        <f>M29-L29</f>
         <v/>
       </c>
       <c r="N20" s="40">
-        <f>N25-M25</f>
+        <f>N29-M29</f>
         <v/>
       </c>
       <c r="O20" s="40">
-        <f>O25-N25</f>
+        <f>O29-N29</f>
         <v/>
       </c>
     </row>
@@ -2318,27 +2331,27 @@
         <v>0.967</v>
       </c>
       <c r="J21" s="42">
-        <f>IFERROR(J25/J24,0)</f>
+        <f>IFERROR(J29/J28,0)</f>
         <v/>
       </c>
       <c r="K21" s="42">
-        <f>IFERROR(K25/K24,0)</f>
+        <f>IFERROR(K29/K28,0)</f>
         <v/>
       </c>
       <c r="L21" s="42">
-        <f>IFERROR(L25/L24,0)</f>
+        <f>IFERROR(L29/L28,0)</f>
         <v/>
       </c>
       <c r="M21" s="42">
-        <f>IFERROR(M25/M24,0)</f>
+        <f>IFERROR(M29/M28,0)</f>
         <v/>
       </c>
       <c r="N21" s="42">
-        <f>IFERROR(N25/N24,0)</f>
+        <f>IFERROR(N29/N28,0)</f>
         <v/>
       </c>
       <c r="O21" s="42">
-        <f>IFERROR(O25/O24,0)</f>
+        <f>IFERROR(O29/O28,0)</f>
         <v/>
       </c>
     </row>
@@ -2392,356 +2405,341 @@
         <v/>
       </c>
     </row>
-    <row r="24" hidden="1">
-      <c r="B24" s="19" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>SUBJECT (Canyon Ridge)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Market Rent  (HD→CoStar)</t>
+        </is>
+      </c>
+      <c r="C24" s="44" t="n"/>
+      <c r="D24" s="44" t="n"/>
+      <c r="E24" s="44" t="n"/>
+      <c r="F24" s="44" t="n"/>
+      <c r="G24" s="44" t="n"/>
+      <c r="H24" s="44" t="n"/>
+      <c r="I24" s="44" t="n"/>
+      <c r="J24" s="45" t="n"/>
+      <c r="K24" s="45" t="n"/>
+      <c r="L24" s="45" t="n"/>
+      <c r="M24" s="45" t="n"/>
+      <c r="N24" s="45" t="n"/>
+      <c r="O24" s="45" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Effective Rent</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="n"/>
+      <c r="D25" s="44" t="n"/>
+      <c r="E25" s="44" t="n"/>
+      <c r="F25" s="44" t="n"/>
+      <c r="G25" s="44" t="n"/>
+      <c r="H25" s="44" t="n"/>
+      <c r="I25" s="44" t="n"/>
+      <c r="J25" s="45" t="n"/>
+      <c r="K25" s="45" t="n"/>
+      <c r="L25" s="45" t="n"/>
+      <c r="M25" s="45" t="n"/>
+      <c r="N25" s="45" t="n"/>
+      <c r="O25" s="45" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Occupancy (T12 financials)</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="n"/>
+      <c r="D26" s="46" t="n"/>
+      <c r="E26" s="46" t="n"/>
+      <c r="F26" s="46" t="n"/>
+      <c r="G26" s="46" t="n"/>
+      <c r="H26" s="46" t="n"/>
+      <c r="I26" s="46" t="n"/>
+      <c r="J26" s="47" t="n"/>
+      <c r="K26" s="47" t="n"/>
+      <c r="L26" s="47" t="n"/>
+      <c r="M26" s="47" t="n"/>
+      <c r="N26" s="47" t="n"/>
+      <c r="O26" s="47" t="n"/>
+    </row>
+    <row r="28" hidden="1">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  inventory</t>
         </is>
       </c>
-      <c r="C24" s="43" t="n">
+      <c r="C28" s="43" t="n">
         <v>4845</v>
       </c>
-      <c r="D24" s="43" t="n">
+      <c r="D28" s="43" t="n">
         <v>5082</v>
       </c>
-      <c r="E24" s="43" t="n">
+      <c r="E28" s="43" t="n">
         <v>5115</v>
       </c>
-      <c r="F24" s="43" t="n">
+      <c r="F28" s="43" t="n">
         <v>5404</v>
       </c>
-      <c r="G24" s="43" t="n">
+      <c r="G28" s="43" t="n">
         <v>5582</v>
       </c>
-      <c r="H24" s="43" t="n">
+      <c r="H28" s="43" t="n">
         <v>5916</v>
       </c>
-      <c r="I24" s="43" t="n">
+      <c r="I28" s="43" t="n">
         <v>5925</v>
       </c>
-      <c r="J24" s="43">
-        <f>I24+J19</f>
-        <v/>
-      </c>
-      <c r="K24" s="43">
-        <f>J24+K19</f>
-        <v/>
-      </c>
-      <c r="L24" s="43">
-        <f>K24+L19</f>
-        <v/>
-      </c>
-      <c r="M24" s="43">
-        <f>L24+M19</f>
-        <v/>
-      </c>
-      <c r="N24" s="43">
-        <f>M24+N19</f>
-        <v/>
-      </c>
-      <c r="O24" s="43">
-        <f>N24+O19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" hidden="1">
-      <c r="B25" s="19" t="inlineStr">
+      <c r="J28" s="43">
+        <f>I28+J19</f>
+        <v/>
+      </c>
+      <c r="K28" s="43">
+        <f>J28+K19</f>
+        <v/>
+      </c>
+      <c r="L28" s="43">
+        <f>K28+L19</f>
+        <v/>
+      </c>
+      <c r="M28" s="43">
+        <f>L28+M19</f>
+        <v/>
+      </c>
+      <c r="N28" s="43">
+        <f>M28+N19</f>
+        <v/>
+      </c>
+      <c r="O28" s="43">
+        <f>N28+O19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" hidden="1">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  occupied</t>
         </is>
       </c>
-      <c r="C25" s="43" t="n">
+      <c r="C29" s="43" t="n">
         <v>4691</v>
       </c>
-      <c r="D25" s="43" t="n">
+      <c r="D29" s="43" t="n">
         <v>4841</v>
       </c>
-      <c r="E25" s="43" t="n">
+      <c r="E29" s="43" t="n">
         <v>4927</v>
       </c>
-      <c r="F25" s="43" t="n">
+      <c r="F29" s="43" t="n">
         <v>4836</v>
       </c>
-      <c r="G25" s="43" t="n">
+      <c r="G29" s="43" t="n">
         <v>5113</v>
       </c>
-      <c r="H25" s="43" t="n">
+      <c r="H29" s="43" t="n">
         <v>5512</v>
       </c>
-      <c r="I25" s="43" t="n">
+      <c r="I29" s="43" t="n">
         <v>5727</v>
       </c>
-      <c r="J25" s="43">
-        <f>MIN($C$6*J24,I25+$C$11)</f>
-        <v/>
-      </c>
-      <c r="K25" s="43">
-        <f>MIN($C$6*K24,J25+$C$11)</f>
-        <v/>
-      </c>
-      <c r="L25" s="43">
-        <f>MIN($C$6*L24,K25+$C$11)</f>
-        <v/>
-      </c>
-      <c r="M25" s="43">
-        <f>MIN($C$6*M24,L25+$C$11)</f>
-        <v/>
-      </c>
-      <c r="N25" s="43">
-        <f>MIN($C$6*N24,M25+$C$11)</f>
-        <v/>
-      </c>
-      <c r="O25" s="43">
-        <f>MIN($C$6*O24,N25+$C$11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="26" t="inlineStr">
+      <c r="J29" s="43">
+        <f>MIN($C$6*J28,I29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="K29" s="43">
+        <f>MIN($C$6*K28,J29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="L29" s="43">
+        <f>MIN($C$6*L28,K29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="M29" s="43">
+        <f>MIN($C$6*M28,L29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="N29" s="43">
+        <f>MIN($C$6*N28,M29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="O29" s="43">
+        <f>MIN($C$6*O28,N29+$C$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
         </is>
       </c>
-      <c r="J27" s="44" t="inlineStr">
+      <c r="J31" s="48" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K27" s="44" t="inlineStr">
+      <c r="K31" s="48" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L27" s="44" t="inlineStr">
+      <c r="L31" s="48" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M27" s="44" t="inlineStr">
+      <c r="M31" s="48" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N27" s="44" t="inlineStr">
+      <c r="N31" s="48" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O27" s="44" t="inlineStr">
+      <c r="O31" s="48" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J28" s="45">
-        <f>MIN($C$6,($C$12+$C$8*1)/J24)</f>
-        <v/>
-      </c>
-      <c r="K28" s="45">
-        <f>MIN($C$6,($C$12+$C$8*2)/K24)</f>
-        <v/>
-      </c>
-      <c r="L28" s="45">
-        <f>MIN($C$6,($C$12+$C$8*3)/L24)</f>
-        <v/>
-      </c>
-      <c r="M28" s="45">
-        <f>MIN($C$6,($C$12+$C$8*4)/M24)</f>
-        <v/>
-      </c>
-      <c r="N28" s="45">
-        <f>MIN($C$6,($C$12+$C$8*5)/N24)</f>
-        <v/>
-      </c>
-      <c r="O28" s="45">
-        <f>MIN($C$6,($C$12+$C$8*6)/O24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J29" s="45">
-        <f>MIN($C$6,($C$12+$C$9*1)/J24)</f>
-        <v/>
-      </c>
-      <c r="K29" s="45">
-        <f>MIN($C$6,($C$12+$C$9*2)/K24)</f>
-        <v/>
-      </c>
-      <c r="L29" s="45">
-        <f>MIN($C$6,($C$12+$C$9*3)/L24)</f>
-        <v/>
-      </c>
-      <c r="M29" s="45">
-        <f>MIN($C$6,($C$12+$C$9*4)/M24)</f>
-        <v/>
-      </c>
-      <c r="N29" s="45">
-        <f>MIN($C$6,($C$12+$C$9*5)/N24)</f>
-        <v/>
-      </c>
-      <c r="O29" s="45">
-        <f>MIN($C$6,($C$12+$C$9*6)/O24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="J30" s="45">
-        <f>MIN($C$6,($C$12+$C$10*1)/J24)</f>
-        <v/>
-      </c>
-      <c r="K30" s="45">
-        <f>MIN($C$6,($C$12+$C$10*2)/K24)</f>
-        <v/>
-      </c>
-      <c r="L30" s="45">
-        <f>MIN($C$6,($C$12+$C$10*3)/L24)</f>
-        <v/>
-      </c>
-      <c r="M30" s="45">
-        <f>MIN($C$6,($C$12+$C$10*4)/M24)</f>
-        <v/>
-      </c>
-      <c r="N30" s="45">
-        <f>MIN($C$6,($C$12+$C$10*5)/N24)</f>
-        <v/>
-      </c>
-      <c r="O30" s="45">
-        <f>MIN($C$6,($C$12+$C$10*6)/O24)</f>
-        <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>MARKET RENT GROWTH (editable assumptions)</t>
-        </is>
-      </c>
-      <c r="J32" s="46" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="K32" s="46" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="L32" s="46" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="M32" s="46" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="N32" s="46" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="O32" s="46" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J32" s="49">
+        <f>MIN($C$6,($C$12+$C$8*1)/J28)</f>
+        <v/>
+      </c>
+      <c r="K32" s="49">
+        <f>MIN($C$6,($C$12+$C$8*2)/K28)</f>
+        <v/>
+      </c>
+      <c r="L32" s="49">
+        <f>MIN($C$6,($C$12+$C$8*3)/L28)</f>
+        <v/>
+      </c>
+      <c r="M32" s="49">
+        <f>MIN($C$6,($C$12+$C$8*4)/M28)</f>
+        <v/>
+      </c>
+      <c r="N32" s="49">
+        <f>MIN($C$6,($C$12+$C$8*5)/N28)</f>
+        <v/>
+      </c>
+      <c r="O32" s="49">
+        <f>MIN($C$6,($C$12+$C$8*6)/O28)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J33" s="47" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="K33" s="47" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="L33" s="47" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M33" s="47" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="N33" s="47" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O33" s="47" t="n">
-        <v>0.0175</v>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J33" s="49">
+        <f>MIN($C$6,($C$12+$C$9*1)/J28)</f>
+        <v/>
+      </c>
+      <c r="K33" s="49">
+        <f>MIN($C$6,($C$12+$C$9*2)/K28)</f>
+        <v/>
+      </c>
+      <c r="L33" s="49">
+        <f>MIN($C$6,($C$12+$C$9*3)/L28)</f>
+        <v/>
+      </c>
+      <c r="M33" s="49">
+        <f>MIN($C$6,($C$12+$C$9*4)/M28)</f>
+        <v/>
+      </c>
+      <c r="N33" s="49">
+        <f>MIN($C$6,($C$12+$C$9*5)/N28)</f>
+        <v/>
+      </c>
+      <c r="O33" s="49">
+        <f>MIN($C$6,($C$12+$C$9*6)/O28)</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="26" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J34" s="47" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K34" s="47" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L34" s="47" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M34" s="47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N34" s="47" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O34" s="47" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="26" t="inlineStr">
-        <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J35" s="47" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K35" s="47" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L35" s="47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M35" s="47" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N35" s="47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O35" s="47" t="n">
-        <v>0.04</v>
+      <c r="J34" s="49">
+        <f>MIN($C$6,($C$12+$C$10*1)/J28)</f>
+        <v/>
+      </c>
+      <c r="K34" s="49">
+        <f>MIN($C$6,($C$12+$C$10*2)/K28)</f>
+        <v/>
+      </c>
+      <c r="L34" s="49">
+        <f>MIN($C$6,($C$12+$C$10*3)/L28)</f>
+        <v/>
+      </c>
+      <c r="M34" s="49">
+        <f>MIN($C$6,($C$12+$C$10*4)/M28)</f>
+        <v/>
+      </c>
+      <c r="N34" s="49">
+        <f>MIN($C$6,($C$12+$C$10*5)/N28)</f>
+        <v/>
+      </c>
+      <c r="O34" s="49">
+        <f>MIN($C$6,($C$12+$C$10*6)/O28)</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="26" t="inlineStr">
         <is>
-          <t>CONCESSIONS (months, editable)</t>
+          <t>MARKET RENT GROWTH (editable assumptions)</t>
+        </is>
+      </c>
+      <c r="J36" s="50" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K36" s="50" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L36" s="50" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M36" s="50" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N36" s="50" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O36" s="50" t="inlineStr">
+        <is>
+          <t>Y6</t>
         </is>
       </c>
     </row>
@@ -2751,23 +2749,23 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="J37" s="47" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K37" s="47" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L37" s="47" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="M37" s="47" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="N37" s="47" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="O37" s="47" t="n">
-        <v>0.035</v>
+      <c r="J37" s="51" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="K37" s="51" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="L37" s="51" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M37" s="51" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="N37" s="51" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O37" s="51" t="n">
+        <v>0.0175</v>
       </c>
     </row>
     <row r="38">
@@ -2776,23 +2774,23 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="J38" s="47" t="n">
+      <c r="J38" s="51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K38" s="51" t="n">
         <v>0.03</v>
       </c>
-      <c r="K38" s="47" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L38" s="47" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M38" s="47" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N38" s="47" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O38" s="47" t="n">
-        <v>0.005</v>
+      <c r="L38" s="51" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M38" s="51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N38" s="51" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O38" s="51" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="39">
@@ -2801,29 +2799,29 @@
           <t>Bull</t>
         </is>
       </c>
-      <c r="J39" s="47" t="n">
+      <c r="J39" s="51" t="n">
         <v>0.02</v>
       </c>
-      <c r="K39" s="47" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L39" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="47" t="n">
-        <v>0</v>
+      <c r="K39" s="51" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L39" s="51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M39" s="51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N39" s="51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O39" s="51" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="26" t="inlineStr">
         <is>
-          <t>EFFECTIVE RENT GROWTH (derived)</t>
+          <t>CONCESSIONS (months, editable)</t>
         </is>
       </c>
     </row>
@@ -2833,29 +2831,23 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="J41" s="45">
-        <f>(1+J33)*(1-J37)-1</f>
-        <v/>
-      </c>
-      <c r="K41" s="45">
-        <f>(1+K33)*(1-K37)/(1-J37)-1</f>
-        <v/>
-      </c>
-      <c r="L41" s="45">
-        <f>(1+L33)*(1-L37)/(1-K37)-1</f>
-        <v/>
-      </c>
-      <c r="M41" s="45">
-        <f>(1+M33)*(1-M37)/(1-L37)-1</f>
-        <v/>
-      </c>
-      <c r="N41" s="45">
-        <f>(1+N33)*(1-N37)/(1-M37)-1</f>
-        <v/>
-      </c>
-      <c r="O41" s="45">
-        <f>(1+O33)*(1-O37)/(1-N37)-1</f>
-        <v/>
+      <c r="J41" s="51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K41" s="51" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L41" s="51" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M41" s="51" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N41" s="51" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O41" s="51" t="n">
+        <v>0.035</v>
       </c>
     </row>
     <row r="42">
@@ -2864,29 +2856,23 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="J42" s="45">
-        <f>(1+J34)*(1-J38)-1</f>
-        <v/>
-      </c>
-      <c r="K42" s="45">
-        <f>(1+K34)*(1-K38)/(1-J38)-1</f>
-        <v/>
-      </c>
-      <c r="L42" s="45">
-        <f>(1+L34)*(1-L38)/(1-K38)-1</f>
-        <v/>
-      </c>
-      <c r="M42" s="45">
-        <f>(1+M34)*(1-M38)/(1-L38)-1</f>
-        <v/>
-      </c>
-      <c r="N42" s="45">
-        <f>(1+N34)*(1-N38)/(1-M38)-1</f>
-        <v/>
-      </c>
-      <c r="O42" s="45">
-        <f>(1+O34)*(1-O38)/(1-N38)-1</f>
-        <v/>
+      <c r="J42" s="51" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K42" s="51" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L42" s="51" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M42" s="51" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N42" s="51" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O42" s="51" t="n">
+        <v>0.005</v>
       </c>
     </row>
     <row r="43">
@@ -2895,47 +2881,141 @@
           <t>Bull</t>
         </is>
       </c>
-      <c r="J43" s="45">
-        <f>(1+J35)*(1-J39)-1</f>
-        <v/>
-      </c>
-      <c r="K43" s="45">
-        <f>(1+K35)*(1-K39)/(1-J39)-1</f>
-        <v/>
-      </c>
-      <c r="L43" s="45">
-        <f>(1+L35)*(1-L39)/(1-K39)-1</f>
-        <v/>
-      </c>
-      <c r="M43" s="45">
-        <f>(1+M35)*(1-M39)/(1-L39)-1</f>
-        <v/>
-      </c>
-      <c r="N43" s="45">
-        <f>(1+N35)*(1-N39)/(1-M39)-1</f>
-        <v/>
-      </c>
-      <c r="O43" s="45">
-        <f>(1+O35)*(1-O39)/(1-N39)-1</f>
-        <v/>
+      <c r="J43" s="51" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K43" s="51" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L43" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="19" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>EFFECTIVE RENT GROWTH (derived)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J45" s="49">
+        <f>(1+J37)*(1-J41)-1</f>
+        <v/>
+      </c>
+      <c r="K45" s="49">
+        <f>(1+K37)*(1-K41)/(1-J41)-1</f>
+        <v/>
+      </c>
+      <c r="L45" s="49">
+        <f>(1+L37)*(1-L41)/(1-K41)-1</f>
+        <v/>
+      </c>
+      <c r="M45" s="49">
+        <f>(1+M37)*(1-M41)/(1-L41)-1</f>
+        <v/>
+      </c>
+      <c r="N45" s="49">
+        <f>(1+N37)*(1-N41)/(1-M41)-1</f>
+        <v/>
+      </c>
+      <c r="O45" s="49">
+        <f>(1+O37)*(1-O41)/(1-N41)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J46" s="49">
+        <f>(1+J38)*(1-J42)-1</f>
+        <v/>
+      </c>
+      <c r="K46" s="49">
+        <f>(1+K38)*(1-K42)/(1-J42)-1</f>
+        <v/>
+      </c>
+      <c r="L46" s="49">
+        <f>(1+L38)*(1-L42)/(1-K42)-1</f>
+        <v/>
+      </c>
+      <c r="M46" s="49">
+        <f>(1+M38)*(1-M42)/(1-L42)-1</f>
+        <v/>
+      </c>
+      <c r="N46" s="49">
+        <f>(1+N38)*(1-N42)/(1-M42)-1</f>
+        <v/>
+      </c>
+      <c r="O46" s="49">
+        <f>(1+O38)*(1-O42)/(1-N42)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J47" s="49">
+        <f>(1+J39)*(1-J43)-1</f>
+        <v/>
+      </c>
+      <c r="K47" s="49">
+        <f>(1+K39)*(1-K43)/(1-J43)-1</f>
+        <v/>
+      </c>
+      <c r="L47" s="49">
+        <f>(1+L39)*(1-L43)/(1-K43)-1</f>
+        <v/>
+      </c>
+      <c r="M47" s="49">
+        <f>(1+M39)*(1-M43)/(1-L43)-1</f>
+        <v/>
+      </c>
+      <c r="N47" s="49">
+        <f>(1+N39)*(1-N43)/(1-M43)-1</f>
+        <v/>
+      </c>
+      <c r="O47" s="49">
+        <f>(1+O39)*(1-O43)/(1-N43)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>Reconciliation: UC pipeline scheduled = 0 units vs CoStar current Under Construction = 27 units.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="19" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>Note: as-of quarter (2026 Q2 QTD) is partial (quarter-to-date). Occupancy is point-in-time (valid); Y0 supply/absorption sums for that quarter are partial.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="19" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += UC (linked from Competitive Analysis) + proposed built this scenario; occupied += selected demand (capped at target). Yellow cells are editable.</t>
         </is>

--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +91,11 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF000000"/>
       <sz val="8"/>
     </font>
@@ -251,9 +256,6 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -270,9 +272,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -294,6 +293,9 @@
     <xf numFmtId="164" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -304,6 +306,7 @@
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -775,35 +778,39 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>The Mill at Loggers Creek</t>
+          <t>The Timbers at Harris Ranch</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>125</v>
+        <v>274</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q2 2023</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.92</v>
+        <v>0.967153</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>2104</v>
+        <v>2196</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Baron Properties</t>
+          <t>Highland Canyon Partners</t>
         </is>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="n"/>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Year built: 2023/2024; Occ: CoStar 97% vs RealPage 100%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="7" t="n">
@@ -851,39 +858,35 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>The Timbers at Harris Ranch</t>
+          <t>The Mill at Loggers Creek</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>274</v>
+        <v>125</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Q2 2023</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.967153</v>
+        <v>0.92</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>2196</v>
+        <v>2104</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Highland Canyon Partners</t>
+          <t>Baron Properties</t>
         </is>
       </c>
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>Year built: 2023/2024; Occ: CoStar 97% vs RealPage 100%</t>
-        </is>
-      </c>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="12" t="n"/>
@@ -899,15 +902,15 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Vista Point</t>
+          <t>Harris Ranch East</t>
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>893</v>
+        <v>59</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Q4 2026</t>
         </is>
       </c>
       <c r="F11" s="17" t="n"/>
@@ -924,7 +927,7 @@
       <c r="I11" s="14" t="n"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K11" s="15" t="inlineStr">
@@ -939,15 +942,15 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>3300 South Vista Avenue</t>
+          <t>Station Village</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Q1 2028</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F12" s="17" t="n"/>
@@ -958,13 +961,13 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I12" s="14" t="n"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K12" s="15" t="inlineStr">
@@ -979,15 +982,15 @@
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Seasons on the Bench</t>
+          <t>1519 South Londoner Avenue</t>
         </is>
       </c>
       <c r="D13" s="16" t="n">
-        <v>358</v>
+        <v>189</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="F13" s="17" t="n"/>
@@ -1019,15 +1022,15 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>1519 South Londoner Avenue</t>
+          <t>Seasons on the Bench</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>189</v>
+        <v>358</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="F14" s="17" t="n"/>
@@ -1059,15 +1062,15 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Station Village</t>
+          <t>3300 South Vista Avenue</t>
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="F15" s="17" t="n"/>
@@ -1078,13 +1081,13 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" s="14" t="n"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K15" s="15" t="inlineStr">
@@ -1099,15 +1102,15 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Harris Ranch East</t>
+          <t>Vista Point</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>59</v>
+        <v>893</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Q4 2026</t>
+          <t>Q2 2028</t>
         </is>
       </c>
       <c r="F16" s="17" t="n"/>
@@ -1124,7 +1127,7 @@
       <c r="I16" s="14" t="n"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K16" s="15" t="inlineStr">
@@ -1155,10 +1158,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Z52"/>
+  <dimension ref="B1:Z60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1179,19 +1182,19 @@
     <col width="28" customWidth="1" min="18" max="18"/>
     <col width="7" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="8" customWidth="1" min="22" max="22"/>
     <col hidden="1" width="7" customWidth="1" min="23" max="23"/>
     <col hidden="1" width="6" customWidth="1" min="24" max="24"/>
     <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="14.4" customHeight="1">
       <c r="Z1" t="n">
         <v>8105</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SUPPLY &amp; ABSORPTION  —  5-MILE MARKET (relative-year / TTM)</t>
@@ -1202,7 +1205,7 @@
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="14.4" customHeight="1">
       <c r="R3" s="20" t="inlineStr">
         <is>
           <t>UNDER CONSTRUCTION (linked from Competitive Analysis)</t>
@@ -1213,7 +1216,7 @@
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="14.4" customHeight="1">
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t>As-of Quarter</t>
@@ -1240,7 +1243,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="14.4" customHeight="1">
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Close Quarter (Y1 start)</t>
@@ -1252,7 +1255,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="14.4" customHeight="1">
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Stabilization Target</t>
@@ -1262,7 +1265,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="14.4" customHeight="1">
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Demand Scenario</t>
@@ -1279,7 +1282,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="14.4" customHeight="1">
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Bear Annual Absorption</t>
@@ -1309,7 +1312,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="14.4" customHeight="1">
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Base Annual Absorption</t>
@@ -1349,7 +1352,7 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="14.4" customHeight="1">
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Bull Annual Absorption</t>
@@ -1389,7 +1392,7 @@
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="14.4" customHeight="1">
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Selected Annual Demand</t>
@@ -1430,17 +1433,7 @@
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>UC scheduled vs CoStar UC</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>0 / 27</t>
-        </is>
-      </c>
+    <row r="12" ht="14.4" customHeight="1">
       <c r="R12" s="27" t="inlineStr">
         <is>
           <t>3300 South Vista Avenue</t>
@@ -1472,17 +1465,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>Subject rent source</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+    <row r="13" ht="14.4" customHeight="1">
       <c r="R13" s="27" t="inlineStr">
         <is>
           <t>Station Village</t>
@@ -1514,7 +1497,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="14.4" customHeight="1">
       <c r="R14" s="27" t="inlineStr">
         <is>
           <t>Harris Ranch East</t>
@@ -1546,7 +1529,9 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="15" ht="14.4" customHeight="1"/>
+    <row r="16" ht="14.4" customHeight="1"/>
+    <row r="17" ht="14.4" customHeight="1">
       <c r="B17" s="21" t="inlineStr">
         <is>
           <t>5-MILE MARKET</t>
@@ -1587,426 +1572,396 @@
           <t>Y0</t>
         </is>
       </c>
-      <c r="J17" s="32" t="inlineStr">
+      <c r="J17" s="31" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K17" s="32" t="inlineStr">
+      <c r="K17" s="31" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L17" s="32" t="inlineStr">
+      <c r="L17" s="31" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M17" s="32" t="inlineStr">
+      <c r="M17" s="31" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N17" s="32" t="inlineStr">
+      <c r="N17" s="31" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O17" s="32" t="inlineStr">
+      <c r="O17" s="31" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="C18" s="33" t="inlineStr">
-        <is>
-          <t>Q3 2019–Q2 2020</t>
-        </is>
-      </c>
-      <c r="D18" s="33" t="inlineStr">
-        <is>
-          <t>Q3 2020–Q2 2021</t>
-        </is>
-      </c>
-      <c r="E18" s="33" t="inlineStr">
-        <is>
-          <t>Q3 2021–Q2 2022</t>
-        </is>
-      </c>
-      <c r="F18" s="33" t="inlineStr">
-        <is>
-          <t>Q3 2022–Q2 2023</t>
-        </is>
-      </c>
-      <c r="G18" s="33" t="inlineStr">
-        <is>
-          <t>Q3 2023–Q2 2024</t>
-        </is>
-      </c>
-      <c r="H18" s="33" t="inlineStr">
-        <is>
-          <t>Q3 2024–Q2 2025</t>
-        </is>
-      </c>
-      <c r="I18" s="33" t="inlineStr">
-        <is>
-          <t>Q3 2025–Q2 2026</t>
-        </is>
-      </c>
-      <c r="J18" s="33" t="inlineStr">
+    <row r="18" ht="14.4" customHeight="1">
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>Q3'19-Q2'20</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>Q3'20-Q2'21</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>Q3'21-Q2'22</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>Q3'22-Q2'23</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="inlineStr">
+        <is>
+          <t>Q3'23-Q2'24</t>
+        </is>
+      </c>
+      <c r="H18" s="32" t="inlineStr">
+        <is>
+          <t>Q3'24-Q2'25</t>
+        </is>
+      </c>
+      <c r="I18" s="32" t="inlineStr">
+        <is>
+          <t>Q3'25-Q2'26</t>
+        </is>
+      </c>
+      <c r="J18" s="32" t="inlineStr">
         <is>
           <t>Hold Yr 1</t>
         </is>
       </c>
-      <c r="K18" s="33" t="inlineStr">
+      <c r="K18" s="32" t="inlineStr">
         <is>
           <t>Hold Yr 2</t>
         </is>
       </c>
-      <c r="L18" s="33" t="inlineStr">
+      <c r="L18" s="32" t="inlineStr">
         <is>
           <t>Hold Yr 3</t>
         </is>
       </c>
-      <c r="M18" s="33" t="inlineStr">
+      <c r="M18" s="32" t="inlineStr">
         <is>
           <t>Hold Yr 4</t>
         </is>
       </c>
-      <c r="N18" s="33" t="inlineStr">
+      <c r="N18" s="32" t="inlineStr">
         <is>
           <t>Hold Yr 5</t>
         </is>
       </c>
-      <c r="O18" s="33" t="inlineStr">
+      <c r="O18" s="32" t="inlineStr">
         <is>
           <t>Hold Yr 6</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="14.4" customHeight="1">
       <c r="B19" s="21" t="inlineStr">
         <is>
           <t>NEW SUPPLY (5-mi)</t>
         </is>
       </c>
-      <c r="C19" s="34" t="n">
+      <c r="C19" s="33" t="n">
         <v>213</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="33" t="n">
         <v>237</v>
       </c>
-      <c r="E19" s="34" t="n">
+      <c r="E19" s="33" t="n">
         <v>33</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="33" t="n">
         <v>289</v>
       </c>
-      <c r="G19" s="34" t="n">
+      <c r="G19" s="33" t="n">
         <v>178</v>
       </c>
-      <c r="H19" s="34" t="n">
+      <c r="H19" s="33" t="n">
         <v>334</v>
       </c>
-      <c r="I19" s="34" t="n">
+      <c r="I19" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="34">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,1)+SUMIFS($S$9:$S$14,$W$9:$W$14,1,$X$9:$X$14,1)</f>
         <v/>
       </c>
-      <c r="K19" s="35">
+      <c r="K19" s="34">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,2)+SUMIFS($S$9:$S$14,$W$9:$W$14,2,$X$9:$X$14,1)</f>
         <v/>
       </c>
-      <c r="L19" s="35">
+      <c r="L19" s="34">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,3)+SUMIFS($S$9:$S$14,$W$9:$W$14,3,$X$9:$X$14,1)</f>
         <v/>
       </c>
-      <c r="M19" s="35">
+      <c r="M19" s="34">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,4)+SUMIFS($S$9:$S$14,$W$9:$W$14,4,$X$9:$X$14,1)</f>
         <v/>
       </c>
-      <c r="N19" s="35">
+      <c r="N19" s="34">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,5)+SUMIFS($S$9:$S$14,$W$9:$W$14,5,$X$9:$X$14,1)</f>
         <v/>
       </c>
-      <c r="O19" s="35">
+      <c r="O19" s="34">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,6)+SUMIFS($S$9:$S$14,$W$9:$W$14,6,$X$9:$X$14,1)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="14.4" customHeight="1">
       <c r="B20" s="21" t="inlineStr">
         <is>
           <t>ABSORPTION (5-mi)</t>
         </is>
       </c>
-      <c r="C20" s="34" t="n">
+      <c r="C20" s="33" t="n">
         <v>213</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="33" t="n">
         <v>150</v>
       </c>
-      <c r="E20" s="34" t="n">
+      <c r="E20" s="33" t="n">
         <v>86</v>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F20" s="33" t="n">
         <v>-91</v>
       </c>
-      <c r="G20" s="34" t="n">
+      <c r="G20" s="33" t="n">
         <v>277</v>
       </c>
-      <c r="H20" s="34" t="n">
+      <c r="H20" s="33" t="n">
         <v>399</v>
       </c>
-      <c r="I20" s="34" t="n">
+      <c r="I20" s="33" t="n">
         <v>216</v>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="34">
         <f>J31-I31</f>
         <v/>
       </c>
-      <c r="K20" s="35">
+      <c r="K20" s="34">
         <f>K31-J31</f>
         <v/>
       </c>
-      <c r="L20" s="35">
+      <c r="L20" s="34">
         <f>L31-K31</f>
         <v/>
       </c>
-      <c r="M20" s="35">
+      <c r="M20" s="34">
         <f>M31-L31</f>
         <v/>
       </c>
-      <c r="N20" s="35">
+      <c r="N20" s="34">
         <f>N31-M31</f>
         <v/>
       </c>
-      <c r="O20" s="35">
+      <c r="O20" s="34">
         <f>O31-N31</f>
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="14.4" customHeight="1">
       <c r="B21" s="21" t="inlineStr">
         <is>
           <t>OCCUPANCY (5-mi)</t>
         </is>
       </c>
-      <c r="C21" s="36" t="n">
+      <c r="C21" s="35" t="n">
         <v>0.968</v>
       </c>
-      <c r="D21" s="36" t="n">
+      <c r="D21" s="35" t="n">
         <v>0.953</v>
       </c>
-      <c r="E21" s="36" t="n">
+      <c r="E21" s="35" t="n">
         <v>0.963</v>
       </c>
-      <c r="F21" s="36" t="n">
+      <c r="F21" s="35" t="n">
         <v>0.895</v>
       </c>
-      <c r="G21" s="36" t="n">
+      <c r="G21" s="35" t="n">
         <v>0.916</v>
       </c>
-      <c r="H21" s="36" t="n">
+      <c r="H21" s="35" t="n">
         <v>0.9320000000000001</v>
       </c>
-      <c r="I21" s="36" t="n">
+      <c r="I21" s="35" t="n">
         <v>0.967</v>
       </c>
-      <c r="J21" s="37">
+      <c r="J21" s="36">
         <f>IFERROR(J31/J30,0)</f>
         <v/>
       </c>
-      <c r="K21" s="37">
+      <c r="K21" s="36">
         <f>IFERROR(K31/K30,0)</f>
         <v/>
       </c>
-      <c r="L21" s="37">
+      <c r="L21" s="36">
         <f>IFERROR(L31/L30,0)</f>
         <v/>
       </c>
-      <c r="M21" s="37">
+      <c r="M21" s="36">
         <f>IFERROR(M31/M30,0)</f>
         <v/>
       </c>
-      <c r="N21" s="37">
+      <c r="N21" s="36">
         <f>IFERROR(N31/N30,0)</f>
         <v/>
       </c>
-      <c r="O21" s="37">
+      <c r="O21" s="36">
         <f>IFERROR(O31/O30,0)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="14.4" customHeight="1">
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>CUM. UNABSORBED (since -Y3)</t>
-        </is>
-      </c>
-      <c r="C22" s="38" t="n"/>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="38" t="n"/>
-      <c r="F22" s="38">
-        <f>F19-F20</f>
-        <v/>
-      </c>
-      <c r="G22" s="38">
-        <f>F22+G19-G20</f>
-        <v/>
-      </c>
-      <c r="H22" s="38">
-        <f>G22+H19-H20</f>
-        <v/>
-      </c>
-      <c r="I22" s="38">
-        <f>H22+I19-I20</f>
-        <v/>
-      </c>
-      <c r="J22" s="38">
-        <f>I22+J19-J20</f>
-        <v/>
-      </c>
-      <c r="K22" s="38">
-        <f>J22+K19-K20</f>
-        <v/>
-      </c>
-      <c r="L22" s="38">
-        <f>K22+L19-L20</f>
-        <v/>
-      </c>
-      <c r="M22" s="38">
-        <f>L22+M19-M20</f>
-        <v/>
-      </c>
-      <c r="N22" s="38">
-        <f>M22+N19-N20</f>
-        <v/>
-      </c>
-      <c r="O22" s="38">
-        <f>N22+O19-O20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
+          <t>SUBJECT (Canyon Ridge)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="14.4" customHeight="1">
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>SUBJECT (Canyon Ridge)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve">  Market Rent  (CoStar→HD)</t>
         </is>
       </c>
-      <c r="C24" s="39" t="n"/>
-      <c r="D24" s="39" t="n"/>
-      <c r="E24" s="39" t="n"/>
-      <c r="F24" s="39" t="n"/>
-      <c r="G24" s="39" t="n"/>
-      <c r="H24" s="39" t="n"/>
-      <c r="I24" s="39" t="n"/>
-      <c r="J24" s="40" t="n"/>
-      <c r="K24" s="40" t="n"/>
-      <c r="L24" s="40" t="n"/>
-      <c r="M24" s="40" t="n"/>
-      <c r="N24" s="40" t="n"/>
-      <c r="O24" s="40" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="41" t="inlineStr">
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="37" t="n"/>
+      <c r="H23" s="37" t="n"/>
+      <c r="I23" s="37" t="n"/>
+      <c r="J23" s="38" t="n"/>
+      <c r="K23" s="38" t="n"/>
+      <c r="L23" s="38" t="n"/>
+      <c r="M23" s="38" t="n"/>
+      <c r="N23" s="38" t="n"/>
+      <c r="O23" s="38" t="n"/>
+    </row>
+    <row r="24" ht="14.4" customHeight="1">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">    Market Rent YoY %</t>
         </is>
       </c>
-      <c r="C25" s="42" t="n"/>
-      <c r="D25" s="42">
-        <f>IFERROR(D24/C24-1,"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="42">
-        <f>IFERROR(E24/D24-1,"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="42">
-        <f>IFERROR(F24/E24-1,"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="42">
-        <f>IFERROR(G24/F24-1,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="42">
-        <f>IFERROR(H24/G24-1,"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="42">
-        <f>IFERROR(I24/H24-1,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="43" t="n"/>
-      <c r="K25" s="43" t="n"/>
-      <c r="L25" s="43" t="n"/>
-      <c r="M25" s="43" t="n"/>
-      <c r="N25" s="43" t="n"/>
-      <c r="O25" s="43" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="21" t="inlineStr">
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40">
+        <f>IFERROR(D23/C23-1,"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="40">
+        <f>IFERROR(E23/D23-1,"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="40">
+        <f>IFERROR(F23/E23-1,"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="40">
+        <f>IFERROR(G23/F23-1,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="40">
+        <f>IFERROR(H23/G23-1,"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="40">
+        <f>IFERROR(I23/H23-1,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="41" t="n"/>
+      <c r="K24" s="41" t="n"/>
+      <c r="L24" s="41" t="n"/>
+      <c r="M24" s="41" t="n"/>
+      <c r="N24" s="41" t="n"/>
+      <c r="O24" s="41" t="n"/>
+    </row>
+    <row r="25" ht="14.4" customHeight="1">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Effective Rent</t>
         </is>
       </c>
-      <c r="C26" s="39" t="n"/>
-      <c r="D26" s="39" t="n"/>
-      <c r="E26" s="39" t="n"/>
-      <c r="F26" s="39" t="n"/>
-      <c r="G26" s="39" t="n"/>
-      <c r="H26" s="39" t="n"/>
-      <c r="I26" s="39" t="n"/>
-      <c r="J26" s="40" t="n"/>
-      <c r="K26" s="40" t="n"/>
-      <c r="L26" s="40" t="n"/>
-      <c r="M26" s="40" t="n"/>
-      <c r="N26" s="40" t="n"/>
-      <c r="O26" s="40" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="41" t="inlineStr">
+      <c r="C25" s="37" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="37" t="n"/>
+      <c r="G25" s="37" t="n"/>
+      <c r="H25" s="37" t="n"/>
+      <c r="I25" s="37" t="n"/>
+      <c r="J25" s="38" t="n"/>
+      <c r="K25" s="38" t="n"/>
+      <c r="L25" s="38" t="n"/>
+      <c r="M25" s="38" t="n"/>
+      <c r="N25" s="38" t="n"/>
+      <c r="O25" s="38" t="n"/>
+    </row>
+    <row r="26" ht="14.4" customHeight="1">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">    Effective Rent YoY %</t>
         </is>
       </c>
+      <c r="C26" s="40" t="n"/>
+      <c r="D26" s="40">
+        <f>IFERROR(D25/C25-1,"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="40">
+        <f>IFERROR(E25/D25-1,"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="40">
+        <f>IFERROR(F25/E25-1,"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="40">
+        <f>IFERROR(G25/F25-1,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="40">
+        <f>IFERROR(H25/G25-1,"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="40">
+        <f>IFERROR(I25/H25-1,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="41" t="n"/>
+      <c r="K26" s="41" t="n"/>
+      <c r="L26" s="41" t="n"/>
+      <c r="M26" s="41" t="n"/>
+      <c r="N26" s="41" t="n"/>
+      <c r="O26" s="41" t="n"/>
+    </row>
+    <row r="27" ht="14.4" customHeight="1">
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Occupancy (financials / CoStar)</t>
+        </is>
+      </c>
       <c r="C27" s="42" t="n"/>
-      <c r="D27" s="42">
-        <f>IFERROR(D26/C26-1,"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="42">
-        <f>IFERROR(E26/D26-1,"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="42">
-        <f>IFERROR(F26/E26-1,"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="42">
-        <f>IFERROR(G26/F26-1,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="42">
-        <f>IFERROR(H26/G26-1,"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="42">
-        <f>IFERROR(I26/H26-1,"")</f>
-        <v/>
-      </c>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="F27" s="42" t="n"/>
+      <c r="G27" s="42" t="n"/>
+      <c r="H27" s="42" t="n"/>
+      <c r="I27" s="42" t="n"/>
       <c r="J27" s="43" t="n"/>
       <c r="K27" s="43" t="n"/>
       <c r="L27" s="43" t="n"/>
@@ -2014,575 +1969,670 @@
       <c r="N27" s="43" t="n"/>
       <c r="O27" s="43" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="14.4" customHeight="1">
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Occupancy (financials / CoStar)</t>
-        </is>
-      </c>
-      <c r="C28" s="44" t="n"/>
-      <c r="D28" s="44" t="n"/>
-      <c r="E28" s="44" t="n"/>
-      <c r="F28" s="44" t="n"/>
-      <c r="G28" s="44" t="n"/>
-      <c r="H28" s="44" t="n"/>
-      <c r="I28" s="44" t="n"/>
-      <c r="J28" s="45" t="n"/>
-      <c r="K28" s="45" t="n"/>
-      <c r="L28" s="45" t="n"/>
-      <c r="M28" s="45" t="n"/>
-      <c r="N28" s="45" t="n"/>
-      <c r="O28" s="45" t="n"/>
-    </row>
-    <row r="30" hidden="1">
+          <t xml:space="preserve">  Concession %</t>
+        </is>
+      </c>
+      <c r="C28" s="42" t="n"/>
+      <c r="D28" s="42" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="F28" s="42" t="n"/>
+      <c r="G28" s="42" t="n"/>
+      <c r="H28" s="42" t="n"/>
+      <c r="I28" s="42" t="n"/>
+      <c r="J28" s="43" t="n"/>
+      <c r="K28" s="43" t="n"/>
+      <c r="L28" s="43" t="n"/>
+      <c r="M28" s="43" t="n"/>
+      <c r="N28" s="43" t="n"/>
+      <c r="O28" s="43" t="n"/>
+    </row>
+    <row r="29" ht="14.4" customHeight="1"/>
+    <row r="30" hidden="1" ht="14.4" customHeight="1">
       <c r="B30" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  inventory</t>
         </is>
       </c>
-      <c r="C30" s="38" t="n">
+      <c r="C30" s="44" t="n">
         <v>4845</v>
       </c>
-      <c r="D30" s="38" t="n">
+      <c r="D30" s="44" t="n">
         <v>5082</v>
       </c>
-      <c r="E30" s="38" t="n">
+      <c r="E30" s="44" t="n">
         <v>5115</v>
       </c>
-      <c r="F30" s="38" t="n">
+      <c r="F30" s="44" t="n">
         <v>5404</v>
       </c>
-      <c r="G30" s="38" t="n">
+      <c r="G30" s="44" t="n">
         <v>5582</v>
       </c>
-      <c r="H30" s="38" t="n">
+      <c r="H30" s="44" t="n">
         <v>5916</v>
       </c>
-      <c r="I30" s="38" t="n">
+      <c r="I30" s="44" t="n">
         <v>5925</v>
       </c>
-      <c r="J30" s="38">
+      <c r="J30" s="44">
         <f>I30+J19</f>
         <v/>
       </c>
-      <c r="K30" s="38">
+      <c r="K30" s="44">
         <f>J30+K19</f>
         <v/>
       </c>
-      <c r="L30" s="38">
+      <c r="L30" s="44">
         <f>K30+L19</f>
         <v/>
       </c>
-      <c r="M30" s="38">
+      <c r="M30" s="44">
         <f>L30+M19</f>
         <v/>
       </c>
-      <c r="N30" s="38">
+      <c r="N30" s="44">
         <f>M30+N19</f>
         <v/>
       </c>
-      <c r="O30" s="38">
+      <c r="O30" s="44">
         <f>N30+O19</f>
         <v/>
       </c>
     </row>
-    <row r="31" hidden="1">
+    <row r="31" hidden="1" ht="14.4" customHeight="1">
       <c r="B31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  occupied</t>
         </is>
       </c>
-      <c r="C31" s="38" t="n">
+      <c r="C31" s="44" t="n">
         <v>4691</v>
       </c>
-      <c r="D31" s="38" t="n">
+      <c r="D31" s="44" t="n">
         <v>4841</v>
       </c>
-      <c r="E31" s="38" t="n">
+      <c r="E31" s="44" t="n">
         <v>4927</v>
       </c>
-      <c r="F31" s="38" t="n">
+      <c r="F31" s="44" t="n">
         <v>4836</v>
       </c>
-      <c r="G31" s="38" t="n">
+      <c r="G31" s="44" t="n">
         <v>5113</v>
       </c>
-      <c r="H31" s="38" t="n">
+      <c r="H31" s="44" t="n">
         <v>5512</v>
       </c>
-      <c r="I31" s="38" t="n">
+      <c r="I31" s="44" t="n">
         <v>5727</v>
       </c>
-      <c r="J31" s="38">
+      <c r="J31" s="44">
         <f>MIN($C$6*J30,I31+$C$11)</f>
         <v/>
       </c>
-      <c r="K31" s="38">
+      <c r="K31" s="44">
         <f>MIN($C$6*K30,J31+$C$11)</f>
         <v/>
       </c>
-      <c r="L31" s="38">
+      <c r="L31" s="44">
         <f>MIN($C$6*L30,K31+$C$11)</f>
         <v/>
       </c>
-      <c r="M31" s="38">
+      <c r="M31" s="44">
         <f>MIN($C$6*M30,L31+$C$11)</f>
         <v/>
       </c>
-      <c r="N31" s="38">
+      <c r="N31" s="44">
         <f>MIN($C$6*N30,M31+$C$11)</f>
         <v/>
       </c>
-      <c r="O31" s="38">
+      <c r="O31" s="44">
         <f>MIN($C$6*O30,N31+$C$11)</f>
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="32" ht="14.4" customHeight="1"/>
+    <row r="33" ht="14.4" customHeight="1">
       <c r="B33" s="21" t="inlineStr">
         <is>
           <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
         </is>
       </c>
-      <c r="J33" s="46" t="inlineStr">
+      <c r="J33" s="45" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K33" s="46" t="inlineStr">
+      <c r="K33" s="45" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L33" s="46" t="inlineStr">
+      <c r="L33" s="45" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M33" s="46" t="inlineStr">
+      <c r="M33" s="45" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N33" s="46" t="inlineStr">
+      <c r="N33" s="45" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O33" s="46" t="inlineStr">
+      <c r="O33" s="45" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="14.4" customHeight="1">
       <c r="B34" s="21" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J34" s="47">
+      <c r="J34" s="46">
         <f>MIN($C$6,($I$31+$C$8*1)/J30)</f>
         <v/>
       </c>
-      <c r="K34" s="47">
+      <c r="K34" s="46">
         <f>MIN($C$6,($I$31+$C$8*2)/K30)</f>
         <v/>
       </c>
-      <c r="L34" s="47">
+      <c r="L34" s="46">
         <f>MIN($C$6,($I$31+$C$8*3)/L30)</f>
         <v/>
       </c>
-      <c r="M34" s="47">
+      <c r="M34" s="46">
         <f>MIN($C$6,($I$31+$C$8*4)/M30)</f>
         <v/>
       </c>
-      <c r="N34" s="47">
+      <c r="N34" s="46">
         <f>MIN($C$6,($I$31+$C$8*5)/N30)</f>
         <v/>
       </c>
-      <c r="O34" s="47">
+      <c r="O34" s="46">
         <f>MIN($C$6,($I$31+$C$8*6)/O30)</f>
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="14.4" customHeight="1">
       <c r="B35" s="21" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J35" s="47">
+      <c r="J35" s="46">
         <f>MIN($C$6,($I$31+$C$9*1)/J30)</f>
         <v/>
       </c>
-      <c r="K35" s="47">
+      <c r="K35" s="46">
         <f>MIN($C$6,($I$31+$C$9*2)/K30)</f>
         <v/>
       </c>
-      <c r="L35" s="47">
+      <c r="L35" s="46">
         <f>MIN($C$6,($I$31+$C$9*3)/L30)</f>
         <v/>
       </c>
-      <c r="M35" s="47">
+      <c r="M35" s="46">
         <f>MIN($C$6,($I$31+$C$9*4)/M30)</f>
         <v/>
       </c>
-      <c r="N35" s="47">
+      <c r="N35" s="46">
         <f>MIN($C$6,($I$31+$C$9*5)/N30)</f>
         <v/>
       </c>
-      <c r="O35" s="47">
+      <c r="O35" s="46">
         <f>MIN($C$6,($I$31+$C$9*6)/O30)</f>
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="14.4" customHeight="1">
       <c r="B36" s="21" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J36" s="47">
+      <c r="J36" s="46">
         <f>MIN($C$6,($I$31+$C$10*1)/J30)</f>
         <v/>
       </c>
-      <c r="K36" s="47">
+      <c r="K36" s="46">
         <f>MIN($C$6,($I$31+$C$10*2)/K30)</f>
         <v/>
       </c>
-      <c r="L36" s="47">
+      <c r="L36" s="46">
         <f>MIN($C$6,($I$31+$C$10*3)/L30)</f>
         <v/>
       </c>
-      <c r="M36" s="47">
+      <c r="M36" s="46">
         <f>MIN($C$6,($I$31+$C$10*4)/M30)</f>
         <v/>
       </c>
-      <c r="N36" s="47">
+      <c r="N36" s="46">
         <f>MIN($C$6,($I$31+$C$10*5)/N30)</f>
         <v/>
       </c>
-      <c r="O36" s="47">
+      <c r="O36" s="46">
         <f>MIN($C$6,($I$31+$C$10*6)/O30)</f>
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="37" ht="14.4" customHeight="1"/>
+    <row r="38" ht="14.4" customHeight="1">
       <c r="B38" s="21" t="inlineStr">
         <is>
           <t>MARKET RENT GROWTH (editable assumptions)</t>
         </is>
       </c>
-      <c r="J38" s="48" t="inlineStr">
+      <c r="J38" s="47" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K38" s="48" t="inlineStr">
+      <c r="K38" s="47" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L38" s="48" t="inlineStr">
+      <c r="L38" s="47" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M38" s="48" t="inlineStr">
+      <c r="M38" s="47" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N38" s="48" t="inlineStr">
+      <c r="N38" s="47" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O38" s="48" t="inlineStr">
+      <c r="O38" s="47" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="14.4" customHeight="1">
       <c r="B39" s="21" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J39" s="49" t="n">
+      <c r="J39" s="48" t="n">
         <v>-0.0025</v>
       </c>
-      <c r="K39" s="49" t="n">
+      <c r="K39" s="48" t="n">
         <v>0.0175</v>
       </c>
-      <c r="L39" s="49" t="n">
+      <c r="L39" s="48" t="n">
         <v>0.0275</v>
       </c>
-      <c r="M39" s="49" t="n">
+      <c r="M39" s="48" t="n">
         <v>0.0375</v>
       </c>
-      <c r="N39" s="49" t="n">
+      <c r="N39" s="48" t="n">
         <v>0.0275</v>
       </c>
-      <c r="O39" s="49" t="n">
+      <c r="O39" s="48" t="n">
         <v>0.0175</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="14.4" customHeight="1">
       <c r="B40" s="21" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J40" s="49" t="n">
+      <c r="J40" s="48" t="n">
         <v>0.01</v>
       </c>
-      <c r="K40" s="49" t="n">
+      <c r="K40" s="48" t="n">
         <v>0.03</v>
       </c>
-      <c r="L40" s="49" t="n">
+      <c r="L40" s="48" t="n">
         <v>0.04</v>
       </c>
-      <c r="M40" s="49" t="n">
+      <c r="M40" s="48" t="n">
         <v>0.05</v>
       </c>
-      <c r="N40" s="49" t="n">
+      <c r="N40" s="48" t="n">
         <v>0.04</v>
       </c>
-      <c r="O40" s="49" t="n">
+      <c r="O40" s="48" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="14.4" customHeight="1">
       <c r="B41" s="21" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J41" s="49" t="n">
+      <c r="J41" s="48" t="n">
         <v>0.02</v>
       </c>
-      <c r="K41" s="49" t="n">
+      <c r="K41" s="48" t="n">
         <v>0.04</v>
       </c>
-      <c r="L41" s="49" t="n">
+      <c r="L41" s="48" t="n">
         <v>0.05</v>
       </c>
-      <c r="M41" s="49" t="n">
+      <c r="M41" s="48" t="n">
         <v>0.06</v>
       </c>
-      <c r="N41" s="49" t="n">
+      <c r="N41" s="48" t="n">
         <v>0.05</v>
       </c>
-      <c r="O41" s="49" t="n">
+      <c r="O41" s="48" t="n">
         <v>0.04</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="14.4" customHeight="1">
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>CONCESSIONS (months, editable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
+          <t>CONCESSIONS % — forward assumption (editable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="14.4" customHeight="1">
       <c r="B43" s="21" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J43" s="49" t="n">
+      <c r="J43" s="48" t="n">
         <v>0.06</v>
       </c>
-      <c r="K43" s="49" t="n">
+      <c r="K43" s="48" t="n">
         <v>0.045</v>
       </c>
-      <c r="L43" s="49" t="n">
+      <c r="L43" s="48" t="n">
         <v>0.035</v>
       </c>
-      <c r="M43" s="49" t="n">
+      <c r="M43" s="48" t="n">
         <v>0.035</v>
       </c>
-      <c r="N43" s="49" t="n">
+      <c r="N43" s="48" t="n">
         <v>0.035</v>
       </c>
-      <c r="O43" s="49" t="n">
+      <c r="O43" s="48" t="n">
         <v>0.035</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="14.4" customHeight="1">
       <c r="B44" s="21" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J44" s="49" t="n">
+      <c r="J44" s="48" t="n">
         <v>0.03</v>
       </c>
-      <c r="K44" s="49" t="n">
+      <c r="K44" s="48" t="n">
         <v>0.015</v>
       </c>
-      <c r="L44" s="49" t="n">
+      <c r="L44" s="48" t="n">
         <v>0.005</v>
       </c>
-      <c r="M44" s="49" t="n">
+      <c r="M44" s="48" t="n">
         <v>0.005</v>
       </c>
-      <c r="N44" s="49" t="n">
+      <c r="N44" s="48" t="n">
         <v>0.005</v>
       </c>
-      <c r="O44" s="49" t="n">
+      <c r="O44" s="48" t="n">
         <v>0.005</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="14.4" customHeight="1">
       <c r="B45" s="21" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J45" s="49" t="n">
+      <c r="J45" s="48" t="n">
         <v>0.02</v>
       </c>
-      <c r="K45" s="49" t="n">
+      <c r="K45" s="48" t="n">
         <v>0.005</v>
       </c>
-      <c r="L45" s="49" t="n">
+      <c r="L45" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="49" t="n">
+      <c r="M45" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="49" t="n">
+      <c r="N45" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="49" t="n">
+      <c r="O45" s="48" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="14.4" customHeight="1">
       <c r="B46" s="21" t="inlineStr">
         <is>
           <t>EFFECTIVE RENT GROWTH (derived)</t>
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="14.4" customHeight="1">
       <c r="B47" s="21" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J47" s="47">
+      <c r="J47" s="46">
         <f>(1+J39)*(1-J43)-1</f>
         <v/>
       </c>
-      <c r="K47" s="47">
+      <c r="K47" s="46">
         <f>(1+K39)*(1-K43)/(1-J43)-1</f>
         <v/>
       </c>
-      <c r="L47" s="47">
+      <c r="L47" s="46">
         <f>(1+L39)*(1-L43)/(1-K43)-1</f>
         <v/>
       </c>
-      <c r="M47" s="47">
+      <c r="M47" s="46">
         <f>(1+M39)*(1-M43)/(1-L43)-1</f>
         <v/>
       </c>
-      <c r="N47" s="47">
+      <c r="N47" s="46">
         <f>(1+N39)*(1-N43)/(1-M43)-1</f>
         <v/>
       </c>
-      <c r="O47" s="47">
+      <c r="O47" s="46">
         <f>(1+O39)*(1-O43)/(1-N43)-1</f>
         <v/>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="14.4" customHeight="1">
       <c r="B48" s="21" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J48" s="47">
+      <c r="J48" s="46">
         <f>(1+J40)*(1-J44)-1</f>
         <v/>
       </c>
-      <c r="K48" s="47">
+      <c r="K48" s="46">
         <f>(1+K40)*(1-K44)/(1-J44)-1</f>
         <v/>
       </c>
-      <c r="L48" s="47">
+      <c r="L48" s="46">
         <f>(1+L40)*(1-L44)/(1-K44)-1</f>
         <v/>
       </c>
-      <c r="M48" s="47">
+      <c r="M48" s="46">
         <f>(1+M40)*(1-M44)/(1-L44)-1</f>
         <v/>
       </c>
-      <c r="N48" s="47">
+      <c r="N48" s="46">
         <f>(1+N40)*(1-N44)/(1-M44)-1</f>
         <v/>
       </c>
-      <c r="O48" s="47">
+      <c r="O48" s="46">
         <f>(1+O40)*(1-O44)/(1-N44)-1</f>
         <v/>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="14.4" customHeight="1">
       <c r="B49" s="21" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J49" s="47">
+      <c r="J49" s="46">
         <f>(1+J41)*(1-J45)-1</f>
         <v/>
       </c>
-      <c r="K49" s="47">
+      <c r="K49" s="46">
         <f>(1+K41)*(1-K45)/(1-J45)-1</f>
         <v/>
       </c>
-      <c r="L49" s="47">
+      <c r="L49" s="46">
         <f>(1+L41)*(1-L45)/(1-K45)-1</f>
         <v/>
       </c>
-      <c r="M49" s="47">
+      <c r="M49" s="46">
         <f>(1+M41)*(1-M45)/(1-L45)-1</f>
         <v/>
       </c>
-      <c r="N49" s="47">
+      <c r="N49" s="46">
         <f>(1+N41)*(1-N45)/(1-M45)-1</f>
         <v/>
       </c>
-      <c r="O49" s="47">
+      <c r="O49" s="46">
         <f>(1+O41)*(1-O45)/(1-N45)-1</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="19" t="inlineStr">
-        <is>
-          <t>Reconciliation: UC pipeline scheduled = 0 units vs CoStar current Under Construction = 27 units.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t>Note: as-of quarter (2026 Q2 QTD) is partial (quarter-to-date). Occupancy is point-in-time (valid); Y0 supply/absorption sums for that quarter are partial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += UC (linked from Competitive Analysis) + proposed built this scenario; occupied += selected demand (capped at target). Yellow cells are editable.</t>
-        </is>
-      </c>
-    </row>
+    <row r="50" ht="14.4" customHeight="1"/>
+    <row r="51" ht="14.4" customHeight="1">
+      <c r="B51" s="47" t="inlineStr">
+        <is>
+          <t>▸ DETAIL: subject rent source by year &amp; reconciliation (grouped — click − to collapse)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B52" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y6  Q3 2019–Q2 2020</t>
+        </is>
+      </c>
+      <c r="E52" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B53" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y5  Q3 2020–Q2 2021</t>
+        </is>
+      </c>
+      <c r="E53" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B54" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y4  Q3 2021–Q2 2022</t>
+        </is>
+      </c>
+      <c r="E54" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B55" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y3  Q3 2022–Q2 2023</t>
+        </is>
+      </c>
+      <c r="E55" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B56" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y2  Q3 2023–Q2 2024</t>
+        </is>
+      </c>
+      <c r="E56" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B57" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y1  Q3 2024–Q2 2025</t>
+        </is>
+      </c>
+      <c r="E57" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B58" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Y0  Q3 2025–Q2 2026</t>
+        </is>
+      </c>
+      <c r="E58" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B59" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  UC scheduled vs CoStar UC</t>
+        </is>
+      </c>
+      <c r="E59" s="49" t="inlineStr">
+        <is>
+          <t>0 / 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  As-of 2026 Q2 QTD is partial (QTD); occupancy is point-in-time, Y0 flow sums partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="14.4" customHeight="1"/>
+    <row r="62" ht="14.4" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:O2"/>

--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -18,10 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot; mi&quot;;;&quot;—&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -174,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -207,6 +208,9 @@
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -224,6 +228,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -274,10 +281,10 @@
     <xf numFmtId="164" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -800,7 +807,9 @@
           <t>Highland Canyon Partners</t>
         </is>
       </c>
-      <c r="I6" s="7" t="n"/>
+      <c r="I6" s="12" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -840,7 +849,9 @@
           <t>Slagle Development</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n"/>
+      <c r="I7" s="12" t="n">
+        <v>4.2</v>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
@@ -880,7 +891,9 @@
           <t>Baron Properties</t>
         </is>
       </c>
-      <c r="I8" s="7" t="n"/>
+      <c r="I8" s="12" t="n">
+        <v>4.3</v>
+      </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
@@ -889,257 +902,269 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>PROPOSED (6 properties, 1,763 units)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Harris Ranch East</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>59</v>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="14" t="n"/>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="I11" s="20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t>Single Family</t>
         </is>
       </c>
-      <c r="K11" s="15" t="inlineStr">
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Station Village</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>84</v>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>Privately Owned</t>
         </is>
       </c>
-      <c r="I12" s="14" t="n"/>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="I12" s="20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>1519 South Londoner Avenue</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>189</v>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="14" t="n"/>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="I13" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Seasons on the Bench</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>358</v>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="I14" s="20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="K14" s="16" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>3300 South Vista Avenue</t>
         </is>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>180</v>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>Q1 2028</t>
         </is>
       </c>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="14" t="n"/>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="I15" s="20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K15" s="16" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Vista Point</t>
         </is>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>893</v>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="I16" s="20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K16" s="15" t="inlineStr">
+      <c r="K16" s="16" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar); Est. delivery set by analyst</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>* 5-Mile radius. Rent ($) = market asking. Proximity (mi) to be filled manually; lease-up rent/occupancy to be verified w/ HelloData. See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>* 5-Mile radius. Rent ($) = market asking. Proximity (mi) = straight-line distance from the subject (geocoded); lease-up rent/occupancy to be verified w/ HelloData. See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1231,7 @@
       </c>
     </row>
     <row r="3" ht="14.4" customHeight="1">
-      <c r="R3" s="20" t="inlineStr">
+      <c r="R3" s="22" t="inlineStr">
         <is>
           <t>UNDER CONSTRUCTION (linked from Competitive Analysis)</t>
         </is>
@@ -1217,124 +1242,124 @@
       </c>
     </row>
     <row r="4" ht="14.4" customHeight="1">
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>As-of Quarter</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="R4" s="23" t="inlineStr">
+      <c r="R4" s="25" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="S4" s="23" t="inlineStr">
+      <c r="S4" s="25" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="T4" s="23" t="inlineStr">
+      <c r="T4" s="25" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14.4" customHeight="1">
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Close Quarter (Y1 start)</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Q4 2026</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14.4" customHeight="1">
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Stabilization Target</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="27" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="7" ht="14.4" customHeight="1">
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Demand Scenario</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="R7" s="20" t="inlineStr">
+      <c r="R7" s="22" t="inlineStr">
         <is>
           <t>PROPOSED PIPELINE (scenario toggle)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14.4" customHeight="1">
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Bear Annual Absorption</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="28" t="n">
         <v>150</v>
       </c>
-      <c r="R8" s="23" t="inlineStr">
+      <c r="R8" s="25" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="S8" s="23" t="inlineStr">
+      <c r="S8" s="25" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="T8" s="23" t="inlineStr">
+      <c r="T8" s="25" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="U8" s="23" t="inlineStr">
+      <c r="U8" s="25" t="inlineStr">
         <is>
           <t>Built In</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14.4" customHeight="1">
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Base Annual Absorption</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="28" t="n">
         <v>300</v>
       </c>
-      <c r="R9" s="27" t="inlineStr">
+      <c r="R9" s="29" t="inlineStr">
         <is>
           <t>Vista Point</t>
         </is>
       </c>
-      <c r="S9" s="28" t="n">
+      <c r="S9" s="30" t="n">
         <v>893</v>
       </c>
-      <c r="T9" s="29" t="inlineStr">
+      <c r="T9" s="31" t="inlineStr">
         <is>
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="U9" s="29" t="inlineStr">
+      <c r="U9" s="31" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -1353,28 +1378,28 @@
       </c>
     </row>
     <row r="10" ht="14.4" customHeight="1">
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Bull Annual Absorption</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="28" t="n">
         <v>450</v>
       </c>
-      <c r="R10" s="27" t="inlineStr">
+      <c r="R10" s="29" t="inlineStr">
         <is>
           <t>Seasons on the Bench</t>
         </is>
       </c>
-      <c r="S10" s="28" t="n">
+      <c r="S10" s="30" t="n">
         <v>358</v>
       </c>
-      <c r="T10" s="29" t="inlineStr">
+      <c r="T10" s="31" t="inlineStr">
         <is>
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="U10" s="29" t="inlineStr">
+      <c r="U10" s="31" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -1393,29 +1418,29 @@
       </c>
     </row>
     <row r="11" ht="14.4" customHeight="1">
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Selected Annual Demand</t>
         </is>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="32">
         <f>IF($C$7="Bear",$C$8,IF($C$7="Bull",$C$10,$C$9))</f>
         <v/>
       </c>
-      <c r="R11" s="27" t="inlineStr">
+      <c r="R11" s="29" t="inlineStr">
         <is>
           <t>1519 South Londoner Avenue</t>
         </is>
       </c>
-      <c r="S11" s="28" t="n">
+      <c r="S11" s="30" t="n">
         <v>189</v>
       </c>
-      <c r="T11" s="29" t="inlineStr">
+      <c r="T11" s="31" t="inlineStr">
         <is>
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="U11" s="29" t="inlineStr">
+      <c r="U11" s="31" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -1434,20 +1459,20 @@
       </c>
     </row>
     <row r="12" ht="14.4" customHeight="1">
-      <c r="R12" s="27" t="inlineStr">
+      <c r="R12" s="29" t="inlineStr">
         <is>
           <t>3300 South Vista Avenue</t>
         </is>
       </c>
-      <c r="S12" s="28" t="n">
+      <c r="S12" s="30" t="n">
         <v>180</v>
       </c>
-      <c r="T12" s="29" t="inlineStr">
+      <c r="T12" s="31" t="inlineStr">
         <is>
           <t>Q1 2028</t>
         </is>
       </c>
-      <c r="U12" s="29" t="inlineStr">
+      <c r="U12" s="31" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -1466,20 +1491,20 @@
       </c>
     </row>
     <row r="13" ht="14.4" customHeight="1">
-      <c r="R13" s="27" t="inlineStr">
+      <c r="R13" s="29" t="inlineStr">
         <is>
           <t>Station Village</t>
         </is>
       </c>
-      <c r="S13" s="28" t="n">
+      <c r="S13" s="30" t="n">
         <v>84</v>
       </c>
-      <c r="T13" s="29" t="inlineStr">
+      <c r="T13" s="31" t="inlineStr">
         <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="U13" s="29" t="inlineStr">
+      <c r="U13" s="31" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -1498,20 +1523,20 @@
       </c>
     </row>
     <row r="14" ht="14.4" customHeight="1">
-      <c r="R14" s="27" t="inlineStr">
+      <c r="R14" s="29" t="inlineStr">
         <is>
           <t>Harris Ranch East</t>
         </is>
       </c>
-      <c r="S14" s="28" t="n">
+      <c r="S14" s="30" t="n">
         <v>59</v>
       </c>
-      <c r="T14" s="29" t="inlineStr">
+      <c r="T14" s="31" t="inlineStr">
         <is>
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="U14" s="29" t="inlineStr">
+      <c r="U14" s="31" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -1532,7 +1557,7 @@
     <row r="15" ht="14.4" customHeight="1"/>
     <row r="16" ht="14.4" customHeight="1"/>
     <row r="17" ht="14.4" customHeight="1">
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>5-MILE MARKET</t>
         </is>
@@ -1572,1060 +1597,1060 @@
           <t>Y0</t>
         </is>
       </c>
-      <c r="J17" s="31" t="inlineStr">
+      <c r="J17" s="33" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K17" s="31" t="inlineStr">
+      <c r="K17" s="33" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L17" s="31" t="inlineStr">
+      <c r="L17" s="33" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M17" s="31" t="inlineStr">
+      <c r="M17" s="33" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N17" s="31" t="inlineStr">
+      <c r="N17" s="33" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O17" s="31" t="inlineStr">
+      <c r="O17" s="33" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14.4" customHeight="1">
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>Q3'19-Q2'20</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" s="34" t="inlineStr">
         <is>
           <t>Q3'20-Q2'21</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="34" t="inlineStr">
         <is>
           <t>Q3'21-Q2'22</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="34" t="inlineStr">
         <is>
           <t>Q3'22-Q2'23</t>
         </is>
       </c>
-      <c r="G18" s="32" t="inlineStr">
+      <c r="G18" s="34" t="inlineStr">
         <is>
           <t>Q3'23-Q2'24</t>
         </is>
       </c>
-      <c r="H18" s="32" t="inlineStr">
+      <c r="H18" s="34" t="inlineStr">
         <is>
           <t>Q3'24-Q2'25</t>
         </is>
       </c>
-      <c r="I18" s="32" t="inlineStr">
+      <c r="I18" s="34" t="inlineStr">
         <is>
           <t>Q3'25-Q2'26</t>
         </is>
       </c>
-      <c r="J18" s="32" t="inlineStr">
+      <c r="J18" s="34" t="inlineStr">
         <is>
           <t>Hold Yr 1</t>
         </is>
       </c>
-      <c r="K18" s="32" t="inlineStr">
+      <c r="K18" s="34" t="inlineStr">
         <is>
           <t>Hold Yr 2</t>
         </is>
       </c>
-      <c r="L18" s="32" t="inlineStr">
+      <c r="L18" s="34" t="inlineStr">
         <is>
           <t>Hold Yr 3</t>
         </is>
       </c>
-      <c r="M18" s="32" t="inlineStr">
+      <c r="M18" s="34" t="inlineStr">
         <is>
           <t>Hold Yr 4</t>
         </is>
       </c>
-      <c r="N18" s="32" t="inlineStr">
+      <c r="N18" s="34" t="inlineStr">
         <is>
           <t>Hold Yr 5</t>
         </is>
       </c>
-      <c r="O18" s="32" t="inlineStr">
+      <c r="O18" s="34" t="inlineStr">
         <is>
           <t>Hold Yr 6</t>
         </is>
       </c>
     </row>
     <row r="19" ht="14.4" customHeight="1">
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>NEW SUPPLY (5-mi)</t>
         </is>
       </c>
-      <c r="C19" s="33" t="n">
+      <c r="C19" s="35" t="n">
         <v>213</v>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D19" s="35" t="n">
         <v>237</v>
       </c>
-      <c r="E19" s="33" t="n">
+      <c r="E19" s="35" t="n">
         <v>33</v>
       </c>
-      <c r="F19" s="33" t="n">
+      <c r="F19" s="35" t="n">
         <v>289</v>
       </c>
-      <c r="G19" s="33" t="n">
+      <c r="G19" s="35" t="n">
         <v>178</v>
       </c>
-      <c r="H19" s="33" t="n">
+      <c r="H19" s="35" t="n">
         <v>334</v>
       </c>
-      <c r="I19" s="33" t="n">
+      <c r="I19" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="36">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,1)+SUMIFS($S$9:$S$14,$W$9:$W$14,1,$X$9:$X$14,1)</f>
         <v/>
       </c>
-      <c r="K19" s="34">
+      <c r="K19" s="36">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,2)+SUMIFS($S$9:$S$14,$W$9:$W$14,2,$X$9:$X$14,1)</f>
         <v/>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="36">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,3)+SUMIFS($S$9:$S$14,$W$9:$W$14,3,$X$9:$X$14,1)</f>
         <v/>
       </c>
-      <c r="M19" s="34">
+      <c r="M19" s="36">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,4)+SUMIFS($S$9:$S$14,$W$9:$W$14,4,$X$9:$X$14,1)</f>
         <v/>
       </c>
-      <c r="N19" s="34">
+      <c r="N19" s="36">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,5)+SUMIFS($S$9:$S$14,$W$9:$W$14,5,$X$9:$X$14,1)</f>
         <v/>
       </c>
-      <c r="O19" s="34">
+      <c r="O19" s="36">
         <f>SUMIFS($S$5:$S$5,$W$5:$W$5,6)+SUMIFS($S$9:$S$14,$W$9:$W$14,6,$X$9:$X$14,1)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="14.4" customHeight="1">
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>ABSORPTION (5-mi)</t>
         </is>
       </c>
-      <c r="C20" s="33" t="n">
+      <c r="C20" s="35" t="n">
         <v>213</v>
       </c>
-      <c r="D20" s="33" t="n">
+      <c r="D20" s="35" t="n">
         <v>150</v>
       </c>
-      <c r="E20" s="33" t="n">
+      <c r="E20" s="35" t="n">
         <v>86</v>
       </c>
-      <c r="F20" s="33" t="n">
+      <c r="F20" s="35" t="n">
         <v>-91</v>
       </c>
-      <c r="G20" s="33" t="n">
+      <c r="G20" s="35" t="n">
         <v>277</v>
       </c>
-      <c r="H20" s="33" t="n">
+      <c r="H20" s="35" t="n">
         <v>399</v>
       </c>
-      <c r="I20" s="33" t="n">
+      <c r="I20" s="35" t="n">
         <v>216</v>
       </c>
-      <c r="J20" s="34">
+      <c r="J20" s="36">
         <f>J31-I31</f>
         <v/>
       </c>
-      <c r="K20" s="34">
+      <c r="K20" s="36">
         <f>K31-J31</f>
         <v/>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="36">
         <f>L31-K31</f>
         <v/>
       </c>
-      <c r="M20" s="34">
+      <c r="M20" s="36">
         <f>M31-L31</f>
         <v/>
       </c>
-      <c r="N20" s="34">
+      <c r="N20" s="36">
         <f>N31-M31</f>
         <v/>
       </c>
-      <c r="O20" s="34">
+      <c r="O20" s="36">
         <f>O31-N31</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="14.4" customHeight="1">
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>OCCUPANCY (5-mi)</t>
         </is>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="37" t="n">
         <v>0.968</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="37" t="n">
         <v>0.953</v>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="37" t="n">
         <v>0.963</v>
       </c>
-      <c r="F21" s="35" t="n">
+      <c r="F21" s="37" t="n">
         <v>0.895</v>
       </c>
-      <c r="G21" s="35" t="n">
+      <c r="G21" s="37" t="n">
         <v>0.916</v>
       </c>
-      <c r="H21" s="35" t="n">
+      <c r="H21" s="37" t="n">
         <v>0.9320000000000001</v>
       </c>
-      <c r="I21" s="35" t="n">
+      <c r="I21" s="37" t="n">
         <v>0.967</v>
       </c>
-      <c r="J21" s="36">
+      <c r="J21" s="38">
         <f>IFERROR(J31/J30,0)</f>
         <v/>
       </c>
-      <c r="K21" s="36">
+      <c r="K21" s="38">
         <f>IFERROR(K31/K30,0)</f>
         <v/>
       </c>
-      <c r="L21" s="36">
+      <c r="L21" s="38">
         <f>IFERROR(L31/L30,0)</f>
         <v/>
       </c>
-      <c r="M21" s="36">
+      <c r="M21" s="38">
         <f>IFERROR(M31/M30,0)</f>
         <v/>
       </c>
-      <c r="N21" s="36">
+      <c r="N21" s="38">
         <f>IFERROR(N31/N30,0)</f>
         <v/>
       </c>
-      <c r="O21" s="36">
+      <c r="O21" s="38">
         <f>IFERROR(O31/O30,0)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="14.4" customHeight="1">
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>SUBJECT (Canyon Ridge)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="14.4" customHeight="1">
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Market Rent  (CoStar→HD)</t>
         </is>
       </c>
-      <c r="C23" s="37" t="n"/>
-      <c r="D23" s="37" t="n"/>
-      <c r="E23" s="37" t="n"/>
-      <c r="F23" s="37" t="n"/>
-      <c r="G23" s="37" t="n"/>
-      <c r="H23" s="37" t="n"/>
-      <c r="I23" s="37" t="n"/>
-      <c r="J23" s="38" t="n"/>
-      <c r="K23" s="38" t="n"/>
-      <c r="L23" s="38" t="n"/>
-      <c r="M23" s="38" t="n"/>
-      <c r="N23" s="38" t="n"/>
-      <c r="O23" s="38" t="n"/>
+      <c r="C23" s="39" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="39" t="n"/>
+      <c r="H23" s="39" t="n"/>
+      <c r="I23" s="39" t="n"/>
+      <c r="J23" s="40" t="n"/>
+      <c r="K23" s="40" t="n"/>
+      <c r="L23" s="40" t="n"/>
+      <c r="M23" s="40" t="n"/>
+      <c r="N23" s="40" t="n"/>
+      <c r="O23" s="40" t="n"/>
     </row>
     <row r="24" ht="14.4" customHeight="1">
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">    Market Rent YoY %</t>
         </is>
       </c>
-      <c r="C24" s="40" t="n"/>
-      <c r="D24" s="40">
+      <c r="C24" s="42" t="n"/>
+      <c r="D24" s="42">
         <f>IFERROR(D23/C23-1,"")</f>
         <v/>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="42">
         <f>IFERROR(E23/D23-1,"")</f>
         <v/>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="42">
         <f>IFERROR(F23/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="40">
+      <c r="G24" s="42">
         <f>IFERROR(G23/F23-1,"")</f>
         <v/>
       </c>
-      <c r="H24" s="40">
+      <c r="H24" s="42">
         <f>IFERROR(H23/G23-1,"")</f>
         <v/>
       </c>
-      <c r="I24" s="40">
+      <c r="I24" s="42">
         <f>IFERROR(I23/H23-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="41" t="n"/>
-      <c r="K24" s="41" t="n"/>
-      <c r="L24" s="41" t="n"/>
-      <c r="M24" s="41" t="n"/>
-      <c r="N24" s="41" t="n"/>
-      <c r="O24" s="41" t="n"/>
+      <c r="J24" s="43" t="n"/>
+      <c r="K24" s="43" t="n"/>
+      <c r="L24" s="43" t="n"/>
+      <c r="M24" s="43" t="n"/>
+      <c r="N24" s="43" t="n"/>
+      <c r="O24" s="43" t="n"/>
     </row>
     <row r="25" ht="14.4" customHeight="1">
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Effective Rent</t>
         </is>
       </c>
-      <c r="C25" s="37" t="n"/>
-      <c r="D25" s="37" t="n"/>
-      <c r="E25" s="37" t="n"/>
-      <c r="F25" s="37" t="n"/>
-      <c r="G25" s="37" t="n"/>
-      <c r="H25" s="37" t="n"/>
-      <c r="I25" s="37" t="n"/>
-      <c r="J25" s="38" t="n"/>
-      <c r="K25" s="38" t="n"/>
-      <c r="L25" s="38" t="n"/>
-      <c r="M25" s="38" t="n"/>
-      <c r="N25" s="38" t="n"/>
-      <c r="O25" s="38" t="n"/>
+      <c r="C25" s="39" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
+      <c r="H25" s="39" t="n"/>
+      <c r="I25" s="39" t="n"/>
+      <c r="J25" s="40" t="n"/>
+      <c r="K25" s="40" t="n"/>
+      <c r="L25" s="40" t="n"/>
+      <c r="M25" s="40" t="n"/>
+      <c r="N25" s="40" t="n"/>
+      <c r="O25" s="40" t="n"/>
     </row>
     <row r="26" ht="14.4" customHeight="1">
-      <c r="B26" s="39" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">    Effective Rent YoY %</t>
         </is>
       </c>
-      <c r="C26" s="40" t="n"/>
-      <c r="D26" s="40">
+      <c r="C26" s="42" t="n"/>
+      <c r="D26" s="42">
         <f>IFERROR(D25/C25-1,"")</f>
         <v/>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="42">
         <f>IFERROR(E25/D25-1,"")</f>
         <v/>
       </c>
-      <c r="F26" s="40">
+      <c r="F26" s="42">
         <f>IFERROR(F25/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="40">
+      <c r="G26" s="42">
         <f>IFERROR(G25/F25-1,"")</f>
         <v/>
       </c>
-      <c r="H26" s="40">
+      <c r="H26" s="42">
         <f>IFERROR(H25/G25-1,"")</f>
         <v/>
       </c>
-      <c r="I26" s="40">
+      <c r="I26" s="42">
         <f>IFERROR(I25/H25-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="41" t="n"/>
-      <c r="K26" s="41" t="n"/>
-      <c r="L26" s="41" t="n"/>
-      <c r="M26" s="41" t="n"/>
-      <c r="N26" s="41" t="n"/>
-      <c r="O26" s="41" t="n"/>
+      <c r="J26" s="43" t="n"/>
+      <c r="K26" s="43" t="n"/>
+      <c r="L26" s="43" t="n"/>
+      <c r="M26" s="43" t="n"/>
+      <c r="N26" s="43" t="n"/>
+      <c r="O26" s="43" t="n"/>
     </row>
     <row r="27" ht="14.4" customHeight="1">
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Occupancy (financials / CoStar)</t>
         </is>
       </c>
-      <c r="C27" s="42" t="n"/>
-      <c r="D27" s="42" t="n"/>
-      <c r="E27" s="42" t="n"/>
-      <c r="F27" s="42" t="n"/>
-      <c r="G27" s="42" t="n"/>
-      <c r="H27" s="42" t="n"/>
-      <c r="I27" s="42" t="n"/>
-      <c r="J27" s="43" t="n"/>
-      <c r="K27" s="43" t="n"/>
-      <c r="L27" s="43" t="n"/>
-      <c r="M27" s="43" t="n"/>
-      <c r="N27" s="43" t="n"/>
-      <c r="O27" s="43" t="n"/>
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="44" t="n"/>
+      <c r="F27" s="44" t="n"/>
+      <c r="G27" s="44" t="n"/>
+      <c r="H27" s="44" t="n"/>
+      <c r="I27" s="44" t="n"/>
+      <c r="J27" s="45" t="n"/>
+      <c r="K27" s="45" t="n"/>
+      <c r="L27" s="45" t="n"/>
+      <c r="M27" s="45" t="n"/>
+      <c r="N27" s="45" t="n"/>
+      <c r="O27" s="45" t="n"/>
     </row>
     <row r="28" ht="14.4" customHeight="1">
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Concession %</t>
         </is>
       </c>
-      <c r="C28" s="42" t="n"/>
-      <c r="D28" s="42" t="n"/>
-      <c r="E28" s="42" t="n"/>
-      <c r="F28" s="42" t="n"/>
-      <c r="G28" s="42" t="n"/>
-      <c r="H28" s="42" t="n"/>
-      <c r="I28" s="42" t="n"/>
-      <c r="J28" s="43" t="n"/>
-      <c r="K28" s="43" t="n"/>
-      <c r="L28" s="43" t="n"/>
-      <c r="M28" s="43" t="n"/>
-      <c r="N28" s="43" t="n"/>
-      <c r="O28" s="43" t="n"/>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="44" t="n"/>
+      <c r="F28" s="44" t="n"/>
+      <c r="G28" s="44" t="n"/>
+      <c r="H28" s="44" t="n"/>
+      <c r="I28" s="44" t="n"/>
+      <c r="J28" s="45" t="n"/>
+      <c r="K28" s="45" t="n"/>
+      <c r="L28" s="45" t="n"/>
+      <c r="M28" s="45" t="n"/>
+      <c r="N28" s="45" t="n"/>
+      <c r="O28" s="45" t="n"/>
     </row>
     <row r="29" ht="14.4" customHeight="1"/>
     <row r="30" hidden="1" ht="14.4" customHeight="1">
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  inventory</t>
         </is>
       </c>
-      <c r="C30" s="44" t="n">
+      <c r="C30" s="46" t="n">
         <v>4845</v>
       </c>
-      <c r="D30" s="44" t="n">
+      <c r="D30" s="46" t="n">
         <v>5082</v>
       </c>
-      <c r="E30" s="44" t="n">
+      <c r="E30" s="46" t="n">
         <v>5115</v>
       </c>
-      <c r="F30" s="44" t="n">
+      <c r="F30" s="46" t="n">
         <v>5404</v>
       </c>
-      <c r="G30" s="44" t="n">
+      <c r="G30" s="46" t="n">
         <v>5582</v>
       </c>
-      <c r="H30" s="44" t="n">
+      <c r="H30" s="46" t="n">
         <v>5916</v>
       </c>
-      <c r="I30" s="44" t="n">
+      <c r="I30" s="46" t="n">
         <v>5925</v>
       </c>
-      <c r="J30" s="44">
+      <c r="J30" s="46">
         <f>I30+J19</f>
         <v/>
       </c>
-      <c r="K30" s="44">
+      <c r="K30" s="46">
         <f>J30+K19</f>
         <v/>
       </c>
-      <c r="L30" s="44">
+      <c r="L30" s="46">
         <f>K30+L19</f>
         <v/>
       </c>
-      <c r="M30" s="44">
+      <c r="M30" s="46">
         <f>L30+M19</f>
         <v/>
       </c>
-      <c r="N30" s="44">
+      <c r="N30" s="46">
         <f>M30+N19</f>
         <v/>
       </c>
-      <c r="O30" s="44">
+      <c r="O30" s="46">
         <f>N30+O19</f>
         <v/>
       </c>
     </row>
     <row r="31" hidden="1" ht="14.4" customHeight="1">
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  occupied</t>
         </is>
       </c>
-      <c r="C31" s="44" t="n">
+      <c r="C31" s="46" t="n">
         <v>4691</v>
       </c>
-      <c r="D31" s="44" t="n">
+      <c r="D31" s="46" t="n">
         <v>4841</v>
       </c>
-      <c r="E31" s="44" t="n">
+      <c r="E31" s="46" t="n">
         <v>4927</v>
       </c>
-      <c r="F31" s="44" t="n">
+      <c r="F31" s="46" t="n">
         <v>4836</v>
       </c>
-      <c r="G31" s="44" t="n">
+      <c r="G31" s="46" t="n">
         <v>5113</v>
       </c>
-      <c r="H31" s="44" t="n">
+      <c r="H31" s="46" t="n">
         <v>5512</v>
       </c>
-      <c r="I31" s="44" t="n">
+      <c r="I31" s="46" t="n">
         <v>5727</v>
       </c>
-      <c r="J31" s="44">
+      <c r="J31" s="46">
         <f>MIN($C$6*J30,I31+$C$11)</f>
         <v/>
       </c>
-      <c r="K31" s="44">
+      <c r="K31" s="46">
         <f>MIN($C$6*K30,J31+$C$11)</f>
         <v/>
       </c>
-      <c r="L31" s="44">
+      <c r="L31" s="46">
         <f>MIN($C$6*L30,K31+$C$11)</f>
         <v/>
       </c>
-      <c r="M31" s="44">
+      <c r="M31" s="46">
         <f>MIN($C$6*M30,L31+$C$11)</f>
         <v/>
       </c>
-      <c r="N31" s="44">
+      <c r="N31" s="46">
         <f>MIN($C$6*N30,M31+$C$11)</f>
         <v/>
       </c>
-      <c r="O31" s="44">
+      <c r="O31" s="46">
         <f>MIN($C$6*O30,N31+$C$11)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="14.4" customHeight="1"/>
     <row r="33" ht="14.4" customHeight="1">
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
         </is>
       </c>
-      <c r="J33" s="45" t="inlineStr">
+      <c r="J33" s="47" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K33" s="45" t="inlineStr">
+      <c r="K33" s="47" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L33" s="45" t="inlineStr">
+      <c r="L33" s="47" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M33" s="45" t="inlineStr">
+      <c r="M33" s="47" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N33" s="45" t="inlineStr">
+      <c r="N33" s="47" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O33" s="45" t="inlineStr">
+      <c r="O33" s="47" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
     </row>
     <row r="34" ht="14.4" customHeight="1">
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J34" s="46">
+      <c r="J34" s="48">
         <f>MIN($C$6,($I$31+$C$8*1)/J30)</f>
         <v/>
       </c>
-      <c r="K34" s="46">
+      <c r="K34" s="48">
         <f>MIN($C$6,($I$31+$C$8*2)/K30)</f>
         <v/>
       </c>
-      <c r="L34" s="46">
+      <c r="L34" s="48">
         <f>MIN($C$6,($I$31+$C$8*3)/L30)</f>
         <v/>
       </c>
-      <c r="M34" s="46">
+      <c r="M34" s="48">
         <f>MIN($C$6,($I$31+$C$8*4)/M30)</f>
         <v/>
       </c>
-      <c r="N34" s="46">
+      <c r="N34" s="48">
         <f>MIN($C$6,($I$31+$C$8*5)/N30)</f>
         <v/>
       </c>
-      <c r="O34" s="46">
+      <c r="O34" s="48">
         <f>MIN($C$6,($I$31+$C$8*6)/O30)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="14.4" customHeight="1">
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J35" s="46">
+      <c r="J35" s="48">
         <f>MIN($C$6,($I$31+$C$9*1)/J30)</f>
         <v/>
       </c>
-      <c r="K35" s="46">
+      <c r="K35" s="48">
         <f>MIN($C$6,($I$31+$C$9*2)/K30)</f>
         <v/>
       </c>
-      <c r="L35" s="46">
+      <c r="L35" s="48">
         <f>MIN($C$6,($I$31+$C$9*3)/L30)</f>
         <v/>
       </c>
-      <c r="M35" s="46">
+      <c r="M35" s="48">
         <f>MIN($C$6,($I$31+$C$9*4)/M30)</f>
         <v/>
       </c>
-      <c r="N35" s="46">
+      <c r="N35" s="48">
         <f>MIN($C$6,($I$31+$C$9*5)/N30)</f>
         <v/>
       </c>
-      <c r="O35" s="46">
+      <c r="O35" s="48">
         <f>MIN($C$6,($I$31+$C$9*6)/O30)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="14.4" customHeight="1">
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J36" s="46">
+      <c r="J36" s="48">
         <f>MIN($C$6,($I$31+$C$10*1)/J30)</f>
         <v/>
       </c>
-      <c r="K36" s="46">
+      <c r="K36" s="48">
         <f>MIN($C$6,($I$31+$C$10*2)/K30)</f>
         <v/>
       </c>
-      <c r="L36" s="46">
+      <c r="L36" s="48">
         <f>MIN($C$6,($I$31+$C$10*3)/L30)</f>
         <v/>
       </c>
-      <c r="M36" s="46">
+      <c r="M36" s="48">
         <f>MIN($C$6,($I$31+$C$10*4)/M30)</f>
         <v/>
       </c>
-      <c r="N36" s="46">
+      <c r="N36" s="48">
         <f>MIN($C$6,($I$31+$C$10*5)/N30)</f>
         <v/>
       </c>
-      <c r="O36" s="46">
+      <c r="O36" s="48">
         <f>MIN($C$6,($I$31+$C$10*6)/O30)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="14.4" customHeight="1"/>
     <row r="38" ht="14.4" customHeight="1">
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>MARKET RENT GROWTH (editable assumptions)</t>
         </is>
       </c>
-      <c r="J38" s="47" t="inlineStr">
+      <c r="J38" s="49" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K38" s="47" t="inlineStr">
+      <c r="K38" s="49" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L38" s="47" t="inlineStr">
+      <c r="L38" s="49" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M38" s="47" t="inlineStr">
+      <c r="M38" s="49" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N38" s="47" t="inlineStr">
+      <c r="N38" s="49" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O38" s="47" t="inlineStr">
+      <c r="O38" s="49" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14.4" customHeight="1">
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J39" s="48" t="n">
+      <c r="J39" s="50" t="n">
         <v>-0.0025</v>
       </c>
-      <c r="K39" s="48" t="n">
+      <c r="K39" s="50" t="n">
         <v>0.0175</v>
       </c>
-      <c r="L39" s="48" t="n">
+      <c r="L39" s="50" t="n">
         <v>0.0275</v>
       </c>
-      <c r="M39" s="48" t="n">
+      <c r="M39" s="50" t="n">
         <v>0.0375</v>
       </c>
-      <c r="N39" s="48" t="n">
+      <c r="N39" s="50" t="n">
         <v>0.0275</v>
       </c>
-      <c r="O39" s="48" t="n">
+      <c r="O39" s="50" t="n">
         <v>0.0175</v>
       </c>
     </row>
     <row r="40" ht="14.4" customHeight="1">
-      <c r="B40" s="21" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J40" s="48" t="n">
+      <c r="J40" s="50" t="n">
         <v>0.01</v>
       </c>
-      <c r="K40" s="48" t="n">
+      <c r="K40" s="50" t="n">
         <v>0.03</v>
       </c>
-      <c r="L40" s="48" t="n">
+      <c r="L40" s="50" t="n">
         <v>0.04</v>
       </c>
-      <c r="M40" s="48" t="n">
+      <c r="M40" s="50" t="n">
         <v>0.05</v>
       </c>
-      <c r="N40" s="48" t="n">
+      <c r="N40" s="50" t="n">
         <v>0.04</v>
       </c>
-      <c r="O40" s="48" t="n">
+      <c r="O40" s="50" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="41" ht="14.4" customHeight="1">
-      <c r="B41" s="21" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J41" s="48" t="n">
+      <c r="J41" s="50" t="n">
         <v>0.02</v>
       </c>
-      <c r="K41" s="48" t="n">
+      <c r="K41" s="50" t="n">
         <v>0.04</v>
       </c>
-      <c r="L41" s="48" t="n">
+      <c r="L41" s="50" t="n">
         <v>0.05</v>
       </c>
-      <c r="M41" s="48" t="n">
+      <c r="M41" s="50" t="n">
         <v>0.06</v>
       </c>
-      <c r="N41" s="48" t="n">
+      <c r="N41" s="50" t="n">
         <v>0.05</v>
       </c>
-      <c r="O41" s="48" t="n">
+      <c r="O41" s="50" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="42" ht="14.4" customHeight="1">
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>CONCESSIONS % — forward assumption (editable)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.4" customHeight="1">
-      <c r="B43" s="21" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J43" s="48" t="n">
+      <c r="J43" s="50" t="n">
         <v>0.06</v>
       </c>
-      <c r="K43" s="48" t="n">
+      <c r="K43" s="50" t="n">
         <v>0.045</v>
       </c>
-      <c r="L43" s="48" t="n">
+      <c r="L43" s="50" t="n">
         <v>0.035</v>
       </c>
-      <c r="M43" s="48" t="n">
+      <c r="M43" s="50" t="n">
         <v>0.035</v>
       </c>
-      <c r="N43" s="48" t="n">
+      <c r="N43" s="50" t="n">
         <v>0.035</v>
       </c>
-      <c r="O43" s="48" t="n">
+      <c r="O43" s="50" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="44" ht="14.4" customHeight="1">
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J44" s="48" t="n">
+      <c r="J44" s="50" t="n">
         <v>0.03</v>
       </c>
-      <c r="K44" s="48" t="n">
+      <c r="K44" s="50" t="n">
         <v>0.015</v>
       </c>
-      <c r="L44" s="48" t="n">
+      <c r="L44" s="50" t="n">
         <v>0.005</v>
       </c>
-      <c r="M44" s="48" t="n">
+      <c r="M44" s="50" t="n">
         <v>0.005</v>
       </c>
-      <c r="N44" s="48" t="n">
+      <c r="N44" s="50" t="n">
         <v>0.005</v>
       </c>
-      <c r="O44" s="48" t="n">
+      <c r="O44" s="50" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="45" ht="14.4" customHeight="1">
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J45" s="48" t="n">
+      <c r="J45" s="50" t="n">
         <v>0.02</v>
       </c>
-      <c r="K45" s="48" t="n">
+      <c r="K45" s="50" t="n">
         <v>0.005</v>
       </c>
-      <c r="L45" s="48" t="n">
+      <c r="L45" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="48" t="n">
+      <c r="M45" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="48" t="n">
+      <c r="N45" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="48" t="n">
+      <c r="O45" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46" ht="14.4" customHeight="1">
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>EFFECTIVE RENT GROWTH (derived)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14.4" customHeight="1">
-      <c r="B47" s="21" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J47" s="46">
+      <c r="J47" s="48">
         <f>(1+J39)*(1-J43)-1</f>
         <v/>
       </c>
-      <c r="K47" s="46">
+      <c r="K47" s="48">
         <f>(1+K39)*(1-K43)/(1-J43)-1</f>
         <v/>
       </c>
-      <c r="L47" s="46">
+      <c r="L47" s="48">
         <f>(1+L39)*(1-L43)/(1-K43)-1</f>
         <v/>
       </c>
-      <c r="M47" s="46">
+      <c r="M47" s="48">
         <f>(1+M39)*(1-M43)/(1-L43)-1</f>
         <v/>
       </c>
-      <c r="N47" s="46">
+      <c r="N47" s="48">
         <f>(1+N39)*(1-N43)/(1-M43)-1</f>
         <v/>
       </c>
-      <c r="O47" s="46">
+      <c r="O47" s="48">
         <f>(1+O39)*(1-O43)/(1-N43)-1</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="14.4" customHeight="1">
-      <c r="B48" s="21" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J48" s="46">
+      <c r="J48" s="48">
         <f>(1+J40)*(1-J44)-1</f>
         <v/>
       </c>
-      <c r="K48" s="46">
+      <c r="K48" s="48">
         <f>(1+K40)*(1-K44)/(1-J44)-1</f>
         <v/>
       </c>
-      <c r="L48" s="46">
+      <c r="L48" s="48">
         <f>(1+L40)*(1-L44)/(1-K44)-1</f>
         <v/>
       </c>
-      <c r="M48" s="46">
+      <c r="M48" s="48">
         <f>(1+M40)*(1-M44)/(1-L44)-1</f>
         <v/>
       </c>
-      <c r="N48" s="46">
+      <c r="N48" s="48">
         <f>(1+N40)*(1-N44)/(1-M44)-1</f>
         <v/>
       </c>
-      <c r="O48" s="46">
+      <c r="O48" s="48">
         <f>(1+O40)*(1-O44)/(1-N44)-1</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="14.4" customHeight="1">
-      <c r="B49" s="21" t="inlineStr">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J49" s="46">
+      <c r="J49" s="48">
         <f>(1+J41)*(1-J45)-1</f>
         <v/>
       </c>
-      <c r="K49" s="46">
+      <c r="K49" s="48">
         <f>(1+K41)*(1-K45)/(1-J45)-1</f>
         <v/>
       </c>
-      <c r="L49" s="46">
+      <c r="L49" s="48">
         <f>(1+L41)*(1-L45)/(1-K45)-1</f>
         <v/>
       </c>
-      <c r="M49" s="46">
+      <c r="M49" s="48">
         <f>(1+M41)*(1-M45)/(1-L45)-1</f>
         <v/>
       </c>
-      <c r="N49" s="46">
+      <c r="N49" s="48">
         <f>(1+N41)*(1-N45)/(1-M45)-1</f>
         <v/>
       </c>
-      <c r="O49" s="46">
+      <c r="O49" s="48">
         <f>(1+O41)*(1-O45)/(1-N45)-1</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="14.4" customHeight="1"/>
     <row r="51" ht="14.4" customHeight="1">
-      <c r="B51" s="47" t="inlineStr">
+      <c r="B51" s="49" t="inlineStr">
         <is>
           <t>▸ DETAIL: subject rent source by year &amp; reconciliation (grouped — click − to collapse)</t>
         </is>
       </c>
     </row>
     <row r="52" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B52" s="49" t="inlineStr">
+      <c r="B52" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y6  Q3 2019–Q2 2020</t>
         </is>
       </c>
-      <c r="E52" s="49" t="inlineStr">
+      <c r="E52" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="53" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B53" s="49" t="inlineStr">
+      <c r="B53" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y5  Q3 2020–Q2 2021</t>
         </is>
       </c>
-      <c r="E53" s="49" t="inlineStr">
+      <c r="E53" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="54" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B54" s="49" t="inlineStr">
+      <c r="B54" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y4  Q3 2021–Q2 2022</t>
         </is>
       </c>
-      <c r="E54" s="49" t="inlineStr">
+      <c r="E54" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="55" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B55" s="49" t="inlineStr">
+      <c r="B55" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y3  Q3 2022–Q2 2023</t>
         </is>
       </c>
-      <c r="E55" s="49" t="inlineStr">
+      <c r="E55" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="56" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B56" s="49" t="inlineStr">
+      <c r="B56" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y2  Q3 2023–Q2 2024</t>
         </is>
       </c>
-      <c r="E56" s="49" t="inlineStr">
+      <c r="E56" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="57" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B57" s="49" t="inlineStr">
+      <c r="B57" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y1  Q3 2024–Q2 2025</t>
         </is>
       </c>
-      <c r="E57" s="49" t="inlineStr">
+      <c r="E57" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="58" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B58" s="49" t="inlineStr">
+      <c r="B58" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  Y0  Q3 2025–Q2 2026</t>
         </is>
       </c>
-      <c r="E58" s="49" t="inlineStr">
+      <c r="E58" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="59" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B59" s="49" t="inlineStr">
+      <c r="B59" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  UC scheduled vs CoStar UC</t>
         </is>
       </c>
-      <c r="E59" s="49" t="inlineStr">
+      <c r="E59" s="51" t="inlineStr">
         <is>
           <t>0 / 27</t>
         </is>
       </c>
     </row>
     <row r="60" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B60" s="19" t="inlineStr">
+      <c r="B60" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  As-of 2026 Q2 QTD is partial (QTD); occupancy is point-in-time, Y0 flow sums partial.</t>
         </is>
@@ -2673,62 +2698,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="50" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="50" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D1" s="50" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="E1" s="50" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="F1" s="50" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="G1" s="50" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>CoStar Occ</t>
         </is>
       </c>
-      <c r="H1" s="50" t="inlineStr">
+      <c r="H1" s="52" t="inlineStr">
         <is>
           <t>RealPage Occ</t>
         </is>
       </c>
-      <c r="I1" s="50" t="inlineStr">
+      <c r="I1" s="52" t="inlineStr">
         <is>
           <t>CoStar Ask Rent</t>
         </is>
       </c>
-      <c r="J1" s="50" t="inlineStr">
+      <c r="J1" s="52" t="inlineStr">
         <is>
           <t>RealPage Eff Rent</t>
         </is>
       </c>
-      <c r="K1" s="50" t="inlineStr">
+      <c r="K1" s="52" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="L1" s="50" t="inlineStr">
+      <c r="L1" s="52" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2761,16 +2786,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G2" s="51" t="n">
+      <c r="G2" s="53" t="n">
         <v>0.92</v>
       </c>
-      <c r="H2" s="51" t="n">
+      <c r="H2" s="53" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="I2" s="52" t="n">
+      <c r="I2" s="54" t="n">
         <v>2104</v>
       </c>
-      <c r="J2" s="52" t="n">
+      <c r="J2" s="54" t="n">
         <v>2150</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -2807,12 +2832,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G3" s="51" t="n"/>
-      <c r="H3" s="51" t="n">
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n">
         <v>0.961</v>
       </c>
-      <c r="I3" s="52" t="n"/>
-      <c r="J3" s="52" t="n">
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n">
         <v>1273</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -2853,16 +2878,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G4" s="51" t="n">
+      <c r="G4" s="53" t="n">
         <v>0.967153</v>
       </c>
-      <c r="H4" s="51" t="n">
+      <c r="H4" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="52" t="n">
+      <c r="I4" s="54" t="n">
         <v>2196</v>
       </c>
-      <c r="J4" s="52" t="n">
+      <c r="J4" s="54" t="n">
         <v>2311</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -2900,10 +2925,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G5" s="51" t="n"/>
-      <c r="H5" s="51" t="n"/>
-      <c r="I5" s="52" t="n"/>
-      <c r="J5" s="52" t="n"/>
+      <c r="G5" s="53" t="n"/>
+      <c r="H5" s="53" t="n"/>
+      <c r="I5" s="54" t="n"/>
+      <c r="J5" s="54" t="n"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2939,10 +2964,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G6" s="51" t="n"/>
-      <c r="H6" s="51" t="n"/>
-      <c r="I6" s="52" t="n"/>
-      <c r="J6" s="52" t="n"/>
+      <c r="G6" s="53" t="n"/>
+      <c r="H6" s="53" t="n"/>
+      <c r="I6" s="54" t="n"/>
+      <c r="J6" s="54" t="n"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -2978,10 +3003,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G7" s="51" t="n"/>
-      <c r="H7" s="51" t="n"/>
-      <c r="I7" s="52" t="n"/>
-      <c r="J7" s="52" t="n"/>
+      <c r="G7" s="53" t="n"/>
+      <c r="H7" s="53" t="n"/>
+      <c r="I7" s="54" t="n"/>
+      <c r="J7" s="54" t="n"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -3017,10 +3042,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G8" s="51" t="n"/>
-      <c r="H8" s="51" t="n"/>
-      <c r="I8" s="52" t="n"/>
-      <c r="J8" s="52" t="n"/>
+      <c r="G8" s="53" t="n"/>
+      <c r="H8" s="53" t="n"/>
+      <c r="I8" s="54" t="n"/>
+      <c r="J8" s="54" t="n"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -3056,10 +3081,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G9" s="51" t="n"/>
-      <c r="H9" s="51" t="n"/>
-      <c r="I9" s="52" t="n"/>
-      <c r="J9" s="52" t="n"/>
+      <c r="G9" s="53" t="n"/>
+      <c r="H9" s="53" t="n"/>
+      <c r="I9" s="54" t="n"/>
+      <c r="J9" s="54" t="n"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -3095,10 +3120,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G10" s="51" t="n"/>
-      <c r="H10" s="51" t="n"/>
-      <c r="I10" s="52" t="n"/>
-      <c r="J10" s="52" t="n"/>
+      <c r="G10" s="53" t="n"/>
+      <c r="H10" s="53" t="n"/>
+      <c r="I10" s="54" t="n"/>
+      <c r="J10" s="54" t="n"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>RealPage</t>

--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -1870,13 +1870,34 @@
       <c r="F23" s="39" t="n"/>
       <c r="G23" s="39" t="n"/>
       <c r="H23" s="39" t="n"/>
-      <c r="I23" s="39" t="n"/>
-      <c r="J23" s="40" t="n"/>
-      <c r="K23" s="40" t="n"/>
-      <c r="L23" s="40" t="n"/>
-      <c r="M23" s="40" t="n"/>
-      <c r="N23" s="40" t="n"/>
-      <c r="O23" s="40" t="n"/>
+      <c r="I23" s="39">
+        <f>IFERROR('Cash Flow (Annual)'!$F$4,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$K$4,"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$L$4,"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$M$4,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$N$4,"")</f>
+        <v/>
+      </c>
+      <c r="N23" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$O$4,"")</f>
+        <v/>
+      </c>
+      <c r="O23" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$P$4,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="14.4" customHeight="1">
       <c r="B24" s="41" t="inlineStr">
@@ -1909,12 +1930,30 @@
         <f>IFERROR(I23/H23-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="43" t="n"/>
-      <c r="K24" s="43" t="n"/>
-      <c r="L24" s="43" t="n"/>
-      <c r="M24" s="43" t="n"/>
-      <c r="N24" s="43" t="n"/>
-      <c r="O24" s="43" t="n"/>
+      <c r="J24" s="43">
+        <f>IFERROR(J23/I23-1,"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="43">
+        <f>IFERROR(K23/J23-1,"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="43">
+        <f>IFERROR(L23/K23-1,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="43">
+        <f>IFERROR(M23/L23-1,"")</f>
+        <v/>
+      </c>
+      <c r="N24" s="43">
+        <f>IFERROR(N23/M23-1,"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="43">
+        <f>IFERROR(O23/N23-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="14.4" customHeight="1">
       <c r="B25" s="23" t="inlineStr">
@@ -1928,13 +1967,34 @@
       <c r="F25" s="39" t="n"/>
       <c r="G25" s="39" t="n"/>
       <c r="H25" s="39" t="n"/>
-      <c r="I25" s="39" t="n"/>
-      <c r="J25" s="40" t="n"/>
-      <c r="K25" s="40" t="n"/>
-      <c r="L25" s="40" t="n"/>
-      <c r="M25" s="40" t="n"/>
-      <c r="N25" s="40" t="n"/>
-      <c r="O25" s="40" t="n"/>
+      <c r="I25" s="39">
+        <f>IFERROR('Cash Flow (Annual)'!$F$5,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$K$5,"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$L$5,"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$M$5,"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$N$5,"")</f>
+        <v/>
+      </c>
+      <c r="N25" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$O$5,"")</f>
+        <v/>
+      </c>
+      <c r="O25" s="40">
+        <f>IFERROR('Cash Flow (Annual)'!$P$5,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="14.4" customHeight="1">
       <c r="B26" s="41" t="inlineStr">
@@ -1967,12 +2027,30 @@
         <f>IFERROR(I25/H25-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="43" t="n"/>
-      <c r="K26" s="43" t="n"/>
-      <c r="L26" s="43" t="n"/>
-      <c r="M26" s="43" t="n"/>
-      <c r="N26" s="43" t="n"/>
-      <c r="O26" s="43" t="n"/>
+      <c r="J26" s="43">
+        <f>IFERROR(J25/I25-1,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="43">
+        <f>IFERROR(K25/J25-1,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="43">
+        <f>IFERROR(L25/K25-1,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="43">
+        <f>IFERROR(M25/L25-1,"")</f>
+        <v/>
+      </c>
+      <c r="N26" s="43">
+        <f>IFERROR(N25/M25-1,"")</f>
+        <v/>
+      </c>
+      <c r="O26" s="43">
+        <f>IFERROR(O25/N25-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="14.4" customHeight="1">
       <c r="B27" s="23" t="inlineStr">
@@ -1986,13 +2064,34 @@
       <c r="F27" s="44" t="n"/>
       <c r="G27" s="44" t="n"/>
       <c r="H27" s="44" t="n"/>
-      <c r="I27" s="44" t="n"/>
-      <c r="J27" s="45" t="n"/>
-      <c r="K27" s="45" t="n"/>
-      <c r="L27" s="45" t="n"/>
-      <c r="M27" s="45" t="n"/>
-      <c r="N27" s="45" t="n"/>
-      <c r="O27" s="45" t="n"/>
+      <c r="I27" s="44">
+        <f>IFERROR('Cash Flow (Annual)'!$F$14,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="45">
+        <f>IFERROR('Cash Flow (Annual)'!$K$14,"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="45">
+        <f>IFERROR('Cash Flow (Annual)'!$L$14,"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="45">
+        <f>IFERROR('Cash Flow (Annual)'!$M$14,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="45">
+        <f>IFERROR('Cash Flow (Annual)'!$N$14,"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="45">
+        <f>IFERROR('Cash Flow (Annual)'!$O$14,"")</f>
+        <v/>
+      </c>
+      <c r="O27" s="45">
+        <f>IFERROR('Cash Flow (Annual)'!$P$14,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="14.4" customHeight="1">
       <c r="B28" s="23" t="inlineStr">
@@ -2000,19 +2099,58 @@
           <t xml:space="preserve">  Concession %</t>
         </is>
       </c>
-      <c r="C28" s="44" t="n"/>
-      <c r="D28" s="44" t="n"/>
-      <c r="E28" s="44" t="n"/>
-      <c r="F28" s="44" t="n"/>
-      <c r="G28" s="44" t="n"/>
-      <c r="H28" s="44" t="n"/>
-      <c r="I28" s="44" t="n"/>
-      <c r="J28" s="45" t="n"/>
-      <c r="K28" s="45" t="n"/>
-      <c r="L28" s="45" t="n"/>
-      <c r="M28" s="45" t="n"/>
-      <c r="N28" s="45" t="n"/>
-      <c r="O28" s="45" t="n"/>
+      <c r="C28" s="44">
+        <f>IFERROR((C23-C25)/C23,"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="44">
+        <f>IFERROR((D23-D25)/D23,"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="44">
+        <f>IFERROR((E23-E25)/E23,"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="44">
+        <f>IFERROR((F23-F25)/F23,"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="44">
+        <f>IFERROR((G23-G25)/G23,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="44">
+        <f>IFERROR((H23-H25)/H23,"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="44">
+        <f>IFERROR((I23-I25)/I23,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="45">
+        <f>IFERROR((J23-J25)/J23,"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="45">
+        <f>IFERROR((K23-K25)/K23,"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="45">
+        <f>IFERROR((L23-L25)/L23,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="45">
+        <f>IFERROR((M23-M25)/M23,"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="45">
+        <f>IFERROR((N23-N25)/N23,"")</f>
+        <v/>
+      </c>
+      <c r="O28" s="45">
+        <f>IFERROR((O23-O25)/O23,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="14.4" customHeight="1"/>
     <row r="30" hidden="1" ht="14.4" customHeight="1">

--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -841,8 +841,10 @@
       <c r="F7" s="10" t="n">
         <v>0.961</v>
       </c>
-      <c r="G7" s="11" t="n">
-        <v>1273</v>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>

--- a/output/Canyon_Ridge__Supply_Chart.xlsx
+++ b/output/Canyon_Ridge__Supply_Chart.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="166" formatCode="0.0&quot; mi&quot;;;&quot;—&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,8 +74,19 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -92,6 +103,18 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="FF153D64"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="8"/>
     </font>
@@ -101,7 +124,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -110,7 +133,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
+        <fgColor rgb="FF153D64"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,6 +171,16 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -175,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -239,16 +272,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -257,7 +290,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -287,11 +320,11 @@
     <xf numFmtId="167" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -303,20 +336,34 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1188,7 +1235,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Z60"/>
+  <dimension ref="B1:Z69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1206,6 +1253,7 @@
     <col width="9.5" customWidth="1" min="13" max="13"/>
     <col width="9.5" customWidth="1" min="14" max="14"/>
     <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="9.5" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="18" max="18"/>
     <col width="7" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
@@ -2261,543 +2309,852 @@
     </row>
     <row r="32" ht="14.4" customHeight="1"/>
     <row r="33" ht="14.4" customHeight="1">
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>MARKET-RENT GROWTH — TMG vs 3RD-PARTY FORECAST</t>
+        </is>
+      </c>
+      <c r="C33" s="47" t="n"/>
+      <c r="D33" s="47" t="n"/>
+      <c r="E33" s="47" t="n"/>
+      <c r="F33" s="47" t="n"/>
+      <c r="G33" s="47" t="n"/>
+      <c r="H33" s="47" t="n"/>
+      <c r="I33" s="47" t="n"/>
+      <c r="J33" s="48" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K33" s="48" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L33" s="48" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M33" s="48" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N33" s="48" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O33" s="48" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="P33" s="48" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="14.4" customHeight="1">
+      <c r="B34" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CoStar</t>
+        </is>
+      </c>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+      <c r="E34" s="50" t="n"/>
+      <c r="F34" s="50" t="n"/>
+      <c r="G34" s="50" t="n"/>
+      <c r="H34" s="50" t="n"/>
+      <c r="I34" s="50" t="n"/>
+      <c r="J34" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$C$31,"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$D$31,"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$E$31,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$F$31,"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$G$31,"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$H$31,"")</f>
+        <v/>
+      </c>
+      <c r="P34" s="44">
+        <f>IFERROR(AVERAGE(J34:O34),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="14.4" customHeight="1">
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RealPage</t>
+        </is>
+      </c>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+      <c r="E35" s="50" t="n"/>
+      <c r="F35" s="50" t="n"/>
+      <c r="G35" s="50" t="n"/>
+      <c r="H35" s="50" t="n"/>
+      <c r="I35" s="50" t="n"/>
+      <c r="J35" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$C$32,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$D$32,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$E$32,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$F$32,"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$G$32,"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$H$32,"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="44">
+        <f>IFERROR(AVERAGE(J35:O35),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="14.4" customHeight="1">
+      <c r="B36" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Yardi</t>
+        </is>
+      </c>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+      <c r="E36" s="50" t="n"/>
+      <c r="F36" s="50" t="n"/>
+      <c r="G36" s="50" t="n"/>
+      <c r="H36" s="50" t="n"/>
+      <c r="I36" s="50" t="n"/>
+      <c r="J36" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$C$33,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$D$33,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$E$33,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$F$33,"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$G$33,"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$H$33,"")</f>
+        <v/>
+      </c>
+      <c r="P36" s="44">
+        <f>IFERROR(AVERAGE(J36:O36),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="14.4" customHeight="1">
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GreenStreet</t>
+        </is>
+      </c>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+      <c r="E37" s="50" t="n"/>
+      <c r="F37" s="50" t="n"/>
+      <c r="G37" s="50" t="n"/>
+      <c r="H37" s="50" t="n"/>
+      <c r="I37" s="50" t="n"/>
+      <c r="J37" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$C$34,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$D$34,"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$E$34,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$F$34,"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$G$34,"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="44">
+        <f>IFERROR('Rent &amp; Occ Data'!$H$34,"")</f>
+        <v/>
+      </c>
+      <c r="P37" s="44">
+        <f>IFERROR(AVERAGE(J37:O37),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="14.4" customHeight="1">
+      <c r="B38" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Consensus (4-source avg)</t>
+        </is>
+      </c>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+      <c r="E38" s="52" t="n"/>
+      <c r="F38" s="52" t="n"/>
+      <c r="G38" s="52" t="n"/>
+      <c r="H38" s="52" t="n"/>
+      <c r="I38" s="52" t="n"/>
+      <c r="J38" s="53">
+        <f>IFERROR(AVERAGE(J34:J37),"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="53">
+        <f>IFERROR(AVERAGE(K34:K37),"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="53">
+        <f>IFERROR(AVERAGE(L34:L37),"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="53">
+        <f>IFERROR(AVERAGE(M34:M37),"")</f>
+        <v/>
+      </c>
+      <c r="N38" s="53">
+        <f>IFERROR(AVERAGE(N34:N37),"")</f>
+        <v/>
+      </c>
+      <c r="O38" s="53">
+        <f>IFERROR(AVERAGE(O34:O37),"")</f>
+        <v/>
+      </c>
+      <c r="P38" s="53">
+        <f>IFERROR(AVERAGE(P34:P37),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="14.4" customHeight="1">
+      <c r="B39" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TMG — our market-rent growth  ◄</t>
+        </is>
+      </c>
+      <c r="C39" s="55" t="n"/>
+      <c r="D39" s="55" t="n"/>
+      <c r="E39" s="55" t="n"/>
+      <c r="F39" s="55" t="n"/>
+      <c r="G39" s="55" t="n"/>
+      <c r="H39" s="55" t="n"/>
+      <c r="I39" s="55" t="n"/>
+      <c r="J39" s="56">
+        <f>IFERROR(J24,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="56">
+        <f>IFERROR(K24,"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="56">
+        <f>IFERROR(L24,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="56">
+        <f>IFERROR(M24,"")</f>
+        <v/>
+      </c>
+      <c r="N39" s="56">
+        <f>IFERROR(N24,"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="56">
+        <f>IFERROR(O24,"")</f>
+        <v/>
+      </c>
+      <c r="P39" s="56">
+        <f>IFERROR(AVERAGE(J39:O39),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="14.4" customHeight="1"/>
+    <row r="41" ht="14.4" customHeight="1">
+      <c r="B41" s="57" t="inlineStr">
+        <is>
+          <t>▸ SCENARIO INPUTS — Bear / Base / Bull  (implied occupancy, rent-growth &amp; concession assumptions — click + to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
         </is>
       </c>
-      <c r="J33" s="47" t="inlineStr">
+      <c r="J42" s="58" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K33" s="47" t="inlineStr">
+      <c r="K42" s="58" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L33" s="47" t="inlineStr">
+      <c r="L42" s="58" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M33" s="47" t="inlineStr">
+      <c r="M42" s="58" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N33" s="47" t="inlineStr">
+      <c r="N42" s="58" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O33" s="47" t="inlineStr">
+      <c r="O42" s="58" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="14.4" customHeight="1">
-      <c r="B34" s="23" t="inlineStr">
+    <row r="43" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J34" s="48">
+      <c r="J43" s="59">
         <f>MIN($C$6,($I$31+$C$8*1)/J30)</f>
         <v/>
       </c>
-      <c r="K34" s="48">
+      <c r="K43" s="59">
         <f>MIN($C$6,($I$31+$C$8*2)/K30)</f>
         <v/>
       </c>
-      <c r="L34" s="48">
+      <c r="L43" s="59">
         <f>MIN($C$6,($I$31+$C$8*3)/L30)</f>
         <v/>
       </c>
-      <c r="M34" s="48">
+      <c r="M43" s="59">
         <f>MIN($C$6,($I$31+$C$8*4)/M30)</f>
         <v/>
       </c>
-      <c r="N34" s="48">
+      <c r="N43" s="59">
         <f>MIN($C$6,($I$31+$C$8*5)/N30)</f>
         <v/>
       </c>
-      <c r="O34" s="48">
+      <c r="O43" s="59">
         <f>MIN($C$6,($I$31+$C$8*6)/O30)</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="14.4" customHeight="1">
-      <c r="B35" s="23" t="inlineStr">
+    <row r="44" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J35" s="48">
+      <c r="J44" s="59">
         <f>MIN($C$6,($I$31+$C$9*1)/J30)</f>
         <v/>
       </c>
-      <c r="K35" s="48">
+      <c r="K44" s="59">
         <f>MIN($C$6,($I$31+$C$9*2)/K30)</f>
         <v/>
       </c>
-      <c r="L35" s="48">
+      <c r="L44" s="59">
         <f>MIN($C$6,($I$31+$C$9*3)/L30)</f>
         <v/>
       </c>
-      <c r="M35" s="48">
+      <c r="M44" s="59">
         <f>MIN($C$6,($I$31+$C$9*4)/M30)</f>
         <v/>
       </c>
-      <c r="N35" s="48">
+      <c r="N44" s="59">
         <f>MIN($C$6,($I$31+$C$9*5)/N30)</f>
         <v/>
       </c>
-      <c r="O35" s="48">
+      <c r="O44" s="59">
         <f>MIN($C$6,($I$31+$C$9*6)/O30)</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="14.4" customHeight="1">
-      <c r="B36" s="23" t="inlineStr">
+    <row r="45" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J36" s="48">
+      <c r="J45" s="59">
         <f>MIN($C$6,($I$31+$C$10*1)/J30)</f>
         <v/>
       </c>
-      <c r="K36" s="48">
+      <c r="K45" s="59">
         <f>MIN($C$6,($I$31+$C$10*2)/K30)</f>
         <v/>
       </c>
-      <c r="L36" s="48">
+      <c r="L45" s="59">
         <f>MIN($C$6,($I$31+$C$10*3)/L30)</f>
         <v/>
       </c>
-      <c r="M36" s="48">
+      <c r="M45" s="59">
         <f>MIN($C$6,($I$31+$C$10*4)/M30)</f>
         <v/>
       </c>
-      <c r="N36" s="48">
+      <c r="N45" s="59">
         <f>MIN($C$6,($I$31+$C$10*5)/N30)</f>
         <v/>
       </c>
-      <c r="O36" s="48">
+      <c r="O45" s="59">
         <f>MIN($C$6,($I$31+$C$10*6)/O30)</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="14.4" customHeight="1"/>
-    <row r="38" ht="14.4" customHeight="1">
-      <c r="B38" s="23" t="inlineStr">
+    <row r="46" hidden="1" outlineLevel="1" ht="14.4" customHeight="1"/>
+    <row r="47" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>MARKET RENT GROWTH (editable assumptions)</t>
         </is>
       </c>
-      <c r="J38" s="49" t="inlineStr">
+      <c r="J47" s="60" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K38" s="49" t="inlineStr">
+      <c r="K47" s="60" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L38" s="49" t="inlineStr">
+      <c r="L47" s="60" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M38" s="49" t="inlineStr">
+      <c r="M47" s="60" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N38" s="49" t="inlineStr">
+      <c r="N47" s="60" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O38" s="49" t="inlineStr">
+      <c r="O47" s="60" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="14.4" customHeight="1">
-      <c r="B39" s="23" t="inlineStr">
+    <row r="48" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J39" s="50" t="n">
+      <c r="J48" s="61" t="n">
         <v>-0.0025</v>
       </c>
-      <c r="K39" s="50" t="n">
+      <c r="K48" s="61" t="n">
         <v>0.0175</v>
       </c>
-      <c r="L39" s="50" t="n">
+      <c r="L48" s="61" t="n">
         <v>0.0275</v>
       </c>
-      <c r="M39" s="50" t="n">
+      <c r="M48" s="61" t="n">
         <v>0.0375</v>
       </c>
-      <c r="N39" s="50" t="n">
+      <c r="N48" s="61" t="n">
         <v>0.0275</v>
       </c>
-      <c r="O39" s="50" t="n">
+      <c r="O48" s="61" t="n">
         <v>0.0175</v>
       </c>
     </row>
-    <row r="40" ht="14.4" customHeight="1">
-      <c r="B40" s="23" t="inlineStr">
+    <row r="49" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J40" s="50" t="n">
+      <c r="J49" s="61" t="n">
         <v>0.01</v>
       </c>
-      <c r="K40" s="50" t="n">
+      <c r="K49" s="61" t="n">
         <v>0.03</v>
       </c>
-      <c r="L40" s="50" t="n">
+      <c r="L49" s="61" t="n">
         <v>0.04</v>
       </c>
-      <c r="M40" s="50" t="n">
+      <c r="M49" s="61" t="n">
         <v>0.05</v>
       </c>
-      <c r="N40" s="50" t="n">
+      <c r="N49" s="61" t="n">
         <v>0.04</v>
       </c>
-      <c r="O40" s="50" t="n">
+      <c r="O49" s="61" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="41" ht="14.4" customHeight="1">
-      <c r="B41" s="23" t="inlineStr">
+    <row r="50" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J41" s="50" t="n">
+      <c r="J50" s="61" t="n">
         <v>0.02</v>
       </c>
-      <c r="K41" s="50" t="n">
+      <c r="K50" s="61" t="n">
         <v>0.04</v>
       </c>
-      <c r="L41" s="50" t="n">
+      <c r="L50" s="61" t="n">
         <v>0.05</v>
       </c>
-      <c r="M41" s="50" t="n">
+      <c r="M50" s="61" t="n">
         <v>0.06</v>
       </c>
-      <c r="N41" s="50" t="n">
+      <c r="N50" s="61" t="n">
         <v>0.05</v>
       </c>
-      <c r="O41" s="50" t="n">
+      <c r="O50" s="61" t="n">
         <v>0.04</v>
       </c>
     </row>
-    <row r="42" ht="14.4" customHeight="1">
-      <c r="B42" s="23" t="inlineStr">
+    <row r="51" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B51" s="23" t="inlineStr">
         <is>
           <t>CONCESSIONS % — forward assumption (editable)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="14.4" customHeight="1">
-      <c r="B43" s="23" t="inlineStr">
+    <row r="52" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J43" s="50" t="n">
+      <c r="J52" s="61" t="n">
         <v>0.06</v>
       </c>
-      <c r="K43" s="50" t="n">
+      <c r="K52" s="61" t="n">
         <v>0.045</v>
       </c>
-      <c r="L43" s="50" t="n">
+      <c r="L52" s="61" t="n">
         <v>0.035</v>
       </c>
-      <c r="M43" s="50" t="n">
+      <c r="M52" s="61" t="n">
         <v>0.035</v>
       </c>
-      <c r="N43" s="50" t="n">
+      <c r="N52" s="61" t="n">
         <v>0.035</v>
       </c>
-      <c r="O43" s="50" t="n">
+      <c r="O52" s="61" t="n">
         <v>0.035</v>
       </c>
     </row>
-    <row r="44" ht="14.4" customHeight="1">
-      <c r="B44" s="23" t="inlineStr">
+    <row r="53" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B53" s="23" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J44" s="50" t="n">
+      <c r="J53" s="61" t="n">
         <v>0.03</v>
       </c>
-      <c r="K44" s="50" t="n">
+      <c r="K53" s="61" t="n">
         <v>0.015</v>
       </c>
-      <c r="L44" s="50" t="n">
+      <c r="L53" s="61" t="n">
         <v>0.005</v>
       </c>
-      <c r="M44" s="50" t="n">
+      <c r="M53" s="61" t="n">
         <v>0.005</v>
       </c>
-      <c r="N44" s="50" t="n">
+      <c r="N53" s="61" t="n">
         <v>0.005</v>
       </c>
-      <c r="O44" s="50" t="n">
+      <c r="O53" s="61" t="n">
         <v>0.005</v>
       </c>
     </row>
-    <row r="45" ht="14.4" customHeight="1">
-      <c r="B45" s="23" t="inlineStr">
+    <row r="54" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B54" s="23" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J45" s="50" t="n">
+      <c r="J54" s="61" t="n">
         <v>0.02</v>
       </c>
-      <c r="K45" s="50" t="n">
+      <c r="K54" s="61" t="n">
         <v>0.005</v>
       </c>
-      <c r="L45" s="50" t="n">
+      <c r="L54" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="50" t="n">
+      <c r="M54" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="50" t="n">
+      <c r="N54" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="50" t="n">
+      <c r="O54" s="61" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="46" ht="14.4" customHeight="1">
-      <c r="B46" s="23" t="inlineStr">
+    <row r="55" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>EFFECTIVE RENT GROWTH (derived)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="14.4" customHeight="1">
-      <c r="B47" s="23" t="inlineStr">
+    <row r="56" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B56" s="23" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J47" s="48">
-        <f>(1+J39)*(1-J43)-1</f>
-        <v/>
-      </c>
-      <c r="K47" s="48">
-        <f>(1+K39)*(1-K43)/(1-J43)-1</f>
-        <v/>
-      </c>
-      <c r="L47" s="48">
-        <f>(1+L39)*(1-L43)/(1-K43)-1</f>
-        <v/>
-      </c>
-      <c r="M47" s="48">
-        <f>(1+M39)*(1-M43)/(1-L43)-1</f>
-        <v/>
-      </c>
-      <c r="N47" s="48">
-        <f>(1+N39)*(1-N43)/(1-M43)-1</f>
-        <v/>
-      </c>
-      <c r="O47" s="48">
-        <f>(1+O39)*(1-O43)/(1-N43)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="14.4" customHeight="1">
-      <c r="B48" s="23" t="inlineStr">
+      <c r="J56" s="59">
+        <f>(1+J48)*(1-J52)-1</f>
+        <v/>
+      </c>
+      <c r="K56" s="59">
+        <f>(1+K48)*(1-K52)/(1-J52)-1</f>
+        <v/>
+      </c>
+      <c r="L56" s="59">
+        <f>(1+L48)*(1-L52)/(1-K52)-1</f>
+        <v/>
+      </c>
+      <c r="M56" s="59">
+        <f>(1+M48)*(1-M52)/(1-L52)-1</f>
+        <v/>
+      </c>
+      <c r="N56" s="59">
+        <f>(1+N48)*(1-N52)/(1-M52)-1</f>
+        <v/>
+      </c>
+      <c r="O56" s="59">
+        <f>(1+O48)*(1-O52)/(1-N52)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B57" s="23" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J48" s="48">
-        <f>(1+J40)*(1-J44)-1</f>
-        <v/>
-      </c>
-      <c r="K48" s="48">
-        <f>(1+K40)*(1-K44)/(1-J44)-1</f>
-        <v/>
-      </c>
-      <c r="L48" s="48">
-        <f>(1+L40)*(1-L44)/(1-K44)-1</f>
-        <v/>
-      </c>
-      <c r="M48" s="48">
-        <f>(1+M40)*(1-M44)/(1-L44)-1</f>
-        <v/>
-      </c>
-      <c r="N48" s="48">
-        <f>(1+N40)*(1-N44)/(1-M44)-1</f>
-        <v/>
-      </c>
-      <c r="O48" s="48">
-        <f>(1+O40)*(1-O44)/(1-N44)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="14.4" customHeight="1">
-      <c r="B49" s="23" t="inlineStr">
+      <c r="J57" s="59">
+        <f>(1+J49)*(1-J53)-1</f>
+        <v/>
+      </c>
+      <c r="K57" s="59">
+        <f>(1+K49)*(1-K53)/(1-J53)-1</f>
+        <v/>
+      </c>
+      <c r="L57" s="59">
+        <f>(1+L49)*(1-L53)/(1-K53)-1</f>
+        <v/>
+      </c>
+      <c r="M57" s="59">
+        <f>(1+M49)*(1-M53)/(1-L53)-1</f>
+        <v/>
+      </c>
+      <c r="N57" s="59">
+        <f>(1+N49)*(1-N53)/(1-M53)-1</f>
+        <v/>
+      </c>
+      <c r="O57" s="59">
+        <f>(1+O49)*(1-O53)/(1-N53)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B58" s="23" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J49" s="48">
-        <f>(1+J41)*(1-J45)-1</f>
-        <v/>
-      </c>
-      <c r="K49" s="48">
-        <f>(1+K41)*(1-K45)/(1-J45)-1</f>
-        <v/>
-      </c>
-      <c r="L49" s="48">
-        <f>(1+L41)*(1-L45)/(1-K45)-1</f>
-        <v/>
-      </c>
-      <c r="M49" s="48">
-        <f>(1+M41)*(1-M45)/(1-L45)-1</f>
-        <v/>
-      </c>
-      <c r="N49" s="48">
-        <f>(1+N41)*(1-N45)/(1-M45)-1</f>
-        <v/>
-      </c>
-      <c r="O49" s="48">
-        <f>(1+O41)*(1-O45)/(1-N45)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="14.4" customHeight="1"/>
-    <row r="51" ht="14.4" customHeight="1">
-      <c r="B51" s="49" t="inlineStr">
+      <c r="J58" s="59">
+        <f>(1+J50)*(1-J54)-1</f>
+        <v/>
+      </c>
+      <c r="K58" s="59">
+        <f>(1+K50)*(1-K54)/(1-J54)-1</f>
+        <v/>
+      </c>
+      <c r="L58" s="59">
+        <f>(1+L50)*(1-L54)/(1-K54)-1</f>
+        <v/>
+      </c>
+      <c r="M58" s="59">
+        <f>(1+M50)*(1-M54)/(1-L54)-1</f>
+        <v/>
+      </c>
+      <c r="N58" s="59">
+        <f>(1+N50)*(1-N54)/(1-M54)-1</f>
+        <v/>
+      </c>
+      <c r="O58" s="59">
+        <f>(1+O50)*(1-O54)/(1-N54)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="14.4" customHeight="1"/>
+    <row r="60" ht="14.4" customHeight="1">
+      <c r="B60" s="60" t="inlineStr">
         <is>
           <t>▸ DETAIL: subject rent source by year &amp; reconciliation (grouped — click − to collapse)</t>
         </is>
       </c>
     </row>
-    <row r="52" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B52" s="51" t="inlineStr">
+    <row r="61" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B61" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y6  Q3 2019–Q2 2020</t>
         </is>
       </c>
-      <c r="E52" s="51" t="inlineStr">
+      <c r="E61" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="53" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B53" s="51" t="inlineStr">
+    <row r="62" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B62" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y5  Q3 2020–Q2 2021</t>
         </is>
       </c>
-      <c r="E53" s="51" t="inlineStr">
+      <c r="E62" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="54" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B54" s="51" t="inlineStr">
+    <row r="63" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B63" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y4  Q3 2021–Q2 2022</t>
         </is>
       </c>
-      <c r="E54" s="51" t="inlineStr">
+      <c r="E63" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="55" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B55" s="51" t="inlineStr">
+    <row r="64" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B64" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y3  Q3 2022–Q2 2023</t>
         </is>
       </c>
-      <c r="E55" s="51" t="inlineStr">
+      <c r="E64" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="56" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B56" s="51" t="inlineStr">
+    <row r="65" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B65" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y2  Q3 2023–Q2 2024</t>
         </is>
       </c>
-      <c r="E56" s="51" t="inlineStr">
+      <c r="E65" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="57" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B57" s="51" t="inlineStr">
+    <row r="66" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B66" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y1  Q3 2024–Q2 2025</t>
         </is>
       </c>
-      <c r="E57" s="51" t="inlineStr">
+      <c r="E66" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="58" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B58" s="51" t="inlineStr">
+    <row r="67" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B67" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  Y0  Q3 2025–Q2 2026</t>
         </is>
       </c>
-      <c r="E58" s="51" t="inlineStr">
+      <c r="E67" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="59" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B59" s="51" t="inlineStr">
+    <row r="68" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B68" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  UC scheduled vs CoStar UC</t>
         </is>
       </c>
-      <c r="E59" s="51" t="inlineStr">
+      <c r="E68" s="62" t="inlineStr">
         <is>
           <t>0 / 27</t>
         </is>
       </c>
     </row>
-    <row r="60" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B60" s="21" t="inlineStr">
+    <row r="69" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B69" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  As-of 2026 Q2 QTD is partial (QTD); occupancy is point-in-time, Y0 flow sums partial.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="14.4" customHeight="1"/>
-    <row r="62" ht="14.4" customHeight="1"/>
+    <row r="70" ht="14.4" customHeight="1"/>
+    <row r="71" ht="14.4" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:O2"/>
@@ -2838,62 +3195,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B1" s="52" t="inlineStr">
+      <c r="B1" s="48" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="52" t="inlineStr">
+      <c r="C1" s="48" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D1" s="52" t="inlineStr">
+      <c r="D1" s="48" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="E1" s="52" t="inlineStr">
+      <c r="E1" s="48" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="F1" s="52" t="inlineStr">
+      <c r="F1" s="48" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="G1" s="52" t="inlineStr">
+      <c r="G1" s="48" t="inlineStr">
         <is>
           <t>CoStar Occ</t>
         </is>
       </c>
-      <c r="H1" s="52" t="inlineStr">
+      <c r="H1" s="48" t="inlineStr">
         <is>
           <t>RealPage Occ</t>
         </is>
       </c>
-      <c r="I1" s="52" t="inlineStr">
+      <c r="I1" s="48" t="inlineStr">
         <is>
           <t>CoStar Ask Rent</t>
         </is>
       </c>
-      <c r="J1" s="52" t="inlineStr">
+      <c r="J1" s="48" t="inlineStr">
         <is>
           <t>RealPage Eff Rent</t>
         </is>
       </c>
-      <c r="K1" s="52" t="inlineStr">
+      <c r="K1" s="48" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="L1" s="52" t="inlineStr">
+      <c r="L1" s="48" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2926,16 +3283,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G2" s="53" t="n">
+      <c r="G2" s="63" t="n">
         <v>0.92</v>
       </c>
-      <c r="H2" s="53" t="n">
+      <c r="H2" s="63" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="I2" s="54" t="n">
+      <c r="I2" s="64" t="n">
         <v>2104</v>
       </c>
-      <c r="J2" s="54" t="n">
+      <c r="J2" s="64" t="n">
         <v>2150</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -2972,12 +3329,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G3" s="53" t="n"/>
-      <c r="H3" s="53" t="n">
+      <c r="G3" s="63" t="n"/>
+      <c r="H3" s="63" t="n">
         <v>0.961</v>
       </c>
-      <c r="I3" s="54" t="n"/>
-      <c r="J3" s="54" t="n">
+      <c r="I3" s="64" t="n"/>
+      <c r="J3" s="64" t="n">
         <v>1273</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -3018,16 +3375,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G4" s="53" t="n">
+      <c r="G4" s="63" t="n">
         <v>0.967153</v>
       </c>
-      <c r="H4" s="53" t="n">
+      <c r="H4" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="54" t="n">
+      <c r="I4" s="64" t="n">
         <v>2196</v>
       </c>
-      <c r="J4" s="54" t="n">
+      <c r="J4" s="64" t="n">
         <v>2311</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -3065,10 +3422,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G5" s="53" t="n"/>
-      <c r="H5" s="53" t="n"/>
-      <c r="I5" s="54" t="n"/>
-      <c r="J5" s="54" t="n"/>
+      <c r="G5" s="63" t="n"/>
+      <c r="H5" s="63" t="n"/>
+      <c r="I5" s="64" t="n"/>
+      <c r="J5" s="64" t="n"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -3104,10 +3461,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G6" s="53" t="n"/>
-      <c r="H6" s="53" t="n"/>
-      <c r="I6" s="54" t="n"/>
-      <c r="J6" s="54" t="n"/>
+      <c r="G6" s="63" t="n"/>
+      <c r="H6" s="63" t="n"/>
+      <c r="I6" s="64" t="n"/>
+      <c r="J6" s="64" t="n"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -3143,10 +3500,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G7" s="53" t="n"/>
-      <c r="H7" s="53" t="n"/>
-      <c r="I7" s="54" t="n"/>
-      <c r="J7" s="54" t="n"/>
+      <c r="G7" s="63" t="n"/>
+      <c r="H7" s="63" t="n"/>
+      <c r="I7" s="64" t="n"/>
+      <c r="J7" s="64" t="n"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -3182,10 +3539,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G8" s="53" t="n"/>
-      <c r="H8" s="53" t="n"/>
-      <c r="I8" s="54" t="n"/>
-      <c r="J8" s="54" t="n"/>
+      <c r="G8" s="63" t="n"/>
+      <c r="H8" s="63" t="n"/>
+      <c r="I8" s="64" t="n"/>
+      <c r="J8" s="64" t="n"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -3221,10 +3578,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G9" s="53" t="n"/>
-      <c r="H9" s="53" t="n"/>
-      <c r="I9" s="54" t="n"/>
-      <c r="J9" s="54" t="n"/>
+      <c r="G9" s="63" t="n"/>
+      <c r="H9" s="63" t="n"/>
+      <c r="I9" s="64" t="n"/>
+      <c r="J9" s="64" t="n"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -3260,10 +3617,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G10" s="53" t="n"/>
-      <c r="H10" s="53" t="n"/>
-      <c r="I10" s="54" t="n"/>
-      <c r="J10" s="54" t="n"/>
+      <c r="G10" s="63" t="n"/>
+      <c r="H10" s="63" t="n"/>
+      <c r="I10" s="64" t="n"/>
+      <c r="J10" s="64" t="n"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>RealPage</t>
